--- a/artfynd/A 1159-2026 artfynd.xlsx
+++ b/artfynd/A 1159-2026 artfynd.xlsx
@@ -1499,41 +1499,40 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131153663</v>
+        <v>131153632</v>
       </c>
       <c r="B10" t="n">
-        <v>8451</v>
+        <v>57881</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1543,10 +1542,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>433024</v>
+        <v>433068</v>
       </c>
       <c r="R10" t="n">
-        <v>6792572</v>
+        <v>6792622</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1587,7 +1586,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1606,40 +1604,41 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131153632</v>
+        <v>131153656</v>
       </c>
       <c r="B11" t="n">
-        <v>57881</v>
+        <v>8451</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N11" t="inlineStr"/>
@@ -1649,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>433068</v>
+        <v>432815</v>
       </c>
       <c r="R11" t="n">
-        <v>6792622</v>
+        <v>6792564</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1693,6 +1692,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1711,7 +1711,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131153656</v>
+        <v>131153663</v>
       </c>
       <c r="B12" t="n">
         <v>8451</v>
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>432815</v>
+        <v>433024</v>
       </c>
       <c r="R12" t="n">
-        <v>6792564</v>
+        <v>6792572</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1818,10 +1818,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131153712</v>
+        <v>131153676</v>
       </c>
       <c r="B13" t="n">
-        <v>79244</v>
+        <v>79001</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1829,21 +1829,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1853,10 +1853,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>432967</v>
+        <v>432719</v>
       </c>
       <c r="R13" t="n">
-        <v>6792669</v>
+        <v>6792423</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1915,10 +1915,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131153621</v>
+        <v>131153712</v>
       </c>
       <c r="B14" t="n">
-        <v>79834</v>
+        <v>79244</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1926,21 +1926,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1950,10 +1950,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>433070</v>
+        <v>432967</v>
       </c>
       <c r="R14" t="n">
-        <v>6792624</v>
+        <v>6792669</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2012,10 +2012,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131153676</v>
+        <v>131153720</v>
       </c>
       <c r="B15" t="n">
-        <v>79001</v>
+        <v>79244</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2023,21 +2023,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2047,10 +2047,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>432719</v>
+        <v>432962</v>
       </c>
       <c r="R15" t="n">
-        <v>6792423</v>
+        <v>6792773</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2109,10 +2109,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131153720</v>
+        <v>131153621</v>
       </c>
       <c r="B16" t="n">
-        <v>79244</v>
+        <v>79834</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2120,21 +2120,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2144,10 +2144,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>432962</v>
+        <v>433070</v>
       </c>
       <c r="R16" t="n">
-        <v>6792773</v>
+        <v>6792624</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2206,40 +2206,41 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131153635</v>
+        <v>131153668</v>
       </c>
       <c r="B17" t="n">
-        <v>57881</v>
+        <v>8451</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2249,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>432968</v>
+        <v>432974</v>
       </c>
       <c r="R17" t="n">
-        <v>6792680</v>
+        <v>6792777</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2293,6 +2294,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2509,41 +2511,40 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131153645</v>
+        <v>131153635</v>
       </c>
       <c r="B20" t="n">
-        <v>5480</v>
+        <v>57881</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>101920</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2553,10 +2554,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>432996</v>
+        <v>432968</v>
       </c>
       <c r="R20" t="n">
-        <v>6792672</v>
+        <v>6792680</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2595,9 +2596,8 @@
         <v>0</v>
       </c>
       <c r="AE20" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF20" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2616,32 +2616,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131153668</v>
+        <v>131153645</v>
       </c>
       <c r="B21" t="n">
-        <v>8451</v>
+        <v>5480</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>101920</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2660,10 +2660,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>432974</v>
+        <v>432996</v>
       </c>
       <c r="R21" t="n">
-        <v>6792777</v>
+        <v>6792672</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2702,7 +2702,7 @@
         <v>0</v>
       </c>
       <c r="AE21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
@@ -2723,10 +2723,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131153729</v>
+        <v>131153622</v>
       </c>
       <c r="B22" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2734,34 +2734,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>432924</v>
+        <v>432996</v>
       </c>
       <c r="R22" t="n">
-        <v>6792835</v>
+        <v>6792778</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2921,10 +2929,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131153622</v>
+        <v>131153729</v>
       </c>
       <c r="B24" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2932,42 +2940,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>432996</v>
+        <v>432924</v>
       </c>
       <c r="R24" t="n">
-        <v>6792778</v>
+        <v>6792835</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3424,10 +3424,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131153716</v>
+        <v>131153630</v>
       </c>
       <c r="B29" t="n">
-        <v>79244</v>
+        <v>57881</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3435,34 +3435,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>432960</v>
+        <v>433062</v>
       </c>
       <c r="R29" t="n">
-        <v>6792712</v>
+        <v>6792357</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3521,7 +3529,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131153630</v>
+        <v>131153641</v>
       </c>
       <c r="B30" t="n">
         <v>57881</v>
@@ -3554,7 +3562,7 @@
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -3564,10 +3572,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>433062</v>
+        <v>432909</v>
       </c>
       <c r="R30" t="n">
-        <v>6792357</v>
+        <v>6792876</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3626,10 +3634,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131153641</v>
+        <v>131153616</v>
       </c>
       <c r="B31" t="n">
-        <v>57881</v>
+        <v>79834</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3637,42 +3645,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>432909</v>
+        <v>432773</v>
       </c>
       <c r="R31" t="n">
-        <v>6792876</v>
+        <v>6792537</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3731,54 +3731,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131153658</v>
+        <v>131153716</v>
       </c>
       <c r="B32" t="n">
-        <v>8451</v>
+        <v>79244</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>433053</v>
+        <v>432960</v>
       </c>
       <c r="R32" t="n">
-        <v>6792381</v>
+        <v>6792712</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3819,7 +3810,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3838,43 +3828,37 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131153665</v>
+        <v>131153690</v>
       </c>
       <c r="B33" t="n">
-        <v>8451</v>
+        <v>79244</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3882,10 +3866,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>432959</v>
+        <v>432874</v>
       </c>
       <c r="R33" t="n">
-        <v>6792711</v>
+        <v>6792733</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3945,45 +3929,54 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131153616</v>
+        <v>131153658</v>
       </c>
       <c r="B34" t="n">
-        <v>79834</v>
+        <v>8451</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>432773</v>
+        <v>433053</v>
       </c>
       <c r="R34" t="n">
-        <v>6792537</v>
+        <v>6792381</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4024,6 +4017,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4042,37 +4036,43 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131153690</v>
+        <v>131153665</v>
       </c>
       <c r="B35" t="n">
-        <v>79244</v>
+        <v>8451</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4080,10 +4080,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>432874</v>
+        <v>432959</v>
       </c>
       <c r="R35" t="n">
-        <v>6792733</v>
+        <v>6792711</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4143,10 +4143,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131153628</v>
+        <v>131153703</v>
       </c>
       <c r="B36" t="n">
-        <v>57881</v>
+        <v>79244</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4154,42 +4154,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>432884</v>
+        <v>433063</v>
       </c>
       <c r="R36" t="n">
-        <v>6792734</v>
+        <v>6792351</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4442,7 +4434,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131153703</v>
+        <v>131153714</v>
       </c>
       <c r="B39" t="n">
         <v>79244</v>
@@ -4477,10 +4469,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>433063</v>
+        <v>432946</v>
       </c>
       <c r="R39" t="n">
-        <v>6792351</v>
+        <v>6792696</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4513,6 +4505,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Måttligt med garnlav inom en radie av 50 m</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4539,10 +4536,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131153714</v>
+        <v>131153628</v>
       </c>
       <c r="B40" t="n">
-        <v>79244</v>
+        <v>57881</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4550,34 +4547,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>432946</v>
+        <v>432884</v>
       </c>
       <c r="R40" t="n">
-        <v>6792696</v>
+        <v>6792734</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4610,11 +4615,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-02-14</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Måttligt med garnlav inom en radie av 50 m</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4641,10 +4641,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131153643</v>
+        <v>131153708</v>
       </c>
       <c r="B41" t="n">
-        <v>57881</v>
+        <v>79244</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4652,42 +4652,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>432969</v>
+        <v>433106</v>
       </c>
       <c r="R41" t="n">
-        <v>6792418</v>
+        <v>6792609</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4746,10 +4738,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131153640</v>
+        <v>131153710</v>
       </c>
       <c r="B42" t="n">
-        <v>57881</v>
+        <v>79244</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4757,42 +4749,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>432940</v>
+        <v>433013</v>
       </c>
       <c r="R42" t="n">
-        <v>6792843</v>
+        <v>6792587</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4851,7 +4835,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131153708</v>
+        <v>131153691</v>
       </c>
       <c r="B43" t="n">
         <v>79244</v>
@@ -4886,10 +4870,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>433106</v>
+        <v>432881</v>
       </c>
       <c r="R43" t="n">
-        <v>6792609</v>
+        <v>6792694</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4948,7 +4932,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131153710</v>
+        <v>131153722</v>
       </c>
       <c r="B44" t="n">
         <v>79244</v>
@@ -4983,10 +4967,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>433013</v>
+        <v>432939</v>
       </c>
       <c r="R44" t="n">
-        <v>6792587</v>
+        <v>6792795</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5045,7 +5029,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131153691</v>
+        <v>131153692</v>
       </c>
       <c r="B45" t="n">
         <v>79244</v>
@@ -5080,10 +5064,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>432881</v>
+        <v>432901</v>
       </c>
       <c r="R45" t="n">
-        <v>6792694</v>
+        <v>6792625</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5142,10 +5126,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131153722</v>
+        <v>131153643</v>
       </c>
       <c r="B46" t="n">
-        <v>79244</v>
+        <v>57881</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5153,34 +5137,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>432939</v>
+        <v>432969</v>
       </c>
       <c r="R46" t="n">
-        <v>6792795</v>
+        <v>6792418</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5239,10 +5231,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131153692</v>
+        <v>131153640</v>
       </c>
       <c r="B47" t="n">
-        <v>79244</v>
+        <v>57881</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5250,34 +5242,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>432901</v>
+        <v>432940</v>
       </c>
       <c r="R47" t="n">
-        <v>6792625</v>
+        <v>6792843</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5550,10 +5550,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131153631</v>
+        <v>131153709</v>
       </c>
       <c r="B50" t="n">
-        <v>57881</v>
+        <v>79244</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5561,42 +5561,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>433074</v>
+        <v>433034</v>
       </c>
       <c r="R50" t="n">
-        <v>6792635</v>
+        <v>6792553</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5655,7 +5647,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131153709</v>
+        <v>131153713</v>
       </c>
       <c r="B51" t="n">
         <v>79244</v>
@@ -5690,10 +5682,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>433034</v>
+        <v>432988</v>
       </c>
       <c r="R51" t="n">
-        <v>6792553</v>
+        <v>6792669</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5752,10 +5744,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131153700</v>
+        <v>131153631</v>
       </c>
       <c r="B52" t="n">
-        <v>79244</v>
+        <v>57881</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5763,34 +5755,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>432910</v>
+        <v>433074</v>
       </c>
       <c r="R52" t="n">
-        <v>6792364</v>
+        <v>6792635</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5849,7 +5849,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131153713</v>
+        <v>131153700</v>
       </c>
       <c r="B53" t="n">
         <v>79244</v>
@@ -5884,10 +5884,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>432988</v>
+        <v>432910</v>
       </c>
       <c r="R53" t="n">
-        <v>6792669</v>
+        <v>6792364</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6148,10 +6148,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131153638</v>
+        <v>131153697</v>
       </c>
       <c r="B56" t="n">
-        <v>57881</v>
+        <v>79244</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6159,42 +6159,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>432927</v>
+        <v>432785</v>
       </c>
       <c r="R56" t="n">
-        <v>6792752</v>
+        <v>6792460</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6253,7 +6245,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131153697</v>
+        <v>131153704</v>
       </c>
       <c r="B57" t="n">
         <v>79244</v>
@@ -6288,10 +6280,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>432785</v>
+        <v>433115</v>
       </c>
       <c r="R57" t="n">
-        <v>6792460</v>
+        <v>6792436</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6738,10 +6730,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131153704</v>
+        <v>131153638</v>
       </c>
       <c r="B62" t="n">
-        <v>79244</v>
+        <v>57881</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6749,34 +6741,42 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>433115</v>
+        <v>432927</v>
       </c>
       <c r="R62" t="n">
-        <v>6792436</v>
+        <v>6792752</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6835,10 +6835,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131153693</v>
+        <v>131153633</v>
       </c>
       <c r="B63" t="n">
-        <v>79244</v>
+        <v>57881</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6846,34 +6846,42 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>432849</v>
+        <v>432972</v>
       </c>
       <c r="R63" t="n">
-        <v>6792616</v>
+        <v>6792667</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6932,7 +6940,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131153727</v>
+        <v>131153693</v>
       </c>
       <c r="B64" t="n">
         <v>79244</v>
@@ -6961,19 +6969,16 @@
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>432935</v>
+        <v>432849</v>
       </c>
       <c r="R64" t="n">
-        <v>6792834</v>
+        <v>6792616</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7014,7 +7019,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7033,43 +7037,37 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131153654</v>
+        <v>131153727</v>
       </c>
       <c r="B65" t="n">
-        <v>8451</v>
+        <v>79244</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7077,10 +7075,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>432866</v>
+        <v>432935</v>
       </c>
       <c r="R65" t="n">
-        <v>6792755</v>
+        <v>6792834</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7140,40 +7138,41 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131153633</v>
+        <v>131153654</v>
       </c>
       <c r="B66" t="n">
-        <v>57881</v>
+        <v>8451</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -7183,10 +7182,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>432972</v>
+        <v>432866</v>
       </c>
       <c r="R66" t="n">
-        <v>6792667</v>
+        <v>6792755</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7227,6 +7226,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7439,41 +7439,40 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131153655</v>
+        <v>131153636</v>
       </c>
       <c r="B69" t="n">
-        <v>8451</v>
+        <v>57881</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
@@ -7483,10 +7482,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>432876</v>
+        <v>432931</v>
       </c>
       <c r="R69" t="n">
-        <v>6792590</v>
+        <v>6792717</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7527,7 +7526,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7546,10 +7544,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131153620</v>
+        <v>131153634</v>
       </c>
       <c r="B70" t="n">
-        <v>79834</v>
+        <v>57881</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7557,26 +7555,31 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -7584,10 +7587,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>433058</v>
+        <v>432989</v>
       </c>
       <c r="R70" t="n">
-        <v>6792468</v>
+        <v>6792671</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7628,7 +7631,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7647,40 +7649,41 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131153636</v>
+        <v>131153655</v>
       </c>
       <c r="B71" t="n">
-        <v>57881</v>
+        <v>8451</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N71" t="inlineStr"/>
@@ -7690,10 +7693,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>432931</v>
+        <v>432876</v>
       </c>
       <c r="R71" t="n">
-        <v>6792717</v>
+        <v>6792590</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7734,6 +7737,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7752,10 +7756,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131153634</v>
+        <v>131153620</v>
       </c>
       <c r="B72" t="n">
-        <v>57881</v>
+        <v>79834</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7763,31 +7767,26 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -7795,10 +7794,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>432989</v>
+        <v>433058</v>
       </c>
       <c r="R72" t="n">
-        <v>6792671</v>
+        <v>6792468</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7839,6 +7838,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7857,10 +7857,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131153639</v>
+        <v>131153625</v>
       </c>
       <c r="B73" t="n">
-        <v>57881</v>
+        <v>91830</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7868,31 +7868,26 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -7900,10 +7895,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>432988</v>
+        <v>433119</v>
       </c>
       <c r="R73" t="n">
-        <v>6792798</v>
+        <v>6792436</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7944,6 +7939,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -7962,7 +7958,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131153721</v>
+        <v>131153711</v>
       </c>
       <c r="B74" t="n">
         <v>79244</v>
@@ -7991,19 +7987,16 @@
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>432957</v>
+        <v>432942</v>
       </c>
       <c r="R74" t="n">
-        <v>6792790</v>
+        <v>6792639</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8038,18 +8031,12 @@
           <t>2026-02-14</t>
         </is>
       </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Måttligt med garnlav inom en radie av 50m</t>
-        </is>
-      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8068,7 +8055,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131153705</v>
+        <v>131153726</v>
       </c>
       <c r="B75" t="n">
         <v>79244</v>
@@ -8103,10 +8090,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>433133</v>
+        <v>432891</v>
       </c>
       <c r="R75" t="n">
-        <v>6792485</v>
+        <v>6792834</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8165,10 +8152,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131153619</v>
+        <v>131153721</v>
       </c>
       <c r="B76" t="n">
-        <v>79834</v>
+        <v>79244</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8176,34 +8163,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>433004</v>
+        <v>432957</v>
       </c>
       <c r="R76" t="n">
-        <v>6792784</v>
+        <v>6792790</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8238,12 +8228,18 @@
           <t>2026-02-14</t>
         </is>
       </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Måttligt med garnlav inom en radie av 50m</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8262,7 +8258,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131153711</v>
+        <v>131153699</v>
       </c>
       <c r="B77" t="n">
         <v>79244</v>
@@ -8297,10 +8293,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>432942</v>
+        <v>432849</v>
       </c>
       <c r="R77" t="n">
-        <v>6792639</v>
+        <v>6792408</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8359,7 +8355,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131153726</v>
+        <v>131153705</v>
       </c>
       <c r="B78" t="n">
         <v>79244</v>
@@ -8394,10 +8390,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>432891</v>
+        <v>433133</v>
       </c>
       <c r="R78" t="n">
-        <v>6792834</v>
+        <v>6792485</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8456,10 +8452,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131153699</v>
+        <v>131153639</v>
       </c>
       <c r="B79" t="n">
-        <v>79244</v>
+        <v>57881</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8467,34 +8463,42 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>432849</v>
+        <v>432988</v>
       </c>
       <c r="R79" t="n">
-        <v>6792408</v>
+        <v>6792798</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8553,37 +8557,43 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131153625</v>
+        <v>131153669</v>
       </c>
       <c r="B80" t="n">
-        <v>91830</v>
+        <v>8451</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
@@ -8591,10 +8601,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>433119</v>
+        <v>432941</v>
       </c>
       <c r="R80" t="n">
-        <v>6792436</v>
+        <v>6792778</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8654,54 +8664,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131153669</v>
+        <v>131153619</v>
       </c>
       <c r="B81" t="n">
-        <v>8451</v>
+        <v>79834</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>432941</v>
+        <v>433004</v>
       </c>
       <c r="R81" t="n">
-        <v>6792778</v>
+        <v>6792784</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8742,7 +8743,6 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -8761,54 +8761,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131153659</v>
+        <v>131153728</v>
       </c>
       <c r="B82" t="n">
-        <v>8451</v>
+        <v>79244</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>433073</v>
+        <v>432945</v>
       </c>
       <c r="R82" t="n">
-        <v>6792412</v>
+        <v>6792842</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8849,7 +8840,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -8868,10 +8858,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131153728</v>
+        <v>131153624</v>
       </c>
       <c r="B83" t="n">
-        <v>79244</v>
+        <v>91830</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8879,34 +8869,37 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>432945</v>
+        <v>433010</v>
       </c>
       <c r="R83" t="n">
-        <v>6792842</v>
+        <v>6792353</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8947,6 +8940,7 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -8965,37 +8959,43 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131153624</v>
+        <v>131153659</v>
       </c>
       <c r="B84" t="n">
-        <v>91830</v>
+        <v>8451</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -9003,10 +9003,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>433010</v>
+        <v>433073</v>
       </c>
       <c r="R84" t="n">
-        <v>6792353</v>
+        <v>6792412</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9066,54 +9066,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131153666</v>
+        <v>131153617</v>
       </c>
       <c r="B85" t="n">
-        <v>8451</v>
+        <v>79834</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>432913</v>
+        <v>432828</v>
       </c>
       <c r="R85" t="n">
-        <v>6792742</v>
+        <v>6792424</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9154,7 +9145,6 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -9173,7 +9163,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131153664</v>
+        <v>131153666</v>
       </c>
       <c r="B86" t="n">
         <v>8451</v>
@@ -9207,7 +9197,7 @@
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N86" t="inlineStr"/>
@@ -9217,10 +9207,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>433001</v>
+        <v>432913</v>
       </c>
       <c r="R86" t="n">
-        <v>6792569</v>
+        <v>6792742</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9280,45 +9270,54 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131153617</v>
+        <v>131153664</v>
       </c>
       <c r="B87" t="n">
-        <v>79834</v>
+        <v>8451</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>432828</v>
+        <v>433001</v>
       </c>
       <c r="R87" t="n">
-        <v>6792424</v>
+        <v>6792569</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9359,6 +9358,7 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9474,10 +9474,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131153652</v>
+        <v>131153678</v>
       </c>
       <c r="B89" t="n">
-        <v>79002</v>
+        <v>79001</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9485,21 +9485,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9509,10 +9509,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>433073</v>
+        <v>433104</v>
       </c>
       <c r="R89" t="n">
-        <v>6792637</v>
+        <v>6792573</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9676,10 +9676,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131153678</v>
+        <v>131153652</v>
       </c>
       <c r="B91" t="n">
-        <v>79001</v>
+        <v>79002</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9687,21 +9687,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9711,10 +9711,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>433104</v>
+        <v>433073</v>
       </c>
       <c r="R91" t="n">
-        <v>6792573</v>
+        <v>6792637</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>

--- a/artfynd/A 1159-2026 artfynd.xlsx
+++ b/artfynd/A 1159-2026 artfynd.xlsx
@@ -1402,10 +1402,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131153689</v>
+        <v>131153632</v>
       </c>
       <c r="B9" t="n">
-        <v>79244</v>
+        <v>57881</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1413,34 +1413,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>432855</v>
+        <v>433068</v>
       </c>
       <c r="R9" t="n">
-        <v>6792784</v>
+        <v>6792622</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,40 +1507,41 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131153632</v>
+        <v>131153656</v>
       </c>
       <c r="B10" t="n">
-        <v>57881</v>
+        <v>8451</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1542,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>433068</v>
+        <v>432815</v>
       </c>
       <c r="R10" t="n">
-        <v>6792622</v>
+        <v>6792564</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1586,6 +1595,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1604,7 +1614,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131153656</v>
+        <v>131153663</v>
       </c>
       <c r="B11" t="n">
         <v>8451</v>
@@ -1648,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>432815</v>
+        <v>433024</v>
       </c>
       <c r="R11" t="n">
-        <v>6792564</v>
+        <v>6792572</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1711,54 +1721,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131153663</v>
+        <v>131153689</v>
       </c>
       <c r="B12" t="n">
-        <v>8451</v>
+        <v>79244</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>433024</v>
+        <v>432855</v>
       </c>
       <c r="R12" t="n">
-        <v>6792572</v>
+        <v>6792784</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1799,7 +1800,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1915,10 +1915,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131153712</v>
+        <v>131153621</v>
       </c>
       <c r="B14" t="n">
-        <v>79244</v>
+        <v>79834</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1926,21 +1926,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1950,10 +1950,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>432967</v>
+        <v>433070</v>
       </c>
       <c r="R14" t="n">
-        <v>6792669</v>
+        <v>6792624</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2109,10 +2109,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131153621</v>
+        <v>131153712</v>
       </c>
       <c r="B16" t="n">
-        <v>79834</v>
+        <v>79244</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2120,21 +2120,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2144,10 +2144,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>433070</v>
+        <v>432967</v>
       </c>
       <c r="R16" t="n">
-        <v>6792624</v>
+        <v>6792669</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2206,41 +2206,40 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131153668</v>
+        <v>131153635</v>
       </c>
       <c r="B17" t="n">
-        <v>8451</v>
+        <v>57881</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2250,10 +2249,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>432974</v>
+        <v>432968</v>
       </c>
       <c r="R17" t="n">
-        <v>6792777</v>
+        <v>6792680</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2294,7 +2293,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2313,37 +2311,43 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131153706</v>
+        <v>131153645</v>
       </c>
       <c r="B18" t="n">
-        <v>79244</v>
+        <v>5480</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>101920</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2351,10 +2355,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>433126</v>
+        <v>432996</v>
       </c>
       <c r="R18" t="n">
-        <v>6792522</v>
+        <v>6792672</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2393,7 +2397,7 @@
         <v>0</v>
       </c>
       <c r="AE18" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
@@ -2414,45 +2418,54 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131153695</v>
+        <v>131153668</v>
       </c>
       <c r="B19" t="n">
-        <v>79244</v>
+        <v>8451</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>432708</v>
+        <v>432974</v>
       </c>
       <c r="R19" t="n">
-        <v>6792430</v>
+        <v>6792777</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2493,6 +2506,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2511,10 +2525,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131153635</v>
+        <v>131153706</v>
       </c>
       <c r="B20" t="n">
-        <v>57881</v>
+        <v>79244</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2522,31 +2536,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2554,10 +2563,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>432968</v>
+        <v>433126</v>
       </c>
       <c r="R20" t="n">
-        <v>6792680</v>
+        <v>6792522</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2598,6 +2607,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2616,54 +2626,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131153645</v>
+        <v>131153695</v>
       </c>
       <c r="B21" t="n">
-        <v>5480</v>
+        <v>79244</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>101920</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>432996</v>
+        <v>432708</v>
       </c>
       <c r="R21" t="n">
-        <v>6792672</v>
+        <v>6792430</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2702,9 +2703,8 @@
         <v>0</v>
       </c>
       <c r="AE21" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF21" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2723,10 +2723,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131153622</v>
+        <v>131153719</v>
       </c>
       <c r="B22" t="n">
-        <v>57884</v>
+        <v>79244</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2734,31 +2734,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2766,10 +2761,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>432996</v>
+        <v>432964</v>
       </c>
       <c r="R22" t="n">
-        <v>6792778</v>
+        <v>6792760</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2810,6 +2805,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2828,7 +2824,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131153719</v>
+        <v>131153729</v>
       </c>
       <c r="B23" t="n">
         <v>79244</v>
@@ -2857,19 +2853,16 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>432964</v>
+        <v>432924</v>
       </c>
       <c r="R23" t="n">
-        <v>6792760</v>
+        <v>6792835</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2910,7 +2903,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2929,10 +2921,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131153729</v>
+        <v>131153622</v>
       </c>
       <c r="B24" t="n">
-        <v>79244</v>
+        <v>57884</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2940,34 +2932,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>432924</v>
+        <v>432996</v>
       </c>
       <c r="R24" t="n">
-        <v>6792835</v>
+        <v>6792778</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3424,10 +3424,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131153630</v>
+        <v>131153716</v>
       </c>
       <c r="B29" t="n">
-        <v>57881</v>
+        <v>79244</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3435,42 +3435,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>433062</v>
+        <v>432960</v>
       </c>
       <c r="R29" t="n">
-        <v>6792357</v>
+        <v>6792712</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3529,10 +3521,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131153641</v>
+        <v>131153690</v>
       </c>
       <c r="B30" t="n">
-        <v>57881</v>
+        <v>79244</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3540,31 +3532,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3572,10 +3559,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>432909</v>
+        <v>432874</v>
       </c>
       <c r="R30" t="n">
-        <v>6792876</v>
+        <v>6792733</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3616,6 +3603,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3634,10 +3622,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131153616</v>
+        <v>131153630</v>
       </c>
       <c r="B31" t="n">
-        <v>79834</v>
+        <v>57881</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3645,34 +3633,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>432773</v>
+        <v>433062</v>
       </c>
       <c r="R31" t="n">
-        <v>6792537</v>
+        <v>6792357</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3731,10 +3727,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131153716</v>
+        <v>131153641</v>
       </c>
       <c r="B32" t="n">
-        <v>79244</v>
+        <v>57881</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3742,34 +3738,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>432960</v>
+        <v>432909</v>
       </c>
       <c r="R32" t="n">
-        <v>6792712</v>
+        <v>6792876</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3828,10 +3832,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131153690</v>
+        <v>131153616</v>
       </c>
       <c r="B33" t="n">
-        <v>79244</v>
+        <v>79834</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3839,37 +3843,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>432874</v>
+        <v>432773</v>
       </c>
       <c r="R33" t="n">
-        <v>6792733</v>
+        <v>6792537</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3910,7 +3911,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4143,7 +4143,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131153703</v>
+        <v>131153698</v>
       </c>
       <c r="B36" t="n">
         <v>79244</v>
@@ -4178,10 +4178,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>433063</v>
+        <v>432819</v>
       </c>
       <c r="R36" t="n">
-        <v>6792351</v>
+        <v>6792432</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4240,7 +4240,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131153702</v>
+        <v>131153714</v>
       </c>
       <c r="B37" t="n">
         <v>79244</v>
@@ -4275,10 +4275,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>433004</v>
+        <v>432946</v>
       </c>
       <c r="R37" t="n">
-        <v>6792374</v>
+        <v>6792696</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4311,6 +4311,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Måttligt med garnlav inom en radie av 50 m</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4337,10 +4342,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131153698</v>
+        <v>131153628</v>
       </c>
       <c r="B38" t="n">
-        <v>79244</v>
+        <v>57881</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4348,34 +4353,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>432819</v>
+        <v>432884</v>
       </c>
       <c r="R38" t="n">
-        <v>6792432</v>
+        <v>6792734</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4434,7 +4447,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131153714</v>
+        <v>131153702</v>
       </c>
       <c r="B39" t="n">
         <v>79244</v>
@@ -4469,10 +4482,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>432946</v>
+        <v>433004</v>
       </c>
       <c r="R39" t="n">
-        <v>6792696</v>
+        <v>6792374</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4505,11 +4518,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-02-14</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Måttligt med garnlav inom en radie av 50 m</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4536,10 +4544,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131153628</v>
+        <v>131153703</v>
       </c>
       <c r="B40" t="n">
-        <v>57881</v>
+        <v>79244</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4547,42 +4555,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>432884</v>
+        <v>433063</v>
       </c>
       <c r="R40" t="n">
-        <v>6792734</v>
+        <v>6792351</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5029,10 +5029,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131153692</v>
+        <v>131153643</v>
       </c>
       <c r="B45" t="n">
-        <v>79244</v>
+        <v>57881</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5040,34 +5040,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>432901</v>
+        <v>432969</v>
       </c>
       <c r="R45" t="n">
-        <v>6792625</v>
+        <v>6792418</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5126,7 +5134,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131153643</v>
+        <v>131153640</v>
       </c>
       <c r="B46" t="n">
         <v>57881</v>
@@ -5169,10 +5177,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>432969</v>
+        <v>432940</v>
       </c>
       <c r="R46" t="n">
-        <v>6792418</v>
+        <v>6792843</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5231,40 +5239,41 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131153640</v>
+        <v>131153660</v>
       </c>
       <c r="B47" t="n">
-        <v>57881</v>
+        <v>8451</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -5274,10 +5283,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>432940</v>
+        <v>433068</v>
       </c>
       <c r="R47" t="n">
-        <v>6792843</v>
+        <v>6792415</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5318,6 +5327,7 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
+      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5336,54 +5346,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131153660</v>
+        <v>131153692</v>
       </c>
       <c r="B48" t="n">
-        <v>8451</v>
+        <v>79244</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>433068</v>
+        <v>432901</v>
       </c>
       <c r="R48" t="n">
-        <v>6792415</v>
+        <v>6792625</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5424,7 +5425,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5550,7 +5550,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131153709</v>
+        <v>131153700</v>
       </c>
       <c r="B50" t="n">
         <v>79244</v>
@@ -5585,10 +5585,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>433034</v>
+        <v>432910</v>
       </c>
       <c r="R50" t="n">
-        <v>6792553</v>
+        <v>6792364</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5744,10 +5744,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131153631</v>
+        <v>131153709</v>
       </c>
       <c r="B52" t="n">
-        <v>57881</v>
+        <v>79244</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5755,42 +5755,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>433074</v>
+        <v>433034</v>
       </c>
       <c r="R52" t="n">
-        <v>6792635</v>
+        <v>6792553</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5849,10 +5841,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131153700</v>
+        <v>131153631</v>
       </c>
       <c r="B53" t="n">
-        <v>79244</v>
+        <v>57881</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5860,34 +5852,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>432910</v>
+        <v>433074</v>
       </c>
       <c r="R53" t="n">
-        <v>6792364</v>
+        <v>6792635</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6148,7 +6148,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131153697</v>
+        <v>131153696</v>
       </c>
       <c r="B56" t="n">
         <v>79244</v>
@@ -6183,10 +6183,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>432785</v>
+        <v>432758</v>
       </c>
       <c r="R56" t="n">
-        <v>6792460</v>
+        <v>6792450</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6245,7 +6245,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131153704</v>
+        <v>131153697</v>
       </c>
       <c r="B57" t="n">
         <v>79244</v>
@@ -6280,10 +6280,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>433115</v>
+        <v>432785</v>
       </c>
       <c r="R57" t="n">
-        <v>6792436</v>
+        <v>6792460</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6342,10 +6342,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131153618</v>
+        <v>131153707</v>
       </c>
       <c r="B58" t="n">
-        <v>79834</v>
+        <v>79244</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6353,21 +6353,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6377,10 +6377,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>433073</v>
+        <v>433128</v>
       </c>
       <c r="R58" t="n">
-        <v>6792637</v>
+        <v>6792592</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6439,10 +6439,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131153649</v>
+        <v>131153704</v>
       </c>
       <c r="B59" t="n">
-        <v>79002</v>
+        <v>79244</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6450,21 +6450,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6474,10 +6474,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>432719</v>
+        <v>433115</v>
       </c>
       <c r="R59" t="n">
-        <v>6792423</v>
+        <v>6792436</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6536,10 +6536,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131153696</v>
+        <v>131153638</v>
       </c>
       <c r="B60" t="n">
-        <v>79244</v>
+        <v>57881</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6547,34 +6547,42 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>432758</v>
+        <v>432927</v>
       </c>
       <c r="R60" t="n">
-        <v>6792450</v>
+        <v>6792752</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6633,10 +6641,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131153707</v>
+        <v>131153618</v>
       </c>
       <c r="B61" t="n">
-        <v>79244</v>
+        <v>79834</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6644,21 +6652,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6668,10 +6676,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>433128</v>
+        <v>433073</v>
       </c>
       <c r="R61" t="n">
-        <v>6792592</v>
+        <v>6792637</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6730,10 +6738,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131153638</v>
+        <v>131153649</v>
       </c>
       <c r="B62" t="n">
-        <v>57881</v>
+        <v>79002</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6741,42 +6749,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>432927</v>
+        <v>432719</v>
       </c>
       <c r="R62" t="n">
-        <v>6792752</v>
+        <v>6792423</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6835,10 +6835,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131153633</v>
+        <v>131153693</v>
       </c>
       <c r="B63" t="n">
-        <v>57881</v>
+        <v>79244</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6846,42 +6846,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>432972</v>
+        <v>432849</v>
       </c>
       <c r="R63" t="n">
-        <v>6792667</v>
+        <v>6792616</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6940,7 +6932,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131153693</v>
+        <v>131153727</v>
       </c>
       <c r="B64" t="n">
         <v>79244</v>
@@ -6969,16 +6961,19 @@
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>432849</v>
+        <v>432935</v>
       </c>
       <c r="R64" t="n">
-        <v>6792616</v>
+        <v>6792834</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7019,6 +7014,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7037,10 +7033,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131153727</v>
+        <v>131153633</v>
       </c>
       <c r="B65" t="n">
-        <v>79244</v>
+        <v>57881</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7048,26 +7044,31 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7075,10 +7076,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>432935</v>
+        <v>432972</v>
       </c>
       <c r="R65" t="n">
-        <v>6792834</v>
+        <v>6792667</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7119,7 +7120,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7245,10 +7245,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131153694</v>
+        <v>131153636</v>
       </c>
       <c r="B67" t="n">
-        <v>79244</v>
+        <v>57881</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7256,34 +7256,42 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>432842</v>
+        <v>432931</v>
       </c>
       <c r="R67" t="n">
-        <v>6792572</v>
+        <v>6792717</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7439,40 +7447,41 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131153636</v>
+        <v>131153655</v>
       </c>
       <c r="B69" t="n">
-        <v>57881</v>
+        <v>8451</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
@@ -7482,10 +7491,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>432931</v>
+        <v>432876</v>
       </c>
       <c r="R69" t="n">
-        <v>6792717</v>
+        <v>6792590</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7526,6 +7535,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7544,10 +7554,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131153634</v>
+        <v>131153694</v>
       </c>
       <c r="B70" t="n">
-        <v>57881</v>
+        <v>79244</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7555,42 +7565,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>432989</v>
+        <v>432842</v>
       </c>
       <c r="R70" t="n">
-        <v>6792671</v>
+        <v>6792572</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7649,41 +7651,40 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131153655</v>
+        <v>131153634</v>
       </c>
       <c r="B71" t="n">
-        <v>8451</v>
+        <v>57881</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N71" t="inlineStr"/>
@@ -7693,10 +7694,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>432876</v>
+        <v>432989</v>
       </c>
       <c r="R71" t="n">
-        <v>6792590</v>
+        <v>6792671</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7737,7 +7738,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7857,10 +7857,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131153625</v>
+        <v>131153726</v>
       </c>
       <c r="B73" t="n">
-        <v>91830</v>
+        <v>79244</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7868,37 +7868,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>433119</v>
+        <v>432891</v>
       </c>
       <c r="R73" t="n">
-        <v>6792436</v>
+        <v>6792834</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7939,7 +7936,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -8055,7 +8051,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131153726</v>
+        <v>131153705</v>
       </c>
       <c r="B75" t="n">
         <v>79244</v>
@@ -8090,10 +8086,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>432891</v>
+        <v>433133</v>
       </c>
       <c r="R75" t="n">
-        <v>6792834</v>
+        <v>6792485</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8152,10 +8148,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131153721</v>
+        <v>131153639</v>
       </c>
       <c r="B76" t="n">
-        <v>79244</v>
+        <v>57881</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8163,26 +8159,31 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
+      <c r="L76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
@@ -8190,10 +8191,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>432957</v>
+        <v>432988</v>
       </c>
       <c r="R76" t="n">
-        <v>6792790</v>
+        <v>6792798</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8228,18 +8229,12 @@
           <t>2026-02-14</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Måttligt med garnlav inom en radie av 50m</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8258,45 +8253,54 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131153699</v>
+        <v>131153669</v>
       </c>
       <c r="B77" t="n">
-        <v>79244</v>
+        <v>8451</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>432849</v>
+        <v>432941</v>
       </c>
       <c r="R77" t="n">
-        <v>6792408</v>
+        <v>6792778</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8337,6 +8341,7 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8355,10 +8360,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131153705</v>
+        <v>131153619</v>
       </c>
       <c r="B78" t="n">
-        <v>79244</v>
+        <v>79834</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8366,21 +8371,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8390,10 +8395,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>433133</v>
+        <v>433004</v>
       </c>
       <c r="R78" t="n">
-        <v>6792485</v>
+        <v>6792784</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8452,10 +8457,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131153639</v>
+        <v>131153721</v>
       </c>
       <c r="B79" t="n">
-        <v>57881</v>
+        <v>79244</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8463,31 +8468,26 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -8495,10 +8495,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>432988</v>
+        <v>432957</v>
       </c>
       <c r="R79" t="n">
-        <v>6792798</v>
+        <v>6792790</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8533,12 +8533,18 @@
           <t>2026-02-14</t>
         </is>
       </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Måttligt med garnlav inom en radie av 50m</t>
+        </is>
+      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8557,54 +8563,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131153669</v>
+        <v>131153699</v>
       </c>
       <c r="B80" t="n">
-        <v>8451</v>
+        <v>79244</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>432941</v>
+        <v>432849</v>
       </c>
       <c r="R80" t="n">
-        <v>6792778</v>
+        <v>6792408</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8645,7 +8642,6 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8664,10 +8660,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131153619</v>
+        <v>131153625</v>
       </c>
       <c r="B81" t="n">
-        <v>79834</v>
+        <v>91830</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8675,34 +8671,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>229821</v>
+        <v>5442</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>433004</v>
+        <v>433119</v>
       </c>
       <c r="R81" t="n">
-        <v>6792784</v>
+        <v>6792436</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8743,6 +8742,7 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -9066,45 +9066,54 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131153617</v>
+        <v>131153666</v>
       </c>
       <c r="B85" t="n">
-        <v>79834</v>
+        <v>8451</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>432828</v>
+        <v>432913</v>
       </c>
       <c r="R85" t="n">
-        <v>6792424</v>
+        <v>6792742</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9145,6 +9154,7 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -9163,7 +9173,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131153666</v>
+        <v>131153664</v>
       </c>
       <c r="B86" t="n">
         <v>8451</v>
@@ -9197,7 +9207,7 @@
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N86" t="inlineStr"/>
@@ -9207,10 +9217,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>432913</v>
+        <v>433001</v>
       </c>
       <c r="R86" t="n">
-        <v>6792742</v>
+        <v>6792569</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9270,54 +9280,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131153664</v>
+        <v>131153617</v>
       </c>
       <c r="B87" t="n">
-        <v>8451</v>
+        <v>79834</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>433001</v>
+        <v>432828</v>
       </c>
       <c r="R87" t="n">
-        <v>6792569</v>
+        <v>6792424</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9358,7 +9359,6 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9474,10 +9474,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131153678</v>
+        <v>131153642</v>
       </c>
       <c r="B89" t="n">
-        <v>79001</v>
+        <v>57881</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9485,34 +9485,42 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>433104</v>
+        <v>432888</v>
       </c>
       <c r="R89" t="n">
-        <v>6792573</v>
+        <v>6792650</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9571,10 +9579,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131153642</v>
+        <v>131153678</v>
       </c>
       <c r="B90" t="n">
-        <v>57881</v>
+        <v>79001</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9582,42 +9590,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>432888</v>
+        <v>433104</v>
       </c>
       <c r="R90" t="n">
-        <v>6792650</v>
+        <v>6792573</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>

--- a/artfynd/A 1159-2026 artfynd.xlsx
+++ b/artfynd/A 1159-2026 artfynd.xlsx
@@ -1104,7 +1104,7 @@
         <v>131153677</v>
       </c>
       <c r="B6" t="n">
-        <v>79001</v>
+        <v>79002</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>131153725</v>
       </c>
       <c r="B7" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1507,54 +1507,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131153656</v>
+        <v>131153689</v>
       </c>
       <c r="B10" t="n">
-        <v>8451</v>
+        <v>79245</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>432815</v>
+        <v>432855</v>
       </c>
       <c r="R10" t="n">
-        <v>6792564</v>
+        <v>6792784</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1595,7 +1586,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1614,7 +1604,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131153663</v>
+        <v>131153656</v>
       </c>
       <c r="B11" t="n">
         <v>8451</v>
@@ -1658,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>433024</v>
+        <v>432815</v>
       </c>
       <c r="R11" t="n">
-        <v>6792572</v>
+        <v>6792564</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1721,45 +1711,54 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131153689</v>
+        <v>131153663</v>
       </c>
       <c r="B12" t="n">
-        <v>79244</v>
+        <v>8451</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>432855</v>
+        <v>433024</v>
       </c>
       <c r="R12" t="n">
-        <v>6792784</v>
+        <v>6792572</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1800,6 +1799,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1821,7 +1821,7 @@
         <v>131153676</v>
       </c>
       <c r="B13" t="n">
-        <v>79001</v>
+        <v>79002</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1915,10 +1915,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131153621</v>
+        <v>131153712</v>
       </c>
       <c r="B14" t="n">
-        <v>79834</v>
+        <v>79245</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1926,21 +1926,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1950,10 +1950,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>433070</v>
+        <v>432967</v>
       </c>
       <c r="R14" t="n">
-        <v>6792624</v>
+        <v>6792669</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2015,7 +2015,7 @@
         <v>131153720</v>
       </c>
       <c r="B15" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2109,10 +2109,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131153712</v>
+        <v>131153621</v>
       </c>
       <c r="B16" t="n">
-        <v>79244</v>
+        <v>79835</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2120,21 +2120,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2144,10 +2144,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>432967</v>
+        <v>433070</v>
       </c>
       <c r="R16" t="n">
-        <v>6792669</v>
+        <v>6792624</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2206,10 +2206,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131153635</v>
+        <v>131153706</v>
       </c>
       <c r="B17" t="n">
-        <v>57881</v>
+        <v>79245</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2217,31 +2217,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2249,10 +2244,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>432968</v>
+        <v>433126</v>
       </c>
       <c r="R17" t="n">
-        <v>6792680</v>
+        <v>6792522</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2293,6 +2288,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2311,54 +2307,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131153645</v>
+        <v>131153695</v>
       </c>
       <c r="B18" t="n">
-        <v>5480</v>
+        <v>79245</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>101920</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>432996</v>
+        <v>432708</v>
       </c>
       <c r="R18" t="n">
-        <v>6792672</v>
+        <v>6792430</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2397,9 +2384,8 @@
         <v>0</v>
       </c>
       <c r="AE18" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF18" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2418,32 +2404,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131153668</v>
+        <v>131153645</v>
       </c>
       <c r="B19" t="n">
-        <v>8451</v>
+        <v>5480</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>101920</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2462,10 +2448,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>432974</v>
+        <v>432996</v>
       </c>
       <c r="R19" t="n">
-        <v>6792777</v>
+        <v>6792672</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2504,7 +2490,7 @@
         <v>0</v>
       </c>
       <c r="AE19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
@@ -2525,37 +2511,43 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131153706</v>
+        <v>131153668</v>
       </c>
       <c r="B20" t="n">
-        <v>79244</v>
+        <v>8451</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2563,10 +2555,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>433126</v>
+        <v>432974</v>
       </c>
       <c r="R20" t="n">
-        <v>6792522</v>
+        <v>6792777</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2626,10 +2618,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131153695</v>
+        <v>131153635</v>
       </c>
       <c r="B21" t="n">
-        <v>79244</v>
+        <v>57881</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2637,34 +2629,42 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>432708</v>
+        <v>432968</v>
       </c>
       <c r="R21" t="n">
-        <v>6792430</v>
+        <v>6792680</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2726,7 +2726,7 @@
         <v>131153719</v>
       </c>
       <c r="B22" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>131153729</v>
       </c>
       <c r="B23" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3029,7 +3029,7 @@
         <v>131153718</v>
       </c>
       <c r="B25" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>131153701</v>
       </c>
       <c r="B27" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3330,7 +3330,7 @@
         <v>131153650</v>
       </c>
       <c r="B28" t="n">
-        <v>79002</v>
+        <v>79003</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         <v>131153716</v>
       </c>
       <c r="B29" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>131153690</v>
       </c>
       <c r="B30" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3832,45 +3832,54 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131153616</v>
+        <v>131153658</v>
       </c>
       <c r="B33" t="n">
-        <v>79834</v>
+        <v>8451</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>432773</v>
+        <v>433053</v>
       </c>
       <c r="R33" t="n">
-        <v>6792537</v>
+        <v>6792381</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3911,6 +3920,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3929,7 +3939,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131153658</v>
+        <v>131153665</v>
       </c>
       <c r="B34" t="n">
         <v>8451</v>
@@ -3963,7 +3973,7 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -3973,10 +3983,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>433053</v>
+        <v>432959</v>
       </c>
       <c r="R34" t="n">
-        <v>6792381</v>
+        <v>6792711</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4036,54 +4046,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131153665</v>
+        <v>131153616</v>
       </c>
       <c r="B35" t="n">
-        <v>8451</v>
+        <v>79835</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>432959</v>
+        <v>432773</v>
       </c>
       <c r="R35" t="n">
-        <v>6792711</v>
+        <v>6792537</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4124,7 +4125,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4143,10 +4143,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131153698</v>
+        <v>131153703</v>
       </c>
       <c r="B36" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4178,10 +4178,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>432819</v>
+        <v>433063</v>
       </c>
       <c r="R36" t="n">
-        <v>6792432</v>
+        <v>6792351</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4240,10 +4240,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131153714</v>
+        <v>131153702</v>
       </c>
       <c r="B37" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4275,10 +4275,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>432946</v>
+        <v>433004</v>
       </c>
       <c r="R37" t="n">
-        <v>6792696</v>
+        <v>6792374</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4311,11 +4311,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2026-02-14</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Måttligt med garnlav inom en radie av 50 m</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4342,10 +4337,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131153628</v>
+        <v>131153698</v>
       </c>
       <c r="B38" t="n">
-        <v>57881</v>
+        <v>79245</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4353,42 +4348,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>432884</v>
+        <v>432819</v>
       </c>
       <c r="R38" t="n">
-        <v>6792734</v>
+        <v>6792432</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4447,10 +4434,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131153702</v>
+        <v>131153714</v>
       </c>
       <c r="B39" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4482,10 +4469,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>433004</v>
+        <v>432946</v>
       </c>
       <c r="R39" t="n">
-        <v>6792374</v>
+        <v>6792696</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4518,6 +4505,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Måttligt med garnlav inom en radie av 50 m</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4544,10 +4536,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131153703</v>
+        <v>131153628</v>
       </c>
       <c r="B40" t="n">
-        <v>79244</v>
+        <v>57881</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4555,34 +4547,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>433063</v>
+        <v>432884</v>
       </c>
       <c r="R40" t="n">
-        <v>6792351</v>
+        <v>6792734</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4641,45 +4641,54 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131153708</v>
+        <v>131153660</v>
       </c>
       <c r="B41" t="n">
-        <v>79244</v>
+        <v>8451</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>433106</v>
+        <v>433068</v>
       </c>
       <c r="R41" t="n">
-        <v>6792609</v>
+        <v>6792415</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4720,6 +4729,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4738,10 +4748,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131153710</v>
+        <v>131153708</v>
       </c>
       <c r="B42" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4773,10 +4783,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>433013</v>
+        <v>433106</v>
       </c>
       <c r="R42" t="n">
-        <v>6792587</v>
+        <v>6792609</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4835,10 +4845,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131153691</v>
+        <v>131153710</v>
       </c>
       <c r="B43" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4870,10 +4880,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>432881</v>
+        <v>433013</v>
       </c>
       <c r="R43" t="n">
-        <v>6792694</v>
+        <v>6792587</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4932,10 +4942,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131153722</v>
+        <v>131153691</v>
       </c>
       <c r="B44" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4967,10 +4977,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>432939</v>
+        <v>432881</v>
       </c>
       <c r="R44" t="n">
-        <v>6792795</v>
+        <v>6792694</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5029,10 +5039,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131153643</v>
+        <v>131153722</v>
       </c>
       <c r="B45" t="n">
-        <v>57881</v>
+        <v>79245</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5040,42 +5050,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>432969</v>
+        <v>432939</v>
       </c>
       <c r="R45" t="n">
-        <v>6792418</v>
+        <v>6792795</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5134,10 +5136,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131153640</v>
+        <v>131153692</v>
       </c>
       <c r="B46" t="n">
-        <v>57881</v>
+        <v>79245</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5145,42 +5147,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>432940</v>
+        <v>432901</v>
       </c>
       <c r="R46" t="n">
-        <v>6792843</v>
+        <v>6792625</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5239,41 +5233,40 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131153660</v>
+        <v>131153643</v>
       </c>
       <c r="B47" t="n">
-        <v>8451</v>
+        <v>57881</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N47" t="inlineStr"/>
@@ -5283,10 +5276,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>433068</v>
+        <v>432969</v>
       </c>
       <c r="R47" t="n">
-        <v>6792415</v>
+        <v>6792418</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5327,7 +5320,6 @@
       <c r="AE47" t="b">
         <v>0</v>
       </c>
-      <c r="AF47" t="inlineStr"/>
       <c r="AG47" t="b">
         <v>0</v>
       </c>
@@ -5346,10 +5338,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131153692</v>
+        <v>131153640</v>
       </c>
       <c r="B48" t="n">
-        <v>79244</v>
+        <v>57881</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5357,34 +5349,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>432901</v>
+        <v>432940</v>
       </c>
       <c r="R48" t="n">
-        <v>6792625</v>
+        <v>6792843</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5550,10 +5550,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131153700</v>
+        <v>131153709</v>
       </c>
       <c r="B50" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5585,10 +5585,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>432910</v>
+        <v>433034</v>
       </c>
       <c r="R50" t="n">
-        <v>6792364</v>
+        <v>6792553</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5647,10 +5647,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131153713</v>
+        <v>131153700</v>
       </c>
       <c r="B51" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5682,10 +5682,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>432988</v>
+        <v>432910</v>
       </c>
       <c r="R51" t="n">
-        <v>6792669</v>
+        <v>6792364</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5744,10 +5744,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131153709</v>
+        <v>131153713</v>
       </c>
       <c r="B52" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5779,10 +5779,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>433034</v>
+        <v>432988</v>
       </c>
       <c r="R52" t="n">
-        <v>6792553</v>
+        <v>6792669</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5841,10 +5841,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131153631</v>
+        <v>131153653</v>
       </c>
       <c r="B53" t="n">
-        <v>57881</v>
+        <v>79003</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5852,31 +5852,26 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -5884,10 +5879,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>433074</v>
+        <v>432956</v>
       </c>
       <c r="R53" t="n">
-        <v>6792635</v>
+        <v>6792683</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5928,6 +5923,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5946,10 +5942,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131153653</v>
+        <v>131153651</v>
       </c>
       <c r="B54" t="n">
-        <v>79002</v>
+        <v>79003</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5984,10 +5980,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>432956</v>
+        <v>433104</v>
       </c>
       <c r="R54" t="n">
-        <v>6792683</v>
+        <v>6792573</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6047,10 +6043,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131153651</v>
+        <v>131153631</v>
       </c>
       <c r="B55" t="n">
-        <v>79002</v>
+        <v>57881</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6058,26 +6054,31 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6085,10 +6086,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>433104</v>
+        <v>433074</v>
       </c>
       <c r="R55" t="n">
-        <v>6792573</v>
+        <v>6792635</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6129,7 +6130,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6151,7 +6151,7 @@
         <v>131153696</v>
       </c>
       <c r="B56" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6245,10 +6245,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131153697</v>
+        <v>131153707</v>
       </c>
       <c r="B57" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6280,10 +6280,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>432785</v>
+        <v>433128</v>
       </c>
       <c r="R57" t="n">
-        <v>6792460</v>
+        <v>6792592</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6342,10 +6342,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131153707</v>
+        <v>131153697</v>
       </c>
       <c r="B58" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6377,10 +6377,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>433128</v>
+        <v>432785</v>
       </c>
       <c r="R58" t="n">
-        <v>6792592</v>
+        <v>6792460</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6442,7 +6442,7 @@
         <v>131153704</v>
       </c>
       <c r="B59" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6644,7 +6644,7 @@
         <v>131153618</v>
       </c>
       <c r="B61" t="n">
-        <v>79834</v>
+        <v>79835</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>131153649</v>
       </c>
       <c r="B62" t="n">
-        <v>79002</v>
+        <v>79003</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6838,7 +6838,7 @@
         <v>131153693</v>
       </c>
       <c r="B63" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6935,7 +6935,7 @@
         <v>131153727</v>
       </c>
       <c r="B64" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7245,10 +7245,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131153636</v>
+        <v>131153620</v>
       </c>
       <c r="B67" t="n">
-        <v>57881</v>
+        <v>79835</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7256,31 +7256,26 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7288,10 +7283,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>432931</v>
+        <v>433058</v>
       </c>
       <c r="R67" t="n">
-        <v>6792717</v>
+        <v>6792468</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7332,6 +7327,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7350,45 +7346,54 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131153679</v>
+        <v>131153655</v>
       </c>
       <c r="B68" t="n">
-        <v>79001</v>
+        <v>8451</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>432956</v>
+        <v>432876</v>
       </c>
       <c r="R68" t="n">
-        <v>6792683</v>
+        <v>6792590</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7429,6 +7434,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7447,54 +7453,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131153655</v>
+        <v>131153694</v>
       </c>
       <c r="B69" t="n">
-        <v>8451</v>
+        <v>79245</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>432876</v>
+        <v>432842</v>
       </c>
       <c r="R69" t="n">
-        <v>6792590</v>
+        <v>6792572</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7535,7 +7532,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7554,10 +7550,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131153694</v>
+        <v>131153679</v>
       </c>
       <c r="B70" t="n">
-        <v>79244</v>
+        <v>79002</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7565,21 +7561,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7589,10 +7585,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>432842</v>
+        <v>432956</v>
       </c>
       <c r="R70" t="n">
-        <v>6792572</v>
+        <v>6792683</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7651,7 +7647,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131153634</v>
+        <v>131153636</v>
       </c>
       <c r="B71" t="n">
         <v>57881</v>
@@ -7684,7 +7680,7 @@
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N71" t="inlineStr"/>
@@ -7694,10 +7690,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>432989</v>
+        <v>432931</v>
       </c>
       <c r="R71" t="n">
-        <v>6792671</v>
+        <v>6792717</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7756,10 +7752,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131153620</v>
+        <v>131153634</v>
       </c>
       <c r="B72" t="n">
-        <v>79834</v>
+        <v>57881</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7767,26 +7763,31 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -7794,10 +7795,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>433058</v>
+        <v>432989</v>
       </c>
       <c r="R72" t="n">
-        <v>6792468</v>
+        <v>6792671</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7838,7 +7839,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7857,10 +7857,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131153726</v>
+        <v>131153711</v>
       </c>
       <c r="B73" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7892,10 +7892,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>432891</v>
+        <v>432942</v>
       </c>
       <c r="R73" t="n">
-        <v>6792834</v>
+        <v>6792639</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7954,10 +7954,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131153711</v>
+        <v>131153726</v>
       </c>
       <c r="B74" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7989,10 +7989,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>432942</v>
+        <v>432891</v>
       </c>
       <c r="R74" t="n">
-        <v>6792639</v>
+        <v>6792834</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8051,10 +8051,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131153705</v>
+        <v>131153721</v>
       </c>
       <c r="B75" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8080,16 +8080,19 @@
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>433133</v>
+        <v>432957</v>
       </c>
       <c r="R75" t="n">
-        <v>6792485</v>
+        <v>6792790</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8124,12 +8127,18 @@
           <t>2026-02-14</t>
         </is>
       </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Måttligt med garnlav inom en radie av 50m</t>
+        </is>
+      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8148,10 +8157,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131153639</v>
+        <v>131153699</v>
       </c>
       <c r="B76" t="n">
-        <v>57881</v>
+        <v>79245</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8159,42 +8168,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>432988</v>
+        <v>432849</v>
       </c>
       <c r="R76" t="n">
-        <v>6792798</v>
+        <v>6792408</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8253,54 +8254,45 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131153669</v>
+        <v>131153705</v>
       </c>
       <c r="B77" t="n">
-        <v>8451</v>
+        <v>79245</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="J77" t="inlineStr"/>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>432941</v>
+        <v>433133</v>
       </c>
       <c r="R77" t="n">
-        <v>6792778</v>
+        <v>6792485</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8341,7 +8333,6 @@
       <c r="AE77" t="b">
         <v>0</v>
       </c>
-      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8360,10 +8351,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131153619</v>
+        <v>131153625</v>
       </c>
       <c r="B78" t="n">
-        <v>79834</v>
+        <v>91831</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8371,34 +8362,37 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>229821</v>
+        <v>5442</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>433004</v>
+        <v>433119</v>
       </c>
       <c r="R78" t="n">
-        <v>6792784</v>
+        <v>6792436</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8439,6 +8433,7 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8457,10 +8452,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131153721</v>
+        <v>131153639</v>
       </c>
       <c r="B79" t="n">
-        <v>79244</v>
+        <v>57881</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8468,26 +8463,31 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -8495,10 +8495,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>432957</v>
+        <v>432988</v>
       </c>
       <c r="R79" t="n">
-        <v>6792790</v>
+        <v>6792798</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8533,18 +8533,12 @@
           <t>2026-02-14</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Måttligt med garnlav inom en radie av 50m</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8563,45 +8557,54 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131153699</v>
+        <v>131153669</v>
       </c>
       <c r="B80" t="n">
-        <v>79244</v>
+        <v>8451</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>432849</v>
+        <v>432941</v>
       </c>
       <c r="R80" t="n">
-        <v>6792408</v>
+        <v>6792778</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8642,6 +8645,7 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8660,10 +8664,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131153625</v>
+        <v>131153619</v>
       </c>
       <c r="B81" t="n">
-        <v>91830</v>
+        <v>79835</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8671,37 +8675,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5442</v>
+        <v>229821</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>433119</v>
+        <v>433004</v>
       </c>
       <c r="R81" t="n">
-        <v>6792436</v>
+        <v>6792784</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8742,7 +8743,6 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -8764,7 +8764,7 @@
         <v>131153728</v>
       </c>
       <c r="B82" t="n">
-        <v>79244</v>
+        <v>79245</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8861,7 +8861,7 @@
         <v>131153624</v>
       </c>
       <c r="B83" t="n">
-        <v>91830</v>
+        <v>91831</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9066,54 +9066,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131153666</v>
+        <v>131153617</v>
       </c>
       <c r="B85" t="n">
-        <v>8451</v>
+        <v>79835</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>432913</v>
+        <v>432828</v>
       </c>
       <c r="R85" t="n">
-        <v>6792742</v>
+        <v>6792424</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9154,7 +9145,6 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -9173,7 +9163,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131153664</v>
+        <v>131153666</v>
       </c>
       <c r="B86" t="n">
         <v>8451</v>
@@ -9207,7 +9197,7 @@
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N86" t="inlineStr"/>
@@ -9217,10 +9207,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>433001</v>
+        <v>432913</v>
       </c>
       <c r="R86" t="n">
-        <v>6792569</v>
+        <v>6792742</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9280,45 +9270,54 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131153617</v>
+        <v>131153664</v>
       </c>
       <c r="B87" t="n">
-        <v>79834</v>
+        <v>8451</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>432828</v>
+        <v>433001</v>
       </c>
       <c r="R87" t="n">
-        <v>6792424</v>
+        <v>6792569</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9359,6 +9358,7 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9377,10 +9377,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131153717</v>
+        <v>131153642</v>
       </c>
       <c r="B88" t="n">
-        <v>79244</v>
+        <v>57881</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9388,34 +9388,42 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>432932</v>
+        <v>432888</v>
       </c>
       <c r="R88" t="n">
-        <v>6792709</v>
+        <v>6792650</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9474,10 +9482,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131153642</v>
+        <v>131153717</v>
       </c>
       <c r="B89" t="n">
-        <v>57881</v>
+        <v>79245</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9485,42 +9493,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>432888</v>
+        <v>432932</v>
       </c>
       <c r="R89" t="n">
-        <v>6792650</v>
+        <v>6792709</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9582,7 +9582,7 @@
         <v>131153678</v>
       </c>
       <c r="B90" t="n">
-        <v>79001</v>
+        <v>79002</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
         <v>131153652</v>
       </c>
       <c r="B91" t="n">
-        <v>79002</v>
+        <v>79003</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 1159-2026 artfynd.xlsx
+++ b/artfynd/A 1159-2026 artfynd.xlsx
@@ -1101,45 +1101,54 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131153677</v>
+        <v>131153667</v>
       </c>
       <c r="B6" t="n">
-        <v>79002</v>
+        <v>8451</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>433058</v>
+        <v>432988</v>
       </c>
       <c r="R6" t="n">
-        <v>6792459</v>
+        <v>6792738</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1180,6 +1189,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1198,10 +1208,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131153725</v>
+        <v>131153677</v>
       </c>
       <c r="B7" t="n">
-        <v>79245</v>
+        <v>79002</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1209,21 +1219,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1233,10 +1243,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>432886</v>
+        <v>433058</v>
       </c>
       <c r="R7" t="n">
-        <v>6792852</v>
+        <v>6792459</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1295,54 +1305,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131153667</v>
+        <v>131153725</v>
       </c>
       <c r="B8" t="n">
-        <v>8451</v>
+        <v>79245</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>432988</v>
+        <v>432886</v>
       </c>
       <c r="R8" t="n">
-        <v>6792738</v>
+        <v>6792852</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1383,7 +1384,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1402,10 +1402,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131153632</v>
+        <v>131153689</v>
       </c>
       <c r="B9" t="n">
-        <v>57881</v>
+        <v>79245</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1413,42 +1413,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>433068</v>
+        <v>432855</v>
       </c>
       <c r="R9" t="n">
-        <v>6792622</v>
+        <v>6792784</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1507,45 +1499,54 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131153689</v>
+        <v>131153656</v>
       </c>
       <c r="B10" t="n">
-        <v>79245</v>
+        <v>8451</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>432855</v>
+        <v>432815</v>
       </c>
       <c r="R10" t="n">
-        <v>6792784</v>
+        <v>6792564</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1586,6 +1587,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1604,7 +1606,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131153656</v>
+        <v>131153663</v>
       </c>
       <c r="B11" t="n">
         <v>8451</v>
@@ -1648,10 +1650,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>432815</v>
+        <v>433024</v>
       </c>
       <c r="R11" t="n">
-        <v>6792564</v>
+        <v>6792572</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1711,41 +1713,40 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131153663</v>
+        <v>131153632</v>
       </c>
       <c r="B12" t="n">
-        <v>8451</v>
+        <v>57881</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1755,10 +1756,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>433024</v>
+        <v>433068</v>
       </c>
       <c r="R12" t="n">
-        <v>6792572</v>
+        <v>6792622</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1799,7 +1800,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -2206,10 +2206,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131153706</v>
+        <v>131153635</v>
       </c>
       <c r="B17" t="n">
-        <v>79245</v>
+        <v>57881</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2217,26 +2217,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2244,10 +2249,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>433126</v>
+        <v>432968</v>
       </c>
       <c r="R17" t="n">
-        <v>6792522</v>
+        <v>6792680</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2288,7 +2293,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2307,7 +2311,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131153695</v>
+        <v>131153706</v>
       </c>
       <c r="B18" t="n">
         <v>79245</v>
@@ -2336,16 +2340,19 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>432708</v>
+        <v>433126</v>
       </c>
       <c r="R18" t="n">
-        <v>6792430</v>
+        <v>6792522</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2386,6 +2393,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2404,54 +2412,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131153645</v>
+        <v>131153695</v>
       </c>
       <c r="B19" t="n">
-        <v>5480</v>
+        <v>79245</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>101920</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>432996</v>
+        <v>432708</v>
       </c>
       <c r="R19" t="n">
-        <v>6792672</v>
+        <v>6792430</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2490,9 +2489,8 @@
         <v>0</v>
       </c>
       <c r="AE19" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF19" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2511,32 +2509,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131153668</v>
+        <v>131153645</v>
       </c>
       <c r="B20" t="n">
-        <v>8451</v>
+        <v>5480</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>101920</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2555,10 +2553,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>432974</v>
+        <v>432996</v>
       </c>
       <c r="R20" t="n">
-        <v>6792777</v>
+        <v>6792672</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2597,7 +2595,7 @@
         <v>0</v>
       </c>
       <c r="AE20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
@@ -2618,40 +2616,41 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131153635</v>
+        <v>131153668</v>
       </c>
       <c r="B21" t="n">
-        <v>57881</v>
+        <v>8451</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2661,10 +2660,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>432968</v>
+        <v>432974</v>
       </c>
       <c r="R21" t="n">
-        <v>6792680</v>
+        <v>6792777</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2705,6 +2704,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3424,45 +3424,54 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131153716</v>
+        <v>131153658</v>
       </c>
       <c r="B29" t="n">
-        <v>79245</v>
+        <v>8451</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>432960</v>
+        <v>433053</v>
       </c>
       <c r="R29" t="n">
-        <v>6792712</v>
+        <v>6792381</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3503,6 +3512,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3521,37 +3531,43 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131153690</v>
+        <v>131153665</v>
       </c>
       <c r="B30" t="n">
-        <v>79245</v>
+        <v>8451</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3559,10 +3575,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>432874</v>
+        <v>432959</v>
       </c>
       <c r="R30" t="n">
-        <v>6792733</v>
+        <v>6792711</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3622,10 +3638,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131153630</v>
+        <v>131153616</v>
       </c>
       <c r="B31" t="n">
-        <v>57881</v>
+        <v>79835</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3633,42 +3649,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>433062</v>
+        <v>432773</v>
       </c>
       <c r="R31" t="n">
-        <v>6792357</v>
+        <v>6792537</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3727,10 +3735,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131153641</v>
+        <v>131153716</v>
       </c>
       <c r="B32" t="n">
-        <v>57881</v>
+        <v>79245</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3738,42 +3746,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>432909</v>
+        <v>432960</v>
       </c>
       <c r="R32" t="n">
-        <v>6792876</v>
+        <v>6792712</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3832,43 +3832,37 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131153658</v>
+        <v>131153690</v>
       </c>
       <c r="B33" t="n">
-        <v>8451</v>
+        <v>79245</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3876,10 +3870,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>433053</v>
+        <v>432874</v>
       </c>
       <c r="R33" t="n">
-        <v>6792381</v>
+        <v>6792733</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3939,41 +3933,40 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131153665</v>
+        <v>131153630</v>
       </c>
       <c r="B34" t="n">
-        <v>8451</v>
+        <v>57881</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -3983,10 +3976,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>432959</v>
+        <v>433062</v>
       </c>
       <c r="R34" t="n">
-        <v>6792711</v>
+        <v>6792357</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4027,7 +4020,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4046,10 +4038,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131153616</v>
+        <v>131153641</v>
       </c>
       <c r="B35" t="n">
-        <v>79835</v>
+        <v>57881</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4057,34 +4049,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>432773</v>
+        <v>432909</v>
       </c>
       <c r="R35" t="n">
-        <v>6792537</v>
+        <v>6792876</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -6536,10 +6536,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131153638</v>
+        <v>131153618</v>
       </c>
       <c r="B60" t="n">
-        <v>57881</v>
+        <v>79835</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6547,42 +6547,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>432927</v>
+        <v>433073</v>
       </c>
       <c r="R60" t="n">
-        <v>6792752</v>
+        <v>6792637</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6641,10 +6633,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131153618</v>
+        <v>131153649</v>
       </c>
       <c r="B61" t="n">
-        <v>79835</v>
+        <v>79003</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6652,21 +6644,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6676,10 +6668,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>433073</v>
+        <v>432719</v>
       </c>
       <c r="R61" t="n">
-        <v>6792637</v>
+        <v>6792423</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6738,10 +6730,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131153649</v>
+        <v>131153638</v>
       </c>
       <c r="B62" t="n">
-        <v>79003</v>
+        <v>57881</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6749,34 +6741,42 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>432719</v>
+        <v>432927</v>
       </c>
       <c r="R62" t="n">
-        <v>6792423</v>
+        <v>6792752</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8858,37 +8858,43 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131153624</v>
+        <v>131153659</v>
       </c>
       <c r="B83" t="n">
-        <v>91831</v>
+        <v>8451</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -8896,10 +8902,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>433010</v>
+        <v>433073</v>
       </c>
       <c r="R83" t="n">
-        <v>6792353</v>
+        <v>6792412</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8959,43 +8965,37 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131153659</v>
+        <v>131153624</v>
       </c>
       <c r="B84" t="n">
-        <v>8451</v>
+        <v>91831</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -9003,10 +9003,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>433073</v>
+        <v>433010</v>
       </c>
       <c r="R84" t="n">
-        <v>6792412</v>
+        <v>6792353</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9066,45 +9066,54 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131153617</v>
+        <v>131153666</v>
       </c>
       <c r="B85" t="n">
-        <v>79835</v>
+        <v>8451</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>432828</v>
+        <v>432913</v>
       </c>
       <c r="R85" t="n">
-        <v>6792424</v>
+        <v>6792742</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9145,6 +9154,7 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -9163,7 +9173,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131153666</v>
+        <v>131153664</v>
       </c>
       <c r="B86" t="n">
         <v>8451</v>
@@ -9197,7 +9207,7 @@
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N86" t="inlineStr"/>
@@ -9207,10 +9217,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>432913</v>
+        <v>433001</v>
       </c>
       <c r="R86" t="n">
-        <v>6792742</v>
+        <v>6792569</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9270,54 +9280,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131153664</v>
+        <v>131153617</v>
       </c>
       <c r="B87" t="n">
-        <v>8451</v>
+        <v>79835</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>433001</v>
+        <v>432828</v>
       </c>
       <c r="R87" t="n">
-        <v>6792569</v>
+        <v>6792424</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9358,7 +9359,6 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 1159-2026 artfynd.xlsx
+++ b/artfynd/A 1159-2026 artfynd.xlsx
@@ -7346,41 +7346,40 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131153655</v>
+        <v>131153636</v>
       </c>
       <c r="B68" t="n">
-        <v>8451</v>
+        <v>57881</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N68" t="inlineStr"/>
@@ -7390,10 +7389,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>432876</v>
+        <v>432931</v>
       </c>
       <c r="R68" t="n">
-        <v>6792590</v>
+        <v>6792717</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7434,7 +7433,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7453,10 +7451,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131153694</v>
+        <v>131153634</v>
       </c>
       <c r="B69" t="n">
-        <v>79245</v>
+        <v>57881</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7464,34 +7462,42 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>432842</v>
+        <v>432989</v>
       </c>
       <c r="R69" t="n">
-        <v>6792572</v>
+        <v>6792671</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7550,45 +7556,54 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131153679</v>
+        <v>131153655</v>
       </c>
       <c r="B70" t="n">
-        <v>79002</v>
+        <v>8451</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>432956</v>
+        <v>432876</v>
       </c>
       <c r="R70" t="n">
-        <v>6792683</v>
+        <v>6792590</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7629,6 +7644,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7647,10 +7663,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131153636</v>
+        <v>131153694</v>
       </c>
       <c r="B71" t="n">
-        <v>57881</v>
+        <v>79245</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7658,42 +7674,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>432931</v>
+        <v>432842</v>
       </c>
       <c r="R71" t="n">
-        <v>6792717</v>
+        <v>6792572</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7752,10 +7760,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131153634</v>
+        <v>131153679</v>
       </c>
       <c r="B72" t="n">
-        <v>57881</v>
+        <v>79002</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7763,42 +7771,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>432989</v>
+        <v>432956</v>
       </c>
       <c r="R72" t="n">
-        <v>6792671</v>
+        <v>6792683</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7857,10 +7857,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131153711</v>
+        <v>131153639</v>
       </c>
       <c r="B73" t="n">
-        <v>79245</v>
+        <v>57881</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7868,34 +7868,42 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>432942</v>
+        <v>432988</v>
       </c>
       <c r="R73" t="n">
-        <v>6792639</v>
+        <v>6792798</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7954,45 +7962,54 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131153726</v>
+        <v>131153669</v>
       </c>
       <c r="B74" t="n">
-        <v>79245</v>
+        <v>8451</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>432891</v>
+        <v>432941</v>
       </c>
       <c r="R74" t="n">
-        <v>6792834</v>
+        <v>6792778</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8033,6 +8050,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8051,10 +8069,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131153721</v>
+        <v>131153619</v>
       </c>
       <c r="B75" t="n">
-        <v>79245</v>
+        <v>79835</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8062,37 +8080,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>432957</v>
+        <v>433004</v>
       </c>
       <c r="R75" t="n">
-        <v>6792790</v>
+        <v>6792784</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8127,18 +8142,12 @@
           <t>2026-02-14</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Måttligt med garnlav inom en radie av 50m</t>
-        </is>
-      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8157,7 +8166,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131153699</v>
+        <v>131153711</v>
       </c>
       <c r="B76" t="n">
         <v>79245</v>
@@ -8192,10 +8201,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>432849</v>
+        <v>432942</v>
       </c>
       <c r="R76" t="n">
-        <v>6792408</v>
+        <v>6792639</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8254,7 +8263,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131153705</v>
+        <v>131153726</v>
       </c>
       <c r="B77" t="n">
         <v>79245</v>
@@ -8289,10 +8298,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>433133</v>
+        <v>432891</v>
       </c>
       <c r="R77" t="n">
-        <v>6792485</v>
+        <v>6792834</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8351,10 +8360,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131153625</v>
+        <v>131153721</v>
       </c>
       <c r="B78" t="n">
-        <v>91831</v>
+        <v>79245</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8362,21 +8371,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8389,10 +8398,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>433119</v>
+        <v>432957</v>
       </c>
       <c r="R78" t="n">
-        <v>6792436</v>
+        <v>6792790</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8425,6 +8434,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Måttligt med garnlav inom en radie av 50m</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8452,10 +8466,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131153639</v>
+        <v>131153699</v>
       </c>
       <c r="B79" t="n">
-        <v>57881</v>
+        <v>79245</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8463,42 +8477,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>432988</v>
+        <v>432849</v>
       </c>
       <c r="R79" t="n">
-        <v>6792798</v>
+        <v>6792408</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8557,54 +8563,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131153669</v>
+        <v>131153705</v>
       </c>
       <c r="B80" t="n">
-        <v>8451</v>
+        <v>79245</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>432941</v>
+        <v>433133</v>
       </c>
       <c r="R80" t="n">
-        <v>6792778</v>
+        <v>6792485</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8645,7 +8642,6 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8664,10 +8660,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131153619</v>
+        <v>131153625</v>
       </c>
       <c r="B81" t="n">
-        <v>79835</v>
+        <v>91831</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8675,34 +8671,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>229821</v>
+        <v>5442</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>433004</v>
+        <v>433119</v>
       </c>
       <c r="R81" t="n">
-        <v>6792784</v>
+        <v>6792436</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8743,6 +8742,7 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -9066,54 +9066,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131153666</v>
+        <v>131153617</v>
       </c>
       <c r="B85" t="n">
-        <v>8451</v>
+        <v>79835</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>432913</v>
+        <v>432828</v>
       </c>
       <c r="R85" t="n">
-        <v>6792742</v>
+        <v>6792424</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9154,7 +9145,6 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -9173,7 +9163,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131153664</v>
+        <v>131153666</v>
       </c>
       <c r="B86" t="n">
         <v>8451</v>
@@ -9207,7 +9197,7 @@
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N86" t="inlineStr"/>
@@ -9217,10 +9207,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>433001</v>
+        <v>432913</v>
       </c>
       <c r="R86" t="n">
-        <v>6792569</v>
+        <v>6792742</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9280,45 +9270,54 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131153617</v>
+        <v>131153664</v>
       </c>
       <c r="B87" t="n">
-        <v>79835</v>
+        <v>8451</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>432828</v>
+        <v>433001</v>
       </c>
       <c r="R87" t="n">
-        <v>6792424</v>
+        <v>6792569</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9359,6 +9358,7 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 1159-2026 artfynd.xlsx
+++ b/artfynd/A 1159-2026 artfynd.xlsx
@@ -1499,41 +1499,40 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131153656</v>
+        <v>131153632</v>
       </c>
       <c r="B10" t="n">
-        <v>8451</v>
+        <v>57881</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1543,10 +1542,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>432815</v>
+        <v>433068</v>
       </c>
       <c r="R10" t="n">
-        <v>6792564</v>
+        <v>6792622</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1587,7 +1586,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1606,7 +1604,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131153663</v>
+        <v>131153656</v>
       </c>
       <c r="B11" t="n">
         <v>8451</v>
@@ -1650,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>433024</v>
+        <v>432815</v>
       </c>
       <c r="R11" t="n">
-        <v>6792572</v>
+        <v>6792564</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1713,40 +1711,41 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131153632</v>
+        <v>131153663</v>
       </c>
       <c r="B12" t="n">
-        <v>57881</v>
+        <v>8451</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1756,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>433068</v>
+        <v>433024</v>
       </c>
       <c r="R12" t="n">
-        <v>6792622</v>
+        <v>6792572</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1800,6 +1799,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1818,10 +1818,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131153676</v>
+        <v>131153621</v>
       </c>
       <c r="B13" t="n">
-        <v>79002</v>
+        <v>79835</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1829,21 +1829,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1853,10 +1853,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>432719</v>
+        <v>433070</v>
       </c>
       <c r="R13" t="n">
-        <v>6792423</v>
+        <v>6792624</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1915,10 +1915,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131153712</v>
+        <v>131153676</v>
       </c>
       <c r="B14" t="n">
-        <v>79245</v>
+        <v>79002</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1926,21 +1926,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1950,10 +1950,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>432967</v>
+        <v>432719</v>
       </c>
       <c r="R14" t="n">
-        <v>6792669</v>
+        <v>6792423</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2012,7 +2012,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131153720</v>
+        <v>131153712</v>
       </c>
       <c r="B15" t="n">
         <v>79245</v>
@@ -2047,10 +2047,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>432962</v>
+        <v>432967</v>
       </c>
       <c r="R15" t="n">
-        <v>6792773</v>
+        <v>6792669</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2109,10 +2109,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131153621</v>
+        <v>131153720</v>
       </c>
       <c r="B16" t="n">
-        <v>79835</v>
+        <v>79245</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2120,21 +2120,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2144,10 +2144,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>433070</v>
+        <v>432962</v>
       </c>
       <c r="R16" t="n">
-        <v>6792624</v>
+        <v>6792773</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2206,10 +2206,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131153635</v>
+        <v>131153706</v>
       </c>
       <c r="B17" t="n">
-        <v>57881</v>
+        <v>79245</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2217,31 +2217,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2249,10 +2244,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>432968</v>
+        <v>433126</v>
       </c>
       <c r="R17" t="n">
-        <v>6792680</v>
+        <v>6792522</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2293,6 +2288,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2311,7 +2307,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131153706</v>
+        <v>131153695</v>
       </c>
       <c r="B18" t="n">
         <v>79245</v>
@@ -2340,19 +2336,16 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>433126</v>
+        <v>432708</v>
       </c>
       <c r="R18" t="n">
-        <v>6792522</v>
+        <v>6792430</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2393,7 +2386,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2412,45 +2404,54 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131153695</v>
+        <v>131153645</v>
       </c>
       <c r="B19" t="n">
-        <v>79245</v>
+        <v>5480</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>101920</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>432708</v>
+        <v>432996</v>
       </c>
       <c r="R19" t="n">
-        <v>6792430</v>
+        <v>6792672</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2489,8 +2490,9 @@
         <v>0</v>
       </c>
       <c r="AE19" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2509,41 +2511,40 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131153645</v>
+        <v>131153635</v>
       </c>
       <c r="B20" t="n">
-        <v>5480</v>
+        <v>57881</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>101920</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2553,10 +2554,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>432996</v>
+        <v>432968</v>
       </c>
       <c r="R20" t="n">
-        <v>6792672</v>
+        <v>6792680</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2595,9 +2596,8 @@
         <v>0</v>
       </c>
       <c r="AE20" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF20" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2723,10 +2723,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131153719</v>
+        <v>131153622</v>
       </c>
       <c r="B22" t="n">
-        <v>79245</v>
+        <v>57884</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2734,26 +2734,31 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2761,10 +2766,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>432964</v>
+        <v>432996</v>
       </c>
       <c r="R22" t="n">
-        <v>6792760</v>
+        <v>6792778</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2805,7 +2810,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2824,7 +2828,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131153729</v>
+        <v>131153719</v>
       </c>
       <c r="B23" t="n">
         <v>79245</v>
@@ -2853,16 +2857,19 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>432924</v>
+        <v>432964</v>
       </c>
       <c r="R23" t="n">
-        <v>6792835</v>
+        <v>6792760</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2903,6 +2910,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2921,10 +2929,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131153622</v>
+        <v>131153729</v>
       </c>
       <c r="B24" t="n">
-        <v>57884</v>
+        <v>79245</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2932,42 +2940,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>432996</v>
+        <v>432924</v>
       </c>
       <c r="R24" t="n">
-        <v>6792778</v>
+        <v>6792835</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3026,45 +3026,54 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131153718</v>
+        <v>131153672</v>
       </c>
       <c r="B25" t="n">
-        <v>79245</v>
+        <v>8451</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>432974</v>
+        <v>432901</v>
       </c>
       <c r="R25" t="n">
-        <v>6792746</v>
+        <v>6792829</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3105,6 +3114,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3123,54 +3133,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131153672</v>
+        <v>131153718</v>
       </c>
       <c r="B26" t="n">
-        <v>8451</v>
+        <v>79245</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>432901</v>
+        <v>432974</v>
       </c>
       <c r="R26" t="n">
-        <v>6792829</v>
+        <v>6792746</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3211,7 +3212,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3424,54 +3424,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131153658</v>
+        <v>131153716</v>
       </c>
       <c r="B29" t="n">
-        <v>8451</v>
+        <v>79245</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>433053</v>
+        <v>432960</v>
       </c>
       <c r="R29" t="n">
-        <v>6792381</v>
+        <v>6792712</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3512,7 +3503,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3531,43 +3521,37 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131153665</v>
+        <v>131153690</v>
       </c>
       <c r="B30" t="n">
-        <v>8451</v>
+        <v>79245</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3575,10 +3559,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>432959</v>
+        <v>432874</v>
       </c>
       <c r="R30" t="n">
-        <v>6792711</v>
+        <v>6792733</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3638,10 +3622,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131153616</v>
+        <v>131153630</v>
       </c>
       <c r="B31" t="n">
-        <v>79835</v>
+        <v>57881</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3649,34 +3633,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>432773</v>
+        <v>433062</v>
       </c>
       <c r="R31" t="n">
-        <v>6792537</v>
+        <v>6792357</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3735,10 +3727,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131153716</v>
+        <v>131153641</v>
       </c>
       <c r="B32" t="n">
-        <v>79245</v>
+        <v>57881</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3746,34 +3738,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>432960</v>
+        <v>432909</v>
       </c>
       <c r="R32" t="n">
-        <v>6792712</v>
+        <v>6792876</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3832,37 +3832,43 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131153690</v>
+        <v>131153658</v>
       </c>
       <c r="B33" t="n">
-        <v>79245</v>
+        <v>8451</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3870,10 +3876,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>432874</v>
+        <v>433053</v>
       </c>
       <c r="R33" t="n">
-        <v>6792733</v>
+        <v>6792381</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3933,40 +3939,41 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131153630</v>
+        <v>131153665</v>
       </c>
       <c r="B34" t="n">
-        <v>57881</v>
+        <v>8451</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -3976,10 +3983,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>433062</v>
+        <v>432959</v>
       </c>
       <c r="R34" t="n">
-        <v>6792357</v>
+        <v>6792711</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4020,6 +4027,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4038,10 +4046,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131153641</v>
+        <v>131153616</v>
       </c>
       <c r="B35" t="n">
-        <v>57881</v>
+        <v>79835</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4049,42 +4057,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>432909</v>
+        <v>432773</v>
       </c>
       <c r="R35" t="n">
-        <v>6792876</v>
+        <v>6792537</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -5550,10 +5550,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131153709</v>
+        <v>131153631</v>
       </c>
       <c r="B50" t="n">
-        <v>79245</v>
+        <v>57881</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5561,34 +5561,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>433034</v>
+        <v>433074</v>
       </c>
       <c r="R50" t="n">
-        <v>6792553</v>
+        <v>6792635</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5647,10 +5655,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131153700</v>
+        <v>131153653</v>
       </c>
       <c r="B51" t="n">
-        <v>79245</v>
+        <v>79003</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5658,34 +5666,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>432910</v>
+        <v>432956</v>
       </c>
       <c r="R51" t="n">
-        <v>6792364</v>
+        <v>6792683</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5726,6 +5737,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5744,10 +5756,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131153713</v>
+        <v>131153651</v>
       </c>
       <c r="B52" t="n">
-        <v>79245</v>
+        <v>79003</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5755,34 +5767,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>432988</v>
+        <v>433104</v>
       </c>
       <c r="R52" t="n">
-        <v>6792669</v>
+        <v>6792573</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5823,6 +5838,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5841,10 +5857,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131153653</v>
+        <v>131153709</v>
       </c>
       <c r="B53" t="n">
-        <v>79003</v>
+        <v>79245</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5852,37 +5868,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>432956</v>
+        <v>433034</v>
       </c>
       <c r="R53" t="n">
-        <v>6792683</v>
+        <v>6792553</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5923,7 +5936,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5942,10 +5954,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131153651</v>
+        <v>131153700</v>
       </c>
       <c r="B54" t="n">
-        <v>79003</v>
+        <v>79245</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5953,37 +5965,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>433104</v>
+        <v>432910</v>
       </c>
       <c r="R54" t="n">
-        <v>6792573</v>
+        <v>6792364</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6024,7 +6033,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6043,10 +6051,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131153631</v>
+        <v>131153713</v>
       </c>
       <c r="B55" t="n">
-        <v>57881</v>
+        <v>79245</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6054,42 +6062,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>433074</v>
+        <v>432988</v>
       </c>
       <c r="R55" t="n">
-        <v>6792635</v>
+        <v>6792669</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6536,10 +6536,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131153618</v>
+        <v>131153638</v>
       </c>
       <c r="B60" t="n">
-        <v>79835</v>
+        <v>57881</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6547,34 +6547,42 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>433073</v>
+        <v>432927</v>
       </c>
       <c r="R60" t="n">
-        <v>6792637</v>
+        <v>6792752</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6633,10 +6641,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131153649</v>
+        <v>131153618</v>
       </c>
       <c r="B61" t="n">
-        <v>79003</v>
+        <v>79835</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6644,21 +6652,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6668,10 +6676,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>432719</v>
+        <v>433073</v>
       </c>
       <c r="R61" t="n">
-        <v>6792423</v>
+        <v>6792637</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6730,10 +6738,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131153638</v>
+        <v>131153649</v>
       </c>
       <c r="B62" t="n">
-        <v>57881</v>
+        <v>79003</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6741,42 +6749,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>432927</v>
+        <v>432719</v>
       </c>
       <c r="R62" t="n">
-        <v>6792752</v>
+        <v>6792423</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7033,40 +7033,41 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131153633</v>
+        <v>131153654</v>
       </c>
       <c r="B65" t="n">
-        <v>57881</v>
+        <v>8451</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -7076,10 +7077,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>432972</v>
+        <v>432866</v>
       </c>
       <c r="R65" t="n">
-        <v>6792667</v>
+        <v>6792755</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7120,6 +7121,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7138,41 +7140,40 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131153654</v>
+        <v>131153633</v>
       </c>
       <c r="B66" t="n">
-        <v>8451</v>
+        <v>57881</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -7182,10 +7183,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>432866</v>
+        <v>432972</v>
       </c>
       <c r="R66" t="n">
-        <v>6792755</v>
+        <v>6792667</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7226,7 +7227,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7245,10 +7245,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131153620</v>
+        <v>131153694</v>
       </c>
       <c r="B67" t="n">
-        <v>79835</v>
+        <v>79245</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7256,37 +7256,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>433058</v>
+        <v>432842</v>
       </c>
       <c r="R67" t="n">
-        <v>6792468</v>
+        <v>6792572</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7327,7 +7324,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7346,10 +7342,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131153636</v>
+        <v>131153679</v>
       </c>
       <c r="B68" t="n">
-        <v>57881</v>
+        <v>79002</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7357,42 +7353,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>432931</v>
+        <v>432956</v>
       </c>
       <c r="R68" t="n">
-        <v>6792717</v>
+        <v>6792683</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7451,7 +7439,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131153634</v>
+        <v>131153636</v>
       </c>
       <c r="B69" t="n">
         <v>57881</v>
@@ -7484,7 +7472,7 @@
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
@@ -7494,10 +7482,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>432989</v>
+        <v>432931</v>
       </c>
       <c r="R69" t="n">
-        <v>6792671</v>
+        <v>6792717</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7556,41 +7544,40 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131153655</v>
+        <v>131153634</v>
       </c>
       <c r="B70" t="n">
-        <v>8451</v>
+        <v>57881</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N70" t="inlineStr"/>
@@ -7600,10 +7587,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>432876</v>
+        <v>432989</v>
       </c>
       <c r="R70" t="n">
-        <v>6792590</v>
+        <v>6792671</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7644,7 +7631,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7663,45 +7649,54 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131153694</v>
+        <v>131153655</v>
       </c>
       <c r="B71" t="n">
-        <v>79245</v>
+        <v>8451</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>432842</v>
+        <v>432876</v>
       </c>
       <c r="R71" t="n">
-        <v>6792572</v>
+        <v>6792590</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7742,6 +7737,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7760,10 +7756,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131153679</v>
+        <v>131153620</v>
       </c>
       <c r="B72" t="n">
-        <v>79002</v>
+        <v>79835</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7771,34 +7767,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>432956</v>
+        <v>433058</v>
       </c>
       <c r="R72" t="n">
-        <v>6792683</v>
+        <v>6792468</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7839,6 +7838,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7857,10 +7857,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131153639</v>
+        <v>131153711</v>
       </c>
       <c r="B73" t="n">
-        <v>57881</v>
+        <v>79245</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7868,42 +7868,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>432988</v>
+        <v>432942</v>
       </c>
       <c r="R73" t="n">
-        <v>6792798</v>
+        <v>6792639</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7962,54 +7954,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131153669</v>
+        <v>131153726</v>
       </c>
       <c r="B74" t="n">
-        <v>8451</v>
+        <v>79245</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>432941</v>
+        <v>432891</v>
       </c>
       <c r="R74" t="n">
-        <v>6792778</v>
+        <v>6792834</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8050,7 +8033,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8069,10 +8051,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131153619</v>
+        <v>131153721</v>
       </c>
       <c r="B75" t="n">
-        <v>79835</v>
+        <v>79245</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8080,34 +8062,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>433004</v>
+        <v>432957</v>
       </c>
       <c r="R75" t="n">
-        <v>6792784</v>
+        <v>6792790</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8142,12 +8127,18 @@
           <t>2026-02-14</t>
         </is>
       </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Måttligt med garnlav inom en radie av 50m</t>
+        </is>
+      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8166,7 +8157,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131153711</v>
+        <v>131153699</v>
       </c>
       <c r="B76" t="n">
         <v>79245</v>
@@ -8201,10 +8192,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>432942</v>
+        <v>432849</v>
       </c>
       <c r="R76" t="n">
-        <v>6792639</v>
+        <v>6792408</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8263,7 +8254,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131153726</v>
+        <v>131153705</v>
       </c>
       <c r="B77" t="n">
         <v>79245</v>
@@ -8298,10 +8289,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>432891</v>
+        <v>433133</v>
       </c>
       <c r="R77" t="n">
-        <v>6792834</v>
+        <v>6792485</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8360,10 +8351,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131153721</v>
+        <v>131153639</v>
       </c>
       <c r="B78" t="n">
-        <v>79245</v>
+        <v>57881</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8371,26 +8362,31 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
+      <c r="L78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -8398,10 +8394,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>432957</v>
+        <v>432988</v>
       </c>
       <c r="R78" t="n">
-        <v>6792790</v>
+        <v>6792798</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8436,18 +8432,12 @@
           <t>2026-02-14</t>
         </is>
       </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Måttligt med garnlav inom en radie av 50m</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8466,10 +8456,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131153699</v>
+        <v>131153619</v>
       </c>
       <c r="B79" t="n">
-        <v>79245</v>
+        <v>79835</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8477,21 +8467,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8501,10 +8491,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>432849</v>
+        <v>433004</v>
       </c>
       <c r="R79" t="n">
-        <v>6792408</v>
+        <v>6792784</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8563,10 +8553,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131153705</v>
+        <v>131153625</v>
       </c>
       <c r="B80" t="n">
-        <v>79245</v>
+        <v>91834</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8574,34 +8564,37 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>433133</v>
+        <v>433119</v>
       </c>
       <c r="R80" t="n">
-        <v>6792485</v>
+        <v>6792436</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8642,6 +8635,7 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8660,37 +8654,43 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131153625</v>
+        <v>131153669</v>
       </c>
       <c r="B81" t="n">
-        <v>91831</v>
+        <v>8451</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -8698,10 +8698,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>433119</v>
+        <v>432941</v>
       </c>
       <c r="R81" t="n">
-        <v>6792436</v>
+        <v>6792778</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8761,10 +8761,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131153728</v>
+        <v>131153624</v>
       </c>
       <c r="B82" t="n">
-        <v>79245</v>
+        <v>91834</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8772,34 +8772,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>432945</v>
+        <v>433010</v>
       </c>
       <c r="R82" t="n">
-        <v>6792842</v>
+        <v>6792353</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8840,6 +8843,7 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -8858,54 +8862,45 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131153659</v>
+        <v>131153728</v>
       </c>
       <c r="B83" t="n">
-        <v>8451</v>
+        <v>79245</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>433073</v>
+        <v>432945</v>
       </c>
       <c r="R83" t="n">
-        <v>6792412</v>
+        <v>6792842</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8946,7 +8941,6 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -8965,37 +8959,43 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131153624</v>
+        <v>131153659</v>
       </c>
       <c r="B84" t="n">
-        <v>91831</v>
+        <v>8451</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -9003,10 +9003,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>433010</v>
+        <v>433073</v>
       </c>
       <c r="R84" t="n">
-        <v>6792353</v>
+        <v>6792412</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9066,45 +9066,54 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131153617</v>
+        <v>131153666</v>
       </c>
       <c r="B85" t="n">
-        <v>79835</v>
+        <v>8451</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>432828</v>
+        <v>432913</v>
       </c>
       <c r="R85" t="n">
-        <v>6792424</v>
+        <v>6792742</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9145,6 +9154,7 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -9163,7 +9173,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131153666</v>
+        <v>131153664</v>
       </c>
       <c r="B86" t="n">
         <v>8451</v>
@@ -9197,7 +9207,7 @@
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N86" t="inlineStr"/>
@@ -9207,10 +9217,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>432913</v>
+        <v>433001</v>
       </c>
       <c r="R86" t="n">
-        <v>6792742</v>
+        <v>6792569</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9270,54 +9280,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131153664</v>
+        <v>131153617</v>
       </c>
       <c r="B87" t="n">
-        <v>8451</v>
+        <v>79835</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>433001</v>
+        <v>432828</v>
       </c>
       <c r="R87" t="n">
-        <v>6792569</v>
+        <v>6792424</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9358,7 +9359,6 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9377,10 +9377,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131153642</v>
+        <v>131153717</v>
       </c>
       <c r="B88" t="n">
-        <v>57881</v>
+        <v>79245</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9388,42 +9388,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>432888</v>
+        <v>432932</v>
       </c>
       <c r="R88" t="n">
-        <v>6792650</v>
+        <v>6792709</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9482,10 +9474,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131153717</v>
+        <v>131153678</v>
       </c>
       <c r="B89" t="n">
-        <v>79245</v>
+        <v>79002</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9493,21 +9485,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9517,10 +9509,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>432932</v>
+        <v>433104</v>
       </c>
       <c r="R89" t="n">
-        <v>6792709</v>
+        <v>6792573</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9579,10 +9571,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131153678</v>
+        <v>131153642</v>
       </c>
       <c r="B90" t="n">
-        <v>79002</v>
+        <v>57881</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9590,34 +9582,42 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>433104</v>
+        <v>432888</v>
       </c>
       <c r="R90" t="n">
-        <v>6792573</v>
+        <v>6792650</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>

--- a/artfynd/A 1159-2026 artfynd.xlsx
+++ b/artfynd/A 1159-2026 artfynd.xlsx
@@ -1101,54 +1101,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131153667</v>
+        <v>131153725</v>
       </c>
       <c r="B6" t="n">
-        <v>8451</v>
+        <v>79246</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>432988</v>
+        <v>432886</v>
       </c>
       <c r="R6" t="n">
-        <v>6792738</v>
+        <v>6792852</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,7 +1180,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1211,7 +1201,7 @@
         <v>131153677</v>
       </c>
       <c r="B7" t="n">
-        <v>79002</v>
+        <v>79003</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1305,45 +1295,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131153725</v>
+        <v>131153667</v>
       </c>
       <c r="B8" t="n">
-        <v>79245</v>
+        <v>8451</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>432886</v>
+        <v>432988</v>
       </c>
       <c r="R8" t="n">
-        <v>6792852</v>
+        <v>6792738</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1384,6 +1383,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1402,10 +1402,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131153689</v>
+        <v>131153632</v>
       </c>
       <c r="B9" t="n">
-        <v>79245</v>
+        <v>57881</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1413,34 +1413,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>432855</v>
+        <v>433068</v>
       </c>
       <c r="R9" t="n">
-        <v>6792784</v>
+        <v>6792622</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,10 +1507,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131153632</v>
+        <v>131153689</v>
       </c>
       <c r="B10" t="n">
-        <v>57881</v>
+        <v>79246</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1510,42 +1518,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>433068</v>
+        <v>432855</v>
       </c>
       <c r="R10" t="n">
-        <v>6792622</v>
+        <v>6792784</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1821,7 +1821,7 @@
         <v>131153621</v>
       </c>
       <c r="B13" t="n">
-        <v>79835</v>
+        <v>79836</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1915,10 +1915,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131153676</v>
+        <v>131153712</v>
       </c>
       <c r="B14" t="n">
-        <v>79002</v>
+        <v>79246</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1926,21 +1926,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1950,10 +1950,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>432719</v>
+        <v>432967</v>
       </c>
       <c r="R14" t="n">
-        <v>6792423</v>
+        <v>6792669</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2012,10 +2012,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131153712</v>
+        <v>131153720</v>
       </c>
       <c r="B15" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2047,10 +2047,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>432967</v>
+        <v>432962</v>
       </c>
       <c r="R15" t="n">
-        <v>6792669</v>
+        <v>6792773</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2109,10 +2109,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131153720</v>
+        <v>131153676</v>
       </c>
       <c r="B16" t="n">
-        <v>79245</v>
+        <v>79003</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2120,21 +2120,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2144,10 +2144,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>432962</v>
+        <v>432719</v>
       </c>
       <c r="R16" t="n">
-        <v>6792773</v>
+        <v>6792423</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2206,37 +2206,43 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131153706</v>
+        <v>131153668</v>
       </c>
       <c r="B17" t="n">
-        <v>79245</v>
+        <v>8451</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2244,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>433126</v>
+        <v>432974</v>
       </c>
       <c r="R17" t="n">
-        <v>6792522</v>
+        <v>6792777</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2310,7 +2316,7 @@
         <v>131153695</v>
       </c>
       <c r="B18" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2404,43 +2410,37 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131153645</v>
+        <v>131153706</v>
       </c>
       <c r="B19" t="n">
-        <v>5480</v>
+        <v>79246</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>101920</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2448,10 +2448,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>432996</v>
+        <v>433126</v>
       </c>
       <c r="R19" t="n">
-        <v>6792672</v>
+        <v>6792522</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2490,7 +2490,7 @@
         <v>0</v>
       </c>
       <c r="AE19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
@@ -2616,32 +2616,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131153668</v>
+        <v>131153645</v>
       </c>
       <c r="B21" t="n">
-        <v>8451</v>
+        <v>5480</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>101920</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2660,10 +2660,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>432974</v>
+        <v>432996</v>
       </c>
       <c r="R21" t="n">
-        <v>6792777</v>
+        <v>6792672</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2702,7 +2702,7 @@
         <v>0</v>
       </c>
       <c r="AE21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
@@ -2831,7 +2831,7 @@
         <v>131153719</v>
       </c>
       <c r="B23" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2932,7 +2932,7 @@
         <v>131153729</v>
       </c>
       <c r="B24" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3026,54 +3026,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131153672</v>
+        <v>131153718</v>
       </c>
       <c r="B25" t="n">
-        <v>8451</v>
+        <v>79246</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>432901</v>
+        <v>432974</v>
       </c>
       <c r="R25" t="n">
-        <v>6792829</v>
+        <v>6792746</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3114,7 +3105,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3133,45 +3123,54 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131153718</v>
+        <v>131153672</v>
       </c>
       <c r="B26" t="n">
-        <v>79245</v>
+        <v>8451</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>432974</v>
+        <v>432901</v>
       </c>
       <c r="R26" t="n">
-        <v>6792746</v>
+        <v>6792829</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3212,6 +3211,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3230,10 +3230,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131153701</v>
+        <v>131153650</v>
       </c>
       <c r="B27" t="n">
-        <v>79245</v>
+        <v>79004</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3241,21 +3241,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>432958</v>
+        <v>433062</v>
       </c>
       <c r="R27" t="n">
-        <v>6792418</v>
+        <v>6792357</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3327,10 +3327,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131153650</v>
+        <v>131153701</v>
       </c>
       <c r="B28" t="n">
-        <v>79003</v>
+        <v>79246</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3338,21 +3338,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3362,10 +3362,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>433062</v>
+        <v>432958</v>
       </c>
       <c r="R28" t="n">
-        <v>6792357</v>
+        <v>6792418</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3424,10 +3424,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131153716</v>
+        <v>131153630</v>
       </c>
       <c r="B29" t="n">
-        <v>79245</v>
+        <v>57881</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3435,34 +3435,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>432960</v>
+        <v>433062</v>
       </c>
       <c r="R29" t="n">
-        <v>6792712</v>
+        <v>6792357</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3521,10 +3529,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131153690</v>
+        <v>131153641</v>
       </c>
       <c r="B30" t="n">
-        <v>79245</v>
+        <v>57881</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3532,26 +3540,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3559,10 +3572,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>432874</v>
+        <v>432909</v>
       </c>
       <c r="R30" t="n">
-        <v>6792733</v>
+        <v>6792876</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3603,7 +3616,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3622,10 +3634,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131153630</v>
+        <v>131153690</v>
       </c>
       <c r="B31" t="n">
-        <v>57881</v>
+        <v>79246</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3633,31 +3645,26 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3665,10 +3672,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>433062</v>
+        <v>432874</v>
       </c>
       <c r="R31" t="n">
-        <v>6792357</v>
+        <v>6792733</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3709,6 +3716,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3727,10 +3735,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131153641</v>
+        <v>131153716</v>
       </c>
       <c r="B32" t="n">
-        <v>57881</v>
+        <v>79246</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3738,42 +3746,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>432909</v>
+        <v>432960</v>
       </c>
       <c r="R32" t="n">
-        <v>6792876</v>
+        <v>6792712</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3832,54 +3832,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131153658</v>
+        <v>131153616</v>
       </c>
       <c r="B33" t="n">
-        <v>8451</v>
+        <v>79836</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>433053</v>
+        <v>432773</v>
       </c>
       <c r="R33" t="n">
-        <v>6792381</v>
+        <v>6792537</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3920,7 +3911,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3939,7 +3929,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131153665</v>
+        <v>131153658</v>
       </c>
       <c r="B34" t="n">
         <v>8451</v>
@@ -3973,7 +3963,7 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -3983,10 +3973,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>432959</v>
+        <v>433053</v>
       </c>
       <c r="R34" t="n">
-        <v>6792711</v>
+        <v>6792381</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4046,45 +4036,54 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131153616</v>
+        <v>131153665</v>
       </c>
       <c r="B35" t="n">
-        <v>79835</v>
+        <v>8451</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>432773</v>
+        <v>432959</v>
       </c>
       <c r="R35" t="n">
-        <v>6792537</v>
+        <v>6792711</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4125,6 +4124,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4146,7 +4146,7 @@
         <v>131153703</v>
       </c>
       <c r="B36" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4243,7 +4243,7 @@
         <v>131153702</v>
       </c>
       <c r="B37" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         <v>131153698</v>
       </c>
       <c r="B38" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
         <v>131153714</v>
       </c>
       <c r="B39" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4641,54 +4641,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131153660</v>
+        <v>131153710</v>
       </c>
       <c r="B41" t="n">
-        <v>8451</v>
+        <v>79246</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>433068</v>
+        <v>433013</v>
       </c>
       <c r="R41" t="n">
-        <v>6792415</v>
+        <v>6792587</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4729,7 +4720,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4748,10 +4738,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131153708</v>
+        <v>131153722</v>
       </c>
       <c r="B42" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4783,10 +4773,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>433106</v>
+        <v>432939</v>
       </c>
       <c r="R42" t="n">
-        <v>6792609</v>
+        <v>6792795</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4845,10 +4835,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131153710</v>
+        <v>131153692</v>
       </c>
       <c r="B43" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4880,10 +4870,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>433013</v>
+        <v>432901</v>
       </c>
       <c r="R43" t="n">
-        <v>6792587</v>
+        <v>6792625</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4942,10 +4932,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131153691</v>
+        <v>131153708</v>
       </c>
       <c r="B44" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4977,10 +4967,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>432881</v>
+        <v>433106</v>
       </c>
       <c r="R44" t="n">
-        <v>6792694</v>
+        <v>6792609</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5039,10 +5029,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131153722</v>
+        <v>131153691</v>
       </c>
       <c r="B45" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5074,10 +5064,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>432939</v>
+        <v>432881</v>
       </c>
       <c r="R45" t="n">
-        <v>6792795</v>
+        <v>6792694</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5136,10 +5126,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131153692</v>
+        <v>131153643</v>
       </c>
       <c r="B46" t="n">
-        <v>79245</v>
+        <v>57881</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5147,34 +5137,42 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>432901</v>
+        <v>432969</v>
       </c>
       <c r="R46" t="n">
-        <v>6792625</v>
+        <v>6792418</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5233,7 +5231,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131153643</v>
+        <v>131153640</v>
       </c>
       <c r="B47" t="n">
         <v>57881</v>
@@ -5276,10 +5274,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>432969</v>
+        <v>432940</v>
       </c>
       <c r="R47" t="n">
-        <v>6792418</v>
+        <v>6792843</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5338,40 +5336,41 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131153640</v>
+        <v>131153660</v>
       </c>
       <c r="B48" t="n">
-        <v>57881</v>
+        <v>8451</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -5381,10 +5380,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>432940</v>
+        <v>433068</v>
       </c>
       <c r="R48" t="n">
-        <v>6792843</v>
+        <v>6792415</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5425,6 +5424,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5658,7 +5658,7 @@
         <v>131153653</v>
       </c>
       <c r="B51" t="n">
-        <v>79003</v>
+        <v>79004</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         <v>131153651</v>
       </c>
       <c r="B52" t="n">
-        <v>79003</v>
+        <v>79004</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         <v>131153709</v>
       </c>
       <c r="B53" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         <v>131153700</v>
       </c>
       <c r="B54" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6054,7 +6054,7 @@
         <v>131153713</v>
       </c>
       <c r="B55" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6148,10 +6148,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131153696</v>
+        <v>131153618</v>
       </c>
       <c r="B56" t="n">
-        <v>79245</v>
+        <v>79836</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6159,21 +6159,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6183,10 +6183,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>432758</v>
+        <v>433073</v>
       </c>
       <c r="R56" t="n">
-        <v>6792450</v>
+        <v>6792637</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6245,10 +6245,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131153707</v>
+        <v>131153649</v>
       </c>
       <c r="B57" t="n">
-        <v>79245</v>
+        <v>79004</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6256,21 +6256,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6280,10 +6280,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>433128</v>
+        <v>432719</v>
       </c>
       <c r="R57" t="n">
-        <v>6792592</v>
+        <v>6792423</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6342,10 +6342,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131153697</v>
+        <v>131153638</v>
       </c>
       <c r="B58" t="n">
-        <v>79245</v>
+        <v>57881</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6353,34 +6353,42 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>432785</v>
+        <v>432927</v>
       </c>
       <c r="R58" t="n">
-        <v>6792460</v>
+        <v>6792752</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6439,10 +6447,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131153704</v>
+        <v>131153696</v>
       </c>
       <c r="B59" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6474,10 +6482,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>433115</v>
+        <v>432758</v>
       </c>
       <c r="R59" t="n">
-        <v>6792436</v>
+        <v>6792450</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6536,10 +6544,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131153638</v>
+        <v>131153697</v>
       </c>
       <c r="B60" t="n">
-        <v>57881</v>
+        <v>79246</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6547,42 +6555,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>432927</v>
+        <v>432785</v>
       </c>
       <c r="R60" t="n">
-        <v>6792752</v>
+        <v>6792460</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6641,10 +6641,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131153618</v>
+        <v>131153704</v>
       </c>
       <c r="B61" t="n">
-        <v>79835</v>
+        <v>79246</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6652,21 +6652,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6676,10 +6676,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>433073</v>
+        <v>433115</v>
       </c>
       <c r="R61" t="n">
-        <v>6792637</v>
+        <v>6792436</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6738,10 +6738,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131153649</v>
+        <v>131153707</v>
       </c>
       <c r="B62" t="n">
-        <v>79003</v>
+        <v>79246</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6749,21 +6749,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6773,10 +6773,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>432719</v>
+        <v>433128</v>
       </c>
       <c r="R62" t="n">
-        <v>6792423</v>
+        <v>6792592</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6835,45 +6835,54 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131153693</v>
+        <v>131153654</v>
       </c>
       <c r="B63" t="n">
-        <v>79245</v>
+        <v>8451</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>432849</v>
+        <v>432866</v>
       </c>
       <c r="R63" t="n">
-        <v>6792616</v>
+        <v>6792755</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6914,6 +6923,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -6932,10 +6942,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131153727</v>
+        <v>131153693</v>
       </c>
       <c r="B64" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6961,19 +6971,16 @@
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>432935</v>
+        <v>432849</v>
       </c>
       <c r="R64" t="n">
-        <v>6792834</v>
+        <v>6792616</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7014,7 +7021,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7033,43 +7039,37 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131153654</v>
+        <v>131153727</v>
       </c>
       <c r="B65" t="n">
-        <v>8451</v>
+        <v>79246</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7077,10 +7077,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>432866</v>
+        <v>432935</v>
       </c>
       <c r="R65" t="n">
-        <v>6792755</v>
+        <v>6792834</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7245,10 +7245,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131153694</v>
+        <v>131153636</v>
       </c>
       <c r="B67" t="n">
-        <v>79245</v>
+        <v>57881</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7256,34 +7256,42 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>432842</v>
+        <v>432931</v>
       </c>
       <c r="R67" t="n">
-        <v>6792572</v>
+        <v>6792717</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7342,10 +7350,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131153679</v>
+        <v>131153634</v>
       </c>
       <c r="B68" t="n">
-        <v>79002</v>
+        <v>57881</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7353,34 +7361,42 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>432956</v>
+        <v>432989</v>
       </c>
       <c r="R68" t="n">
-        <v>6792683</v>
+        <v>6792671</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7439,10 +7455,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131153636</v>
+        <v>131153694</v>
       </c>
       <c r="B69" t="n">
-        <v>57881</v>
+        <v>79246</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7450,42 +7466,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>432931</v>
+        <v>432842</v>
       </c>
       <c r="R69" t="n">
-        <v>6792717</v>
+        <v>6792572</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7544,10 +7552,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131153634</v>
+        <v>131153679</v>
       </c>
       <c r="B70" t="n">
-        <v>57881</v>
+        <v>79003</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7555,42 +7563,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>432989</v>
+        <v>432956</v>
       </c>
       <c r="R70" t="n">
-        <v>6792671</v>
+        <v>6792683</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7759,7 +7759,7 @@
         <v>131153620</v>
       </c>
       <c r="B72" t="n">
-        <v>79835</v>
+        <v>79836</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7860,7 +7860,7 @@
         <v>131153711</v>
       </c>
       <c r="B73" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7957,7 +7957,7 @@
         <v>131153726</v>
       </c>
       <c r="B74" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8054,7 +8054,7 @@
         <v>131153721</v>
       </c>
       <c r="B75" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8160,7 +8160,7 @@
         <v>131153699</v>
       </c>
       <c r="B76" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8257,7 +8257,7 @@
         <v>131153705</v>
       </c>
       <c r="B77" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8351,10 +8351,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131153639</v>
+        <v>131153625</v>
       </c>
       <c r="B78" t="n">
-        <v>57881</v>
+        <v>91835</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8362,31 +8362,26 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
@@ -8394,10 +8389,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>432988</v>
+        <v>433119</v>
       </c>
       <c r="R78" t="n">
-        <v>6792798</v>
+        <v>6792436</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8438,6 +8433,7 @@
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8456,45 +8452,54 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131153619</v>
+        <v>131153669</v>
       </c>
       <c r="B79" t="n">
-        <v>79835</v>
+        <v>8451</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>433004</v>
+        <v>432941</v>
       </c>
       <c r="R79" t="n">
-        <v>6792784</v>
+        <v>6792778</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8535,6 +8540,7 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8553,10 +8559,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131153625</v>
+        <v>131153619</v>
       </c>
       <c r="B80" t="n">
-        <v>91834</v>
+        <v>79836</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8564,37 +8570,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5442</v>
+        <v>229821</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>433119</v>
+        <v>433004</v>
       </c>
       <c r="R80" t="n">
-        <v>6792436</v>
+        <v>6792784</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8635,7 +8638,6 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8654,41 +8656,40 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131153669</v>
+        <v>131153639</v>
       </c>
       <c r="B81" t="n">
-        <v>8451</v>
+        <v>57881</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N81" t="inlineStr"/>
@@ -8698,10 +8699,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>432941</v>
+        <v>432988</v>
       </c>
       <c r="R81" t="n">
-        <v>6792778</v>
+        <v>6792798</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8742,7 +8743,6 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -8761,37 +8761,43 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131153624</v>
+        <v>131153659</v>
       </c>
       <c r="B82" t="n">
-        <v>91834</v>
+        <v>8451</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -8799,10 +8805,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>433010</v>
+        <v>433073</v>
       </c>
       <c r="R82" t="n">
-        <v>6792353</v>
+        <v>6792412</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8865,7 +8871,7 @@
         <v>131153728</v>
       </c>
       <c r="B83" t="n">
-        <v>79245</v>
+        <v>79246</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8959,43 +8965,37 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131153659</v>
+        <v>131153624</v>
       </c>
       <c r="B84" t="n">
-        <v>8451</v>
+        <v>91835</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -9003,10 +9003,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>433073</v>
+        <v>433010</v>
       </c>
       <c r="R84" t="n">
-        <v>6792412</v>
+        <v>6792353</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9066,54 +9066,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131153666</v>
+        <v>131153617</v>
       </c>
       <c r="B85" t="n">
-        <v>8451</v>
+        <v>79836</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>432913</v>
+        <v>432828</v>
       </c>
       <c r="R85" t="n">
-        <v>6792742</v>
+        <v>6792424</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9154,7 +9145,6 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -9173,7 +9163,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131153664</v>
+        <v>131153666</v>
       </c>
       <c r="B86" t="n">
         <v>8451</v>
@@ -9207,7 +9197,7 @@
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N86" t="inlineStr"/>
@@ -9217,10 +9207,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>433001</v>
+        <v>432913</v>
       </c>
       <c r="R86" t="n">
-        <v>6792569</v>
+        <v>6792742</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9280,45 +9270,54 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131153617</v>
+        <v>131153664</v>
       </c>
       <c r="B87" t="n">
-        <v>79835</v>
+        <v>8451</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>432828</v>
+        <v>433001</v>
       </c>
       <c r="R87" t="n">
-        <v>6792424</v>
+        <v>6792569</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9359,6 +9358,7 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9377,10 +9377,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131153717</v>
+        <v>131153678</v>
       </c>
       <c r="B88" t="n">
-        <v>79245</v>
+        <v>79003</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9388,21 +9388,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9412,10 +9412,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>432932</v>
+        <v>433104</v>
       </c>
       <c r="R88" t="n">
-        <v>6792709</v>
+        <v>6792573</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9474,10 +9474,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131153678</v>
+        <v>131153717</v>
       </c>
       <c r="B89" t="n">
-        <v>79002</v>
+        <v>79246</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9485,21 +9485,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9509,10 +9509,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>433104</v>
+        <v>432932</v>
       </c>
       <c r="R89" t="n">
-        <v>6792573</v>
+        <v>6792709</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9679,7 +9679,7 @@
         <v>131153652</v>
       </c>
       <c r="B91" t="n">
-        <v>79003</v>
+        <v>79004</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 1159-2026 artfynd.xlsx
+++ b/artfynd/A 1159-2026 artfynd.xlsx
@@ -1818,10 +1818,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131153621</v>
+        <v>131153720</v>
       </c>
       <c r="B13" t="n">
-        <v>79836</v>
+        <v>79246</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1829,21 +1829,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1853,10 +1853,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>433070</v>
+        <v>432962</v>
       </c>
       <c r="R13" t="n">
-        <v>6792624</v>
+        <v>6792773</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1915,10 +1915,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131153712</v>
+        <v>131153676</v>
       </c>
       <c r="B14" t="n">
-        <v>79246</v>
+        <v>79003</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1926,21 +1926,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1950,10 +1950,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>432967</v>
+        <v>432719</v>
       </c>
       <c r="R14" t="n">
-        <v>6792669</v>
+        <v>6792423</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2012,7 +2012,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131153720</v>
+        <v>131153712</v>
       </c>
       <c r="B15" t="n">
         <v>79246</v>
@@ -2047,10 +2047,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>432962</v>
+        <v>432967</v>
       </c>
       <c r="R15" t="n">
-        <v>6792773</v>
+        <v>6792669</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2109,10 +2109,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131153676</v>
+        <v>131153621</v>
       </c>
       <c r="B16" t="n">
-        <v>79003</v>
+        <v>79836</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2120,21 +2120,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2144,10 +2144,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>432719</v>
+        <v>433070</v>
       </c>
       <c r="R16" t="n">
-        <v>6792423</v>
+        <v>6792624</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -4932,10 +4932,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131153708</v>
+        <v>131153643</v>
       </c>
       <c r="B44" t="n">
-        <v>79246</v>
+        <v>57881</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4943,34 +4943,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>433106</v>
+        <v>432969</v>
       </c>
       <c r="R44" t="n">
-        <v>6792609</v>
+        <v>6792418</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5029,10 +5037,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131153691</v>
+        <v>131153640</v>
       </c>
       <c r="B45" t="n">
-        <v>79246</v>
+        <v>57881</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5040,34 +5048,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>432881</v>
+        <v>432940</v>
       </c>
       <c r="R45" t="n">
-        <v>6792694</v>
+        <v>6792843</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5126,10 +5142,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131153643</v>
+        <v>131153708</v>
       </c>
       <c r="B46" t="n">
-        <v>57881</v>
+        <v>79246</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5137,42 +5153,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>432969</v>
+        <v>433106</v>
       </c>
       <c r="R46" t="n">
-        <v>6792418</v>
+        <v>6792609</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5231,10 +5239,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131153640</v>
+        <v>131153691</v>
       </c>
       <c r="B47" t="n">
-        <v>57881</v>
+        <v>79246</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5242,42 +5250,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>432940</v>
+        <v>432881</v>
       </c>
       <c r="R47" t="n">
-        <v>6792843</v>
+        <v>6792694</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5655,10 +5655,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131153653</v>
+        <v>131153709</v>
       </c>
       <c r="B51" t="n">
-        <v>79004</v>
+        <v>79246</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5666,37 +5666,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>432956</v>
+        <v>433034</v>
       </c>
       <c r="R51" t="n">
-        <v>6792683</v>
+        <v>6792553</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5737,7 +5734,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5756,10 +5752,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131153651</v>
+        <v>131153700</v>
       </c>
       <c r="B52" t="n">
-        <v>79004</v>
+        <v>79246</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5767,37 +5763,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>433104</v>
+        <v>432910</v>
       </c>
       <c r="R52" t="n">
-        <v>6792573</v>
+        <v>6792364</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5838,7 +5831,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5857,7 +5849,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131153709</v>
+        <v>131153713</v>
       </c>
       <c r="B53" t="n">
         <v>79246</v>
@@ -5892,10 +5884,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>433034</v>
+        <v>432988</v>
       </c>
       <c r="R53" t="n">
-        <v>6792553</v>
+        <v>6792669</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5954,10 +5946,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131153700</v>
+        <v>131153653</v>
       </c>
       <c r="B54" t="n">
-        <v>79246</v>
+        <v>79004</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5965,34 +5957,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>432910</v>
+        <v>432956</v>
       </c>
       <c r="R54" t="n">
-        <v>6792364</v>
+        <v>6792683</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6033,6 +6028,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6051,10 +6047,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131153713</v>
+        <v>131153651</v>
       </c>
       <c r="B55" t="n">
-        <v>79246</v>
+        <v>79004</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6062,34 +6058,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>432988</v>
+        <v>433104</v>
       </c>
       <c r="R55" t="n">
-        <v>6792669</v>
+        <v>6792573</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6130,6 +6129,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6835,54 +6835,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131153654</v>
+        <v>131153693</v>
       </c>
       <c r="B63" t="n">
-        <v>8451</v>
+        <v>79246</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>432866</v>
+        <v>432849</v>
       </c>
       <c r="R63" t="n">
-        <v>6792755</v>
+        <v>6792616</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6923,7 +6914,6 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -6942,7 +6932,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131153693</v>
+        <v>131153727</v>
       </c>
       <c r="B64" t="n">
         <v>79246</v>
@@ -6971,16 +6961,19 @@
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>432849</v>
+        <v>432935</v>
       </c>
       <c r="R64" t="n">
-        <v>6792616</v>
+        <v>6792834</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7021,6 +7014,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7039,10 +7033,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131153727</v>
+        <v>131153633</v>
       </c>
       <c r="B65" t="n">
-        <v>79246</v>
+        <v>57881</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7050,26 +7044,31 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7077,10 +7076,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>432935</v>
+        <v>432972</v>
       </c>
       <c r="R65" t="n">
-        <v>6792834</v>
+        <v>6792667</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7121,7 +7120,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7140,40 +7138,41 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131153633</v>
+        <v>131153654</v>
       </c>
       <c r="B66" t="n">
-        <v>57881</v>
+        <v>8451</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -7183,10 +7182,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>432972</v>
+        <v>432866</v>
       </c>
       <c r="R66" t="n">
-        <v>6792667</v>
+        <v>6792755</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7227,6 +7226,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7245,10 +7245,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131153636</v>
+        <v>131153694</v>
       </c>
       <c r="B67" t="n">
-        <v>57881</v>
+        <v>79246</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7256,42 +7256,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>432931</v>
+        <v>432842</v>
       </c>
       <c r="R67" t="n">
-        <v>6792717</v>
+        <v>6792572</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7350,10 +7342,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131153634</v>
+        <v>131153679</v>
       </c>
       <c r="B68" t="n">
-        <v>57881</v>
+        <v>79003</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7361,42 +7353,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>432989</v>
+        <v>432956</v>
       </c>
       <c r="R68" t="n">
-        <v>6792671</v>
+        <v>6792683</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7455,45 +7439,54 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131153694</v>
+        <v>131153655</v>
       </c>
       <c r="B69" t="n">
-        <v>79246</v>
+        <v>8451</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>432842</v>
+        <v>432876</v>
       </c>
       <c r="R69" t="n">
-        <v>6792572</v>
+        <v>6792590</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7534,6 +7527,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7552,10 +7546,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131153679</v>
+        <v>131153620</v>
       </c>
       <c r="B70" t="n">
-        <v>79003</v>
+        <v>79836</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7563,34 +7557,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>432956</v>
+        <v>433058</v>
       </c>
       <c r="R70" t="n">
-        <v>6792683</v>
+        <v>6792468</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7631,6 +7628,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7649,41 +7647,40 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131153655</v>
+        <v>131153636</v>
       </c>
       <c r="B71" t="n">
-        <v>8451</v>
+        <v>57881</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N71" t="inlineStr"/>
@@ -7693,10 +7690,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>432876</v>
+        <v>432931</v>
       </c>
       <c r="R71" t="n">
-        <v>6792590</v>
+        <v>6792717</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7737,7 +7734,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7756,10 +7752,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131153620</v>
+        <v>131153634</v>
       </c>
       <c r="B72" t="n">
-        <v>79836</v>
+        <v>57881</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7767,26 +7763,31 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -7794,10 +7795,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>433058</v>
+        <v>432989</v>
       </c>
       <c r="R72" t="n">
-        <v>6792468</v>
+        <v>6792671</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7838,7 +7839,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -8452,41 +8452,40 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131153669</v>
+        <v>131153639</v>
       </c>
       <c r="B79" t="n">
-        <v>8451</v>
+        <v>57881</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N79" t="inlineStr"/>
@@ -8496,10 +8495,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>432941</v>
+        <v>432988</v>
       </c>
       <c r="R79" t="n">
-        <v>6792778</v>
+        <v>6792798</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8540,7 +8539,6 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8559,45 +8557,54 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131153619</v>
+        <v>131153669</v>
       </c>
       <c r="B80" t="n">
-        <v>79836</v>
+        <v>8451</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>433004</v>
+        <v>432941</v>
       </c>
       <c r="R80" t="n">
-        <v>6792784</v>
+        <v>6792778</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8638,6 +8645,7 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8656,10 +8664,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131153639</v>
+        <v>131153619</v>
       </c>
       <c r="B81" t="n">
-        <v>57881</v>
+        <v>79836</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8667,42 +8675,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>432988</v>
+        <v>433004</v>
       </c>
       <c r="R81" t="n">
-        <v>6792798</v>
+        <v>6792784</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9377,10 +9377,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131153678</v>
+        <v>131153717</v>
       </c>
       <c r="B88" t="n">
-        <v>79003</v>
+        <v>79246</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9388,21 +9388,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9412,10 +9412,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>433104</v>
+        <v>432932</v>
       </c>
       <c r="R88" t="n">
-        <v>6792573</v>
+        <v>6792709</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9474,10 +9474,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131153717</v>
+        <v>131153642</v>
       </c>
       <c r="B89" t="n">
-        <v>79246</v>
+        <v>57881</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9485,34 +9485,42 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>432932</v>
+        <v>432888</v>
       </c>
       <c r="R89" t="n">
-        <v>6792709</v>
+        <v>6792650</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9571,10 +9579,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131153642</v>
+        <v>131153652</v>
       </c>
       <c r="B90" t="n">
-        <v>57881</v>
+        <v>79004</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9582,42 +9590,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>432888</v>
+        <v>433073</v>
       </c>
       <c r="R90" t="n">
-        <v>6792650</v>
+        <v>6792637</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9676,10 +9676,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131153652</v>
+        <v>131153678</v>
       </c>
       <c r="B91" t="n">
-        <v>79004</v>
+        <v>79003</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9687,21 +9687,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9711,10 +9711,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>433073</v>
+        <v>433104</v>
       </c>
       <c r="R91" t="n">
-        <v>6792637</v>
+        <v>6792573</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>

--- a/artfynd/A 1159-2026 artfynd.xlsx
+++ b/artfynd/A 1159-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131153674</v>
       </c>
       <c r="B2" t="n">
-        <v>58256</v>
+        <v>58258</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1101,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131153725</v>
+        <v>131153677</v>
       </c>
       <c r="B6" t="n">
-        <v>79246</v>
+        <v>79005</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1112,21 +1112,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1136,10 +1136,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>432886</v>
+        <v>433058</v>
       </c>
       <c r="R6" t="n">
-        <v>6792852</v>
+        <v>6792459</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,10 +1198,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131153677</v>
+        <v>131153725</v>
       </c>
       <c r="B7" t="n">
-        <v>79003</v>
+        <v>79248</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1209,21 +1209,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1233,10 +1233,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>433058</v>
+        <v>432886</v>
       </c>
       <c r="R7" t="n">
-        <v>6792459</v>
+        <v>6792852</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1402,10 +1402,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131153632</v>
+        <v>131153689</v>
       </c>
       <c r="B9" t="n">
-        <v>57881</v>
+        <v>79248</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1413,42 +1413,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>433068</v>
+        <v>432855</v>
       </c>
       <c r="R9" t="n">
-        <v>6792622</v>
+        <v>6792784</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1507,45 +1499,54 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131153689</v>
+        <v>131153656</v>
       </c>
       <c r="B10" t="n">
-        <v>79246</v>
+        <v>8451</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>432855</v>
+        <v>432815</v>
       </c>
       <c r="R10" t="n">
-        <v>6792784</v>
+        <v>6792564</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1586,6 +1587,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1604,7 +1606,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131153656</v>
+        <v>131153663</v>
       </c>
       <c r="B11" t="n">
         <v>8451</v>
@@ -1648,10 +1650,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>432815</v>
+        <v>433024</v>
       </c>
       <c r="R11" t="n">
-        <v>6792564</v>
+        <v>6792572</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1711,41 +1713,40 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131153663</v>
+        <v>131153632</v>
       </c>
       <c r="B12" t="n">
-        <v>8451</v>
+        <v>57883</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1755,10 +1756,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>433024</v>
+        <v>433068</v>
       </c>
       <c r="R12" t="n">
-        <v>6792572</v>
+        <v>6792622</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1799,7 +1800,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1818,10 +1818,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131153720</v>
+        <v>131153676</v>
       </c>
       <c r="B13" t="n">
-        <v>79246</v>
+        <v>79005</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1829,21 +1829,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1853,10 +1853,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>432962</v>
+        <v>432719</v>
       </c>
       <c r="R13" t="n">
-        <v>6792773</v>
+        <v>6792423</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1915,10 +1915,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131153676</v>
+        <v>131153712</v>
       </c>
       <c r="B14" t="n">
-        <v>79003</v>
+        <v>79248</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1926,21 +1926,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1950,10 +1950,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>432719</v>
+        <v>432967</v>
       </c>
       <c r="R14" t="n">
-        <v>6792423</v>
+        <v>6792669</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2012,10 +2012,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131153712</v>
+        <v>131153720</v>
       </c>
       <c r="B15" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2047,10 +2047,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>432967</v>
+        <v>432962</v>
       </c>
       <c r="R15" t="n">
-        <v>6792669</v>
+        <v>6792773</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2112,7 +2112,7 @@
         <v>131153621</v>
       </c>
       <c r="B16" t="n">
-        <v>79836</v>
+        <v>79838</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2206,43 +2206,37 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131153668</v>
+        <v>131153706</v>
       </c>
       <c r="B17" t="n">
-        <v>8451</v>
+        <v>79248</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2250,10 +2244,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>432974</v>
+        <v>433126</v>
       </c>
       <c r="R17" t="n">
-        <v>6792777</v>
+        <v>6792522</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2316,7 +2310,7 @@
         <v>131153695</v>
       </c>
       <c r="B18" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2410,37 +2404,43 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131153706</v>
+        <v>131153645</v>
       </c>
       <c r="B19" t="n">
-        <v>79246</v>
+        <v>5480</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>101920</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2448,10 +2448,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>433126</v>
+        <v>432996</v>
       </c>
       <c r="R19" t="n">
-        <v>6792522</v>
+        <v>6792672</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2490,7 +2490,7 @@
         <v>0</v>
       </c>
       <c r="AE19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
@@ -2511,40 +2511,41 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131153635</v>
+        <v>131153668</v>
       </c>
       <c r="B20" t="n">
-        <v>57881</v>
+        <v>8451</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2554,10 +2555,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>432968</v>
+        <v>432974</v>
       </c>
       <c r="R20" t="n">
-        <v>6792680</v>
+        <v>6792777</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2598,6 +2599,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2616,41 +2618,40 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131153645</v>
+        <v>131153635</v>
       </c>
       <c r="B21" t="n">
-        <v>5480</v>
+        <v>57883</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>101920</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N21" t="inlineStr"/>
@@ -2660,10 +2661,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>432996</v>
+        <v>432968</v>
       </c>
       <c r="R21" t="n">
-        <v>6792672</v>
+        <v>6792680</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2702,9 +2703,8 @@
         <v>0</v>
       </c>
       <c r="AE21" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF21" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2723,10 +2723,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131153622</v>
+        <v>131153729</v>
       </c>
       <c r="B22" t="n">
-        <v>57884</v>
+        <v>79248</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2734,42 +2734,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>432996</v>
+        <v>432924</v>
       </c>
       <c r="R22" t="n">
-        <v>6792778</v>
+        <v>6792835</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2828,10 +2820,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131153719</v>
+        <v>131153622</v>
       </c>
       <c r="B23" t="n">
-        <v>79246</v>
+        <v>57886</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2839,26 +2831,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2866,10 +2863,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>432964</v>
+        <v>432996</v>
       </c>
       <c r="R23" t="n">
-        <v>6792760</v>
+        <v>6792778</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2910,7 +2907,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2929,10 +2925,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131153729</v>
+        <v>131153719</v>
       </c>
       <c r="B24" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2958,16 +2954,19 @@
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>432924</v>
+        <v>432964</v>
       </c>
       <c r="R24" t="n">
-        <v>6792835</v>
+        <v>6792760</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3008,6 +3007,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3029,7 +3029,7 @@
         <v>131153718</v>
       </c>
       <c r="B25" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3230,10 +3230,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131153650</v>
+        <v>131153701</v>
       </c>
       <c r="B27" t="n">
-        <v>79004</v>
+        <v>79248</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3241,21 +3241,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>433062</v>
+        <v>432958</v>
       </c>
       <c r="R27" t="n">
-        <v>6792357</v>
+        <v>6792418</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3327,10 +3327,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131153701</v>
+        <v>131153650</v>
       </c>
       <c r="B28" t="n">
-        <v>79246</v>
+        <v>79006</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3338,21 +3338,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3362,10 +3362,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>432958</v>
+        <v>433062</v>
       </c>
       <c r="R28" t="n">
-        <v>6792418</v>
+        <v>6792357</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3424,10 +3424,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131153630</v>
+        <v>131153716</v>
       </c>
       <c r="B29" t="n">
-        <v>57881</v>
+        <v>79248</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3435,42 +3435,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>433062</v>
+        <v>432960</v>
       </c>
       <c r="R29" t="n">
-        <v>6792357</v>
+        <v>6792712</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3529,10 +3521,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131153641</v>
+        <v>131153690</v>
       </c>
       <c r="B30" t="n">
-        <v>57881</v>
+        <v>79248</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3540,31 +3532,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3572,10 +3559,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>432909</v>
+        <v>432874</v>
       </c>
       <c r="R30" t="n">
-        <v>6792876</v>
+        <v>6792733</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3616,6 +3603,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3634,10 +3622,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131153690</v>
+        <v>131153630</v>
       </c>
       <c r="B31" t="n">
-        <v>79246</v>
+        <v>57883</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3645,26 +3633,31 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3672,10 +3665,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>432874</v>
+        <v>433062</v>
       </c>
       <c r="R31" t="n">
-        <v>6792733</v>
+        <v>6792357</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3716,7 +3709,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3735,10 +3727,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131153716</v>
+        <v>131153641</v>
       </c>
       <c r="B32" t="n">
-        <v>79246</v>
+        <v>57883</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3746,34 +3738,42 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>432960</v>
+        <v>432909</v>
       </c>
       <c r="R32" t="n">
-        <v>6792712</v>
+        <v>6792876</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3832,45 +3832,54 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131153616</v>
+        <v>131153658</v>
       </c>
       <c r="B33" t="n">
-        <v>79836</v>
+        <v>8451</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>432773</v>
+        <v>433053</v>
       </c>
       <c r="R33" t="n">
-        <v>6792537</v>
+        <v>6792381</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3911,6 +3920,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3929,7 +3939,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131153658</v>
+        <v>131153665</v>
       </c>
       <c r="B34" t="n">
         <v>8451</v>
@@ -3963,7 +3973,7 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -3973,10 +3983,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>433053</v>
+        <v>432959</v>
       </c>
       <c r="R34" t="n">
-        <v>6792381</v>
+        <v>6792711</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4036,54 +4046,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131153665</v>
+        <v>131153616</v>
       </c>
       <c r="B35" t="n">
-        <v>8451</v>
+        <v>79838</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>432959</v>
+        <v>432773</v>
       </c>
       <c r="R35" t="n">
-        <v>6792711</v>
+        <v>6792537</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4124,7 +4125,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4146,7 +4146,7 @@
         <v>131153703</v>
       </c>
       <c r="B36" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4243,7 +4243,7 @@
         <v>131153702</v>
       </c>
       <c r="B37" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4340,7 +4340,7 @@
         <v>131153698</v>
       </c>
       <c r="B38" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4437,7 +4437,7 @@
         <v>131153714</v>
       </c>
       <c r="B39" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4539,7 +4539,7 @@
         <v>131153628</v>
       </c>
       <c r="B40" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4641,10 +4641,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131153710</v>
+        <v>131153708</v>
       </c>
       <c r="B41" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4676,10 +4676,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>433013</v>
+        <v>433106</v>
       </c>
       <c r="R41" t="n">
-        <v>6792587</v>
+        <v>6792609</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4738,10 +4738,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131153722</v>
+        <v>131153710</v>
       </c>
       <c r="B42" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4773,10 +4773,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>432939</v>
+        <v>433013</v>
       </c>
       <c r="R42" t="n">
-        <v>6792795</v>
+        <v>6792587</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4835,10 +4835,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131153692</v>
+        <v>131153691</v>
       </c>
       <c r="B43" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4870,10 +4870,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>432901</v>
+        <v>432881</v>
       </c>
       <c r="R43" t="n">
-        <v>6792625</v>
+        <v>6792694</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4932,10 +4932,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131153643</v>
+        <v>131153722</v>
       </c>
       <c r="B44" t="n">
-        <v>57881</v>
+        <v>79248</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4943,42 +4943,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>432969</v>
+        <v>432939</v>
       </c>
       <c r="R44" t="n">
-        <v>6792418</v>
+        <v>6792795</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5037,10 +5029,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131153640</v>
+        <v>131153692</v>
       </c>
       <c r="B45" t="n">
-        <v>57881</v>
+        <v>79248</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5048,42 +5040,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>432940</v>
+        <v>432901</v>
       </c>
       <c r="R45" t="n">
-        <v>6792843</v>
+        <v>6792625</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5142,45 +5126,54 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131153708</v>
+        <v>131153660</v>
       </c>
       <c r="B46" t="n">
-        <v>79246</v>
+        <v>8451</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>433106</v>
+        <v>433068</v>
       </c>
       <c r="R46" t="n">
-        <v>6792609</v>
+        <v>6792415</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5221,6 +5214,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5239,10 +5233,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131153691</v>
+        <v>131153643</v>
       </c>
       <c r="B47" t="n">
-        <v>79246</v>
+        <v>57883</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5250,34 +5244,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>432881</v>
+        <v>432969</v>
       </c>
       <c r="R47" t="n">
-        <v>6792694</v>
+        <v>6792418</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5336,41 +5338,40 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131153660</v>
+        <v>131153640</v>
       </c>
       <c r="B48" t="n">
-        <v>8451</v>
+        <v>57883</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -5380,10 +5381,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>433068</v>
+        <v>432940</v>
       </c>
       <c r="R48" t="n">
-        <v>6792415</v>
+        <v>6792843</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5424,7 +5425,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5550,10 +5550,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131153631</v>
+        <v>131153709</v>
       </c>
       <c r="B50" t="n">
-        <v>57881</v>
+        <v>79248</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5561,42 +5561,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>433074</v>
+        <v>433034</v>
       </c>
       <c r="R50" t="n">
-        <v>6792635</v>
+        <v>6792553</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5655,10 +5647,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131153709</v>
+        <v>131153700</v>
       </c>
       <c r="B51" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5690,10 +5682,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>433034</v>
+        <v>432910</v>
       </c>
       <c r="R51" t="n">
-        <v>6792553</v>
+        <v>6792364</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5752,10 +5744,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131153700</v>
+        <v>131153713</v>
       </c>
       <c r="B52" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5787,10 +5779,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>432910</v>
+        <v>432988</v>
       </c>
       <c r="R52" t="n">
-        <v>6792364</v>
+        <v>6792669</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5849,10 +5841,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131153713</v>
+        <v>131153631</v>
       </c>
       <c r="B53" t="n">
-        <v>79246</v>
+        <v>57883</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5860,34 +5852,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>432988</v>
+        <v>433074</v>
       </c>
       <c r="R53" t="n">
-        <v>6792669</v>
+        <v>6792635</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5949,7 +5949,7 @@
         <v>131153653</v>
       </c>
       <c r="B54" t="n">
-        <v>79004</v>
+        <v>79006</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
         <v>131153651</v>
       </c>
       <c r="B55" t="n">
-        <v>79004</v>
+        <v>79006</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6148,10 +6148,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131153618</v>
+        <v>131153696</v>
       </c>
       <c r="B56" t="n">
-        <v>79836</v>
+        <v>79248</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6159,21 +6159,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6183,10 +6183,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>433073</v>
+        <v>432758</v>
       </c>
       <c r="R56" t="n">
-        <v>6792637</v>
+        <v>6792450</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6245,10 +6245,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131153649</v>
+        <v>131153697</v>
       </c>
       <c r="B57" t="n">
-        <v>79004</v>
+        <v>79248</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6256,21 +6256,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6280,10 +6280,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>432719</v>
+        <v>432785</v>
       </c>
       <c r="R57" t="n">
-        <v>6792423</v>
+        <v>6792460</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6345,7 +6345,7 @@
         <v>131153638</v>
       </c>
       <c r="B58" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6447,10 +6447,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131153696</v>
+        <v>131153707</v>
       </c>
       <c r="B59" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6482,10 +6482,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>432758</v>
+        <v>433128</v>
       </c>
       <c r="R59" t="n">
-        <v>6792450</v>
+        <v>6792592</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6544,10 +6544,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131153697</v>
+        <v>131153704</v>
       </c>
       <c r="B60" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6579,10 +6579,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>432785</v>
+        <v>433115</v>
       </c>
       <c r="R60" t="n">
-        <v>6792460</v>
+        <v>6792436</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6641,10 +6641,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131153704</v>
+        <v>131153618</v>
       </c>
       <c r="B61" t="n">
-        <v>79246</v>
+        <v>79838</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6652,21 +6652,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6676,10 +6676,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>433115</v>
+        <v>433073</v>
       </c>
       <c r="R61" t="n">
-        <v>6792436</v>
+        <v>6792637</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6738,10 +6738,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131153707</v>
+        <v>131153649</v>
       </c>
       <c r="B62" t="n">
-        <v>79246</v>
+        <v>79006</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6749,21 +6749,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6773,10 +6773,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>433128</v>
+        <v>432719</v>
       </c>
       <c r="R62" t="n">
-        <v>6792592</v>
+        <v>6792423</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6838,7 +6838,7 @@
         <v>131153693</v>
       </c>
       <c r="B63" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6932,10 +6932,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131153727</v>
+        <v>131153633</v>
       </c>
       <c r="B64" t="n">
-        <v>79246</v>
+        <v>57883</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6943,26 +6943,31 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -6970,10 +6975,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>432935</v>
+        <v>432972</v>
       </c>
       <c r="R64" t="n">
-        <v>6792834</v>
+        <v>6792667</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7014,7 +7019,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7033,10 +7037,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131153633</v>
+        <v>131153727</v>
       </c>
       <c r="B65" t="n">
-        <v>57881</v>
+        <v>79248</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7044,31 +7048,26 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7076,10 +7075,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>432972</v>
+        <v>432935</v>
       </c>
       <c r="R65" t="n">
-        <v>6792667</v>
+        <v>6792834</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7120,6 +7119,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7245,10 +7245,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131153694</v>
+        <v>131153620</v>
       </c>
       <c r="B67" t="n">
-        <v>79246</v>
+        <v>79838</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7256,34 +7256,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>432842</v>
+        <v>433058</v>
       </c>
       <c r="R67" t="n">
-        <v>6792572</v>
+        <v>6792468</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7324,6 +7327,7 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
+      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7345,7 +7349,7 @@
         <v>131153679</v>
       </c>
       <c r="B68" t="n">
-        <v>79003</v>
+        <v>79005</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7439,54 +7443,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131153655</v>
+        <v>131153694</v>
       </c>
       <c r="B69" t="n">
-        <v>8451</v>
+        <v>79248</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>432876</v>
+        <v>432842</v>
       </c>
       <c r="R69" t="n">
-        <v>6792590</v>
+        <v>6792572</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7527,7 +7522,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7546,10 +7540,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131153620</v>
+        <v>131153636</v>
       </c>
       <c r="B70" t="n">
-        <v>79836</v>
+        <v>57883</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7557,26 +7551,31 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -7584,10 +7583,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>433058</v>
+        <v>432931</v>
       </c>
       <c r="R70" t="n">
-        <v>6792468</v>
+        <v>6792717</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7628,7 +7627,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7647,10 +7645,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131153636</v>
+        <v>131153634</v>
       </c>
       <c r="B71" t="n">
-        <v>57881</v>
+        <v>57883</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7680,7 +7678,7 @@
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N71" t="inlineStr"/>
@@ -7690,10 +7688,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>432931</v>
+        <v>432989</v>
       </c>
       <c r="R71" t="n">
-        <v>6792717</v>
+        <v>6792671</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7752,40 +7750,41 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131153634</v>
+        <v>131153655</v>
       </c>
       <c r="B72" t="n">
-        <v>57881</v>
+        <v>8451</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N72" t="inlineStr"/>
@@ -7795,10 +7794,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>432989</v>
+        <v>432876</v>
       </c>
       <c r="R72" t="n">
-        <v>6792671</v>
+        <v>6792590</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7839,6 +7838,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7857,10 +7857,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131153711</v>
+        <v>131153625</v>
       </c>
       <c r="B73" t="n">
-        <v>79246</v>
+        <v>91837</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7868,34 +7868,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>432942</v>
+        <v>433119</v>
       </c>
       <c r="R73" t="n">
-        <v>6792639</v>
+        <v>6792436</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7936,6 +7939,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -7954,10 +7958,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131153726</v>
+        <v>131153639</v>
       </c>
       <c r="B74" t="n">
-        <v>79246</v>
+        <v>57883</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7965,34 +7969,42 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>432891</v>
+        <v>432988</v>
       </c>
       <c r="R74" t="n">
-        <v>6792834</v>
+        <v>6792798</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8051,10 +8063,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131153721</v>
+        <v>131153619</v>
       </c>
       <c r="B75" t="n">
-        <v>79246</v>
+        <v>79838</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8062,37 +8074,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>432957</v>
+        <v>433004</v>
       </c>
       <c r="R75" t="n">
-        <v>6792790</v>
+        <v>6792784</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8127,18 +8136,12 @@
           <t>2026-02-14</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Måttligt med garnlav inom en radie av 50m</t>
-        </is>
-      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8157,10 +8160,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131153699</v>
+        <v>131153711</v>
       </c>
       <c r="B76" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8192,10 +8195,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>432849</v>
+        <v>432942</v>
       </c>
       <c r="R76" t="n">
-        <v>6792408</v>
+        <v>6792639</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8254,10 +8257,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131153705</v>
+        <v>131153726</v>
       </c>
       <c r="B77" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8289,10 +8292,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>433133</v>
+        <v>432891</v>
       </c>
       <c r="R77" t="n">
-        <v>6792485</v>
+        <v>6792834</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8351,10 +8354,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131153625</v>
+        <v>131153721</v>
       </c>
       <c r="B78" t="n">
-        <v>91835</v>
+        <v>79248</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8362,21 +8365,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8389,10 +8392,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>433119</v>
+        <v>432957</v>
       </c>
       <c r="R78" t="n">
-        <v>6792436</v>
+        <v>6792790</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8425,6 +8428,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Måttligt med garnlav inom en radie av 50m</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8452,10 +8460,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131153639</v>
+        <v>131153699</v>
       </c>
       <c r="B79" t="n">
-        <v>57881</v>
+        <v>79248</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8463,42 +8471,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>432988</v>
+        <v>432849</v>
       </c>
       <c r="R79" t="n">
-        <v>6792798</v>
+        <v>6792408</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8557,54 +8557,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131153669</v>
+        <v>131153705</v>
       </c>
       <c r="B80" t="n">
-        <v>8451</v>
+        <v>79248</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>432941</v>
+        <v>433133</v>
       </c>
       <c r="R80" t="n">
-        <v>6792778</v>
+        <v>6792485</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8645,7 +8636,6 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8664,45 +8654,54 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131153619</v>
+        <v>131153669</v>
       </c>
       <c r="B81" t="n">
-        <v>79836</v>
+        <v>8451</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>433004</v>
+        <v>432941</v>
       </c>
       <c r="R81" t="n">
-        <v>6792784</v>
+        <v>6792778</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8743,6 +8742,7 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -8761,43 +8761,37 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131153659</v>
+        <v>131153624</v>
       </c>
       <c r="B82" t="n">
-        <v>8451</v>
+        <v>91837</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
       <c r="K82" t="inlineStr"/>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -8805,10 +8799,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>433073</v>
+        <v>433010</v>
       </c>
       <c r="R82" t="n">
-        <v>6792412</v>
+        <v>6792353</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8871,7 +8865,7 @@
         <v>131153728</v>
       </c>
       <c r="B83" t="n">
-        <v>79246</v>
+        <v>79248</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8965,37 +8959,43 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131153624</v>
+        <v>131153659</v>
       </c>
       <c r="B84" t="n">
-        <v>91835</v>
+        <v>8451</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -9003,10 +9003,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>433010</v>
+        <v>433073</v>
       </c>
       <c r="R84" t="n">
-        <v>6792353</v>
+        <v>6792412</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9066,45 +9066,54 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131153617</v>
+        <v>131153666</v>
       </c>
       <c r="B85" t="n">
-        <v>79836</v>
+        <v>8451</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>432828</v>
+        <v>432913</v>
       </c>
       <c r="R85" t="n">
-        <v>6792424</v>
+        <v>6792742</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9145,6 +9154,7 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -9163,7 +9173,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131153666</v>
+        <v>131153664</v>
       </c>
       <c r="B86" t="n">
         <v>8451</v>
@@ -9197,7 +9207,7 @@
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N86" t="inlineStr"/>
@@ -9207,10 +9217,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>432913</v>
+        <v>433001</v>
       </c>
       <c r="R86" t="n">
-        <v>6792742</v>
+        <v>6792569</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9270,54 +9280,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131153664</v>
+        <v>131153617</v>
       </c>
       <c r="B87" t="n">
-        <v>8451</v>
+        <v>79838</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>433001</v>
+        <v>432828</v>
       </c>
       <c r="R87" t="n">
-        <v>6792569</v>
+        <v>6792424</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9358,7 +9359,6 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9377,10 +9377,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131153717</v>
+        <v>131153642</v>
       </c>
       <c r="B88" t="n">
-        <v>79246</v>
+        <v>57883</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9388,34 +9388,42 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>432932</v>
+        <v>432888</v>
       </c>
       <c r="R88" t="n">
-        <v>6792709</v>
+        <v>6792650</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9474,10 +9482,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131153642</v>
+        <v>131153678</v>
       </c>
       <c r="B89" t="n">
-        <v>57881</v>
+        <v>79005</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9485,42 +9493,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>432888</v>
+        <v>433104</v>
       </c>
       <c r="R89" t="n">
-        <v>6792650</v>
+        <v>6792573</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9579,10 +9579,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131153652</v>
+        <v>131153717</v>
       </c>
       <c r="B90" t="n">
-        <v>79004</v>
+        <v>79248</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9590,21 +9590,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9614,10 +9614,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>433073</v>
+        <v>432932</v>
       </c>
       <c r="R90" t="n">
-        <v>6792637</v>
+        <v>6792709</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9676,10 +9676,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131153678</v>
+        <v>131153652</v>
       </c>
       <c r="B91" t="n">
-        <v>79003</v>
+        <v>79006</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9687,21 +9687,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9711,10 +9711,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>433104</v>
+        <v>433073</v>
       </c>
       <c r="R91" t="n">
-        <v>6792573</v>
+        <v>6792637</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9776,7 +9776,7 @@
         <v>131153681</v>
       </c>
       <c r="B92" t="n">
-        <v>57884</v>
+        <v>57886</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 1159-2026 artfynd.xlsx
+++ b/artfynd/A 1159-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131153674</v>
       </c>
       <c r="B2" t="n">
-        <v>58258</v>
+        <v>58259</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1101,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131153677</v>
+        <v>131153725</v>
       </c>
       <c r="B6" t="n">
-        <v>79005</v>
+        <v>79249</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1112,21 +1112,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1136,10 +1136,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>433058</v>
+        <v>432886</v>
       </c>
       <c r="R6" t="n">
-        <v>6792459</v>
+        <v>6792852</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,10 +1198,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131153725</v>
+        <v>131153677</v>
       </c>
       <c r="B7" t="n">
-        <v>79248</v>
+        <v>79006</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1209,21 +1209,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1233,10 +1233,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>432886</v>
+        <v>433058</v>
       </c>
       <c r="R7" t="n">
-        <v>6792852</v>
+        <v>6792459</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1405,7 +1405,7 @@
         <v>131153689</v>
       </c>
       <c r="B9" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1499,41 +1499,40 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131153656</v>
+        <v>131153632</v>
       </c>
       <c r="B10" t="n">
-        <v>8451</v>
+        <v>57884</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1543,10 +1542,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>432815</v>
+        <v>433068</v>
       </c>
       <c r="R10" t="n">
-        <v>6792564</v>
+        <v>6792622</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1587,7 +1586,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1606,7 +1604,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131153663</v>
+        <v>131153656</v>
       </c>
       <c r="B11" t="n">
         <v>8451</v>
@@ -1650,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>433024</v>
+        <v>432815</v>
       </c>
       <c r="R11" t="n">
-        <v>6792572</v>
+        <v>6792564</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1713,40 +1711,41 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131153632</v>
+        <v>131153663</v>
       </c>
       <c r="B12" t="n">
-        <v>57883</v>
+        <v>8451</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N12" t="inlineStr"/>
@@ -1756,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>433068</v>
+        <v>433024</v>
       </c>
       <c r="R12" t="n">
-        <v>6792622</v>
+        <v>6792572</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1800,6 +1799,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1821,7 +1821,7 @@
         <v>131153676</v>
       </c>
       <c r="B13" t="n">
-        <v>79005</v>
+        <v>79006</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>131153712</v>
       </c>
       <c r="B14" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2015,7 +2015,7 @@
         <v>131153720</v>
       </c>
       <c r="B15" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         <v>131153621</v>
       </c>
       <c r="B16" t="n">
-        <v>79838</v>
+        <v>79839</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2206,10 +2206,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131153706</v>
+        <v>131153635</v>
       </c>
       <c r="B17" t="n">
-        <v>79248</v>
+        <v>57884</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2217,26 +2217,31 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2244,10 +2249,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>433126</v>
+        <v>432968</v>
       </c>
       <c r="R17" t="n">
-        <v>6792522</v>
+        <v>6792680</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2288,7 +2293,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2307,45 +2311,54 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131153695</v>
+        <v>131153645</v>
       </c>
       <c r="B18" t="n">
-        <v>79248</v>
+        <v>5480</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>101920</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>432708</v>
+        <v>432996</v>
       </c>
       <c r="R18" t="n">
-        <v>6792430</v>
+        <v>6792672</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2384,8 +2397,9 @@
         <v>0</v>
       </c>
       <c r="AE18" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2404,32 +2418,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131153645</v>
+        <v>131153668</v>
       </c>
       <c r="B19" t="n">
-        <v>5480</v>
+        <v>8451</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>101920</v>
+        <v>106545</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2448,10 +2462,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>432996</v>
+        <v>432974</v>
       </c>
       <c r="R19" t="n">
-        <v>6792672</v>
+        <v>6792777</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2490,7 +2504,7 @@
         <v>0</v>
       </c>
       <c r="AE19" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
@@ -2511,43 +2525,37 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131153668</v>
+        <v>131153706</v>
       </c>
       <c r="B20" t="n">
-        <v>8451</v>
+        <v>79249</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2555,10 +2563,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>432974</v>
+        <v>433126</v>
       </c>
       <c r="R20" t="n">
-        <v>6792777</v>
+        <v>6792522</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2618,10 +2626,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131153635</v>
+        <v>131153695</v>
       </c>
       <c r="B21" t="n">
-        <v>57883</v>
+        <v>79249</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2629,42 +2637,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>432968</v>
+        <v>432708</v>
       </c>
       <c r="R21" t="n">
-        <v>6792680</v>
+        <v>6792430</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2723,10 +2723,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131153729</v>
+        <v>131153719</v>
       </c>
       <c r="B22" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2752,16 +2752,19 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>432924</v>
+        <v>432964</v>
       </c>
       <c r="R22" t="n">
-        <v>6792835</v>
+        <v>6792760</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2802,6 +2805,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2820,10 +2824,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131153622</v>
+        <v>131153729</v>
       </c>
       <c r="B23" t="n">
-        <v>57886</v>
+        <v>79249</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2831,42 +2835,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>432996</v>
+        <v>432924</v>
       </c>
       <c r="R23" t="n">
-        <v>6792778</v>
+        <v>6792835</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2925,10 +2921,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131153719</v>
+        <v>131153622</v>
       </c>
       <c r="B24" t="n">
-        <v>79248</v>
+        <v>57887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2936,26 +2932,31 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -2963,10 +2964,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>432964</v>
+        <v>432996</v>
       </c>
       <c r="R24" t="n">
-        <v>6792760</v>
+        <v>6792778</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3007,7 +3008,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3026,45 +3026,54 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131153718</v>
+        <v>131153672</v>
       </c>
       <c r="B25" t="n">
-        <v>79248</v>
+        <v>8451</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>432974</v>
+        <v>432901</v>
       </c>
       <c r="R25" t="n">
-        <v>6792746</v>
+        <v>6792829</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3105,6 +3114,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3123,54 +3133,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131153672</v>
+        <v>131153718</v>
       </c>
       <c r="B26" t="n">
-        <v>8451</v>
+        <v>79249</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>432901</v>
+        <v>432974</v>
       </c>
       <c r="R26" t="n">
-        <v>6792829</v>
+        <v>6792746</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3211,7 +3212,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3230,10 +3230,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131153701</v>
+        <v>131153650</v>
       </c>
       <c r="B27" t="n">
-        <v>79248</v>
+        <v>79007</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3241,21 +3241,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>432958</v>
+        <v>433062</v>
       </c>
       <c r="R27" t="n">
-        <v>6792418</v>
+        <v>6792357</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3327,10 +3327,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131153650</v>
+        <v>131153701</v>
       </c>
       <c r="B28" t="n">
-        <v>79006</v>
+        <v>79249</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3338,21 +3338,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3362,10 +3362,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>433062</v>
+        <v>432958</v>
       </c>
       <c r="R28" t="n">
-        <v>6792357</v>
+        <v>6792418</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3424,10 +3424,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131153716</v>
+        <v>131153630</v>
       </c>
       <c r="B29" t="n">
-        <v>79248</v>
+        <v>57884</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3435,34 +3435,42 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>432960</v>
+        <v>433062</v>
       </c>
       <c r="R29" t="n">
-        <v>6792712</v>
+        <v>6792357</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3521,10 +3529,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131153690</v>
+        <v>131153641</v>
       </c>
       <c r="B30" t="n">
-        <v>79248</v>
+        <v>57884</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3532,26 +3540,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3559,10 +3572,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>432874</v>
+        <v>432909</v>
       </c>
       <c r="R30" t="n">
-        <v>6792733</v>
+        <v>6792876</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3603,7 +3616,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3622,10 +3634,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131153630</v>
+        <v>131153616</v>
       </c>
       <c r="B31" t="n">
-        <v>57883</v>
+        <v>79839</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3633,42 +3645,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>433062</v>
+        <v>432773</v>
       </c>
       <c r="R31" t="n">
-        <v>6792357</v>
+        <v>6792537</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3727,40 +3731,41 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131153641</v>
+        <v>131153658</v>
       </c>
       <c r="B32" t="n">
-        <v>57883</v>
+        <v>8451</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3770,10 +3775,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>432909</v>
+        <v>433053</v>
       </c>
       <c r="R32" t="n">
-        <v>6792876</v>
+        <v>6792381</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3814,6 +3819,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3832,7 +3838,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131153658</v>
+        <v>131153665</v>
       </c>
       <c r="B33" t="n">
         <v>8451</v>
@@ -3866,7 +3872,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -3876,10 +3882,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>433053</v>
+        <v>432959</v>
       </c>
       <c r="R33" t="n">
-        <v>6792381</v>
+        <v>6792711</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3939,54 +3945,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131153665</v>
+        <v>131153716</v>
       </c>
       <c r="B34" t="n">
-        <v>8451</v>
+        <v>79249</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>432959</v>
+        <v>432960</v>
       </c>
       <c r="R34" t="n">
-        <v>6792711</v>
+        <v>6792712</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4027,7 +4024,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4046,10 +4042,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131153616</v>
+        <v>131153690</v>
       </c>
       <c r="B35" t="n">
-        <v>79838</v>
+        <v>79249</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4057,34 +4053,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>432773</v>
+        <v>432874</v>
       </c>
       <c r="R35" t="n">
-        <v>6792537</v>
+        <v>6792733</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4125,6 +4124,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4143,10 +4143,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131153703</v>
+        <v>131153628</v>
       </c>
       <c r="B36" t="n">
-        <v>79248</v>
+        <v>57884</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4154,34 +4154,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>433063</v>
+        <v>432884</v>
       </c>
       <c r="R36" t="n">
-        <v>6792351</v>
+        <v>6792734</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4240,10 +4248,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131153702</v>
+        <v>131153703</v>
       </c>
       <c r="B37" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4275,10 +4283,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>433004</v>
+        <v>433063</v>
       </c>
       <c r="R37" t="n">
-        <v>6792374</v>
+        <v>6792351</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4337,10 +4345,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131153698</v>
+        <v>131153702</v>
       </c>
       <c r="B38" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4372,10 +4380,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>432819</v>
+        <v>433004</v>
       </c>
       <c r="R38" t="n">
-        <v>6792432</v>
+        <v>6792374</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4434,10 +4442,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131153714</v>
+        <v>131153698</v>
       </c>
       <c r="B39" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4469,10 +4477,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>432946</v>
+        <v>432819</v>
       </c>
       <c r="R39" t="n">
-        <v>6792696</v>
+        <v>6792432</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4505,11 +4513,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-02-14</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Måttligt med garnlav inom en radie av 50 m</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4536,10 +4539,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131153628</v>
+        <v>131153714</v>
       </c>
       <c r="B40" t="n">
-        <v>57883</v>
+        <v>79249</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4547,42 +4550,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>432884</v>
+        <v>432946</v>
       </c>
       <c r="R40" t="n">
-        <v>6792734</v>
+        <v>6792696</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4615,6 +4610,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Måttligt med garnlav inom en radie av 50 m</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4641,10 +4641,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131153708</v>
+        <v>131153710</v>
       </c>
       <c r="B41" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4676,10 +4676,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>433106</v>
+        <v>433013</v>
       </c>
       <c r="R41" t="n">
-        <v>6792609</v>
+        <v>6792587</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4738,10 +4738,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131153710</v>
+        <v>131153691</v>
       </c>
       <c r="B42" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4773,10 +4773,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>433013</v>
+        <v>432881</v>
       </c>
       <c r="R42" t="n">
-        <v>6792587</v>
+        <v>6792694</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4835,10 +4835,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131153691</v>
+        <v>131153692</v>
       </c>
       <c r="B43" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4870,10 +4870,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>432881</v>
+        <v>432901</v>
       </c>
       <c r="R43" t="n">
-        <v>6792694</v>
+        <v>6792625</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4932,10 +4932,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131153722</v>
+        <v>131153640</v>
       </c>
       <c r="B44" t="n">
-        <v>79248</v>
+        <v>57884</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4943,34 +4943,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>432939</v>
+        <v>432940</v>
       </c>
       <c r="R44" t="n">
-        <v>6792795</v>
+        <v>6792843</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5029,10 +5037,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131153692</v>
+        <v>131153643</v>
       </c>
       <c r="B45" t="n">
-        <v>79248</v>
+        <v>57884</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5040,34 +5048,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>432901</v>
+        <v>432969</v>
       </c>
       <c r="R45" t="n">
-        <v>6792625</v>
+        <v>6792418</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5126,54 +5142,45 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131153660</v>
+        <v>131153708</v>
       </c>
       <c r="B46" t="n">
-        <v>8451</v>
+        <v>79249</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>433068</v>
+        <v>433106</v>
       </c>
       <c r="R46" t="n">
-        <v>6792415</v>
+        <v>6792609</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5214,7 +5221,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5233,10 +5239,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131153643</v>
+        <v>131153722</v>
       </c>
       <c r="B47" t="n">
-        <v>57883</v>
+        <v>79249</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5244,42 +5250,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>432969</v>
+        <v>432939</v>
       </c>
       <c r="R47" t="n">
-        <v>6792418</v>
+        <v>6792795</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5338,40 +5336,41 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131153640</v>
+        <v>131153660</v>
       </c>
       <c r="B48" t="n">
-        <v>57883</v>
+        <v>8451</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -5381,10 +5380,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>432940</v>
+        <v>433068</v>
       </c>
       <c r="R48" t="n">
-        <v>6792843</v>
+        <v>6792415</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5425,6 +5424,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5550,10 +5550,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131153709</v>
+        <v>131153631</v>
       </c>
       <c r="B50" t="n">
-        <v>79248</v>
+        <v>57884</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5561,34 +5561,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>433034</v>
+        <v>433074</v>
       </c>
       <c r="R50" t="n">
-        <v>6792553</v>
+        <v>6792635</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5647,10 +5655,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131153700</v>
+        <v>131153709</v>
       </c>
       <c r="B51" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5682,10 +5690,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>432910</v>
+        <v>433034</v>
       </c>
       <c r="R51" t="n">
-        <v>6792364</v>
+        <v>6792553</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5744,10 +5752,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131153713</v>
+        <v>131153700</v>
       </c>
       <c r="B52" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5779,10 +5787,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>432988</v>
+        <v>432910</v>
       </c>
       <c r="R52" t="n">
-        <v>6792669</v>
+        <v>6792364</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5841,10 +5849,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131153631</v>
+        <v>131153713</v>
       </c>
       <c r="B53" t="n">
-        <v>57883</v>
+        <v>79249</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5852,42 +5860,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>433074</v>
+        <v>432988</v>
       </c>
       <c r="R53" t="n">
-        <v>6792635</v>
+        <v>6792669</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5949,7 +5949,7 @@
         <v>131153653</v>
       </c>
       <c r="B54" t="n">
-        <v>79006</v>
+        <v>79007</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6050,7 +6050,7 @@
         <v>131153651</v>
       </c>
       <c r="B55" t="n">
-        <v>79006</v>
+        <v>79007</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6151,7 +6151,7 @@
         <v>131153696</v>
       </c>
       <c r="B56" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6245,10 +6245,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131153697</v>
+        <v>131153707</v>
       </c>
       <c r="B57" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6280,10 +6280,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>432785</v>
+        <v>433128</v>
       </c>
       <c r="R57" t="n">
-        <v>6792460</v>
+        <v>6792592</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6342,10 +6342,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131153638</v>
+        <v>131153704</v>
       </c>
       <c r="B58" t="n">
-        <v>57883</v>
+        <v>79249</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6353,42 +6353,34 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>432927</v>
+        <v>433115</v>
       </c>
       <c r="R58" t="n">
-        <v>6792752</v>
+        <v>6792436</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6447,10 +6439,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131153707</v>
+        <v>131153697</v>
       </c>
       <c r="B59" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6482,10 +6474,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>433128</v>
+        <v>432785</v>
       </c>
       <c r="R59" t="n">
-        <v>6792592</v>
+        <v>6792460</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6544,10 +6536,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131153704</v>
+        <v>131153638</v>
       </c>
       <c r="B60" t="n">
-        <v>79248</v>
+        <v>57884</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6555,34 +6547,42 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>433115</v>
+        <v>432927</v>
       </c>
       <c r="R60" t="n">
-        <v>6792436</v>
+        <v>6792752</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6644,7 +6644,7 @@
         <v>131153618</v>
       </c>
       <c r="B61" t="n">
-        <v>79838</v>
+        <v>79839</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>131153649</v>
       </c>
       <c r="B62" t="n">
-        <v>79006</v>
+        <v>79007</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6835,45 +6835,54 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131153693</v>
+        <v>131153654</v>
       </c>
       <c r="B63" t="n">
-        <v>79248</v>
+        <v>8451</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>432849</v>
+        <v>432866</v>
       </c>
       <c r="R63" t="n">
-        <v>6792616</v>
+        <v>6792755</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6914,6 +6923,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -6932,10 +6942,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131153633</v>
+        <v>131153727</v>
       </c>
       <c r="B64" t="n">
-        <v>57883</v>
+        <v>79249</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6943,31 +6953,26 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -6975,10 +6980,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>432972</v>
+        <v>432935</v>
       </c>
       <c r="R64" t="n">
-        <v>6792667</v>
+        <v>6792834</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7019,6 +7024,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7037,10 +7043,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131153727</v>
+        <v>131153693</v>
       </c>
       <c r="B65" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7066,19 +7072,16 @@
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>432935</v>
+        <v>432849</v>
       </c>
       <c r="R65" t="n">
-        <v>6792834</v>
+        <v>6792616</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7119,7 +7122,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7138,41 +7140,40 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131153654</v>
+        <v>131153633</v>
       </c>
       <c r="B66" t="n">
-        <v>8451</v>
+        <v>57884</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -7182,10 +7183,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>432866</v>
+        <v>432972</v>
       </c>
       <c r="R66" t="n">
-        <v>6792755</v>
+        <v>6792667</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7226,7 +7227,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7248,7 +7248,7 @@
         <v>131153620</v>
       </c>
       <c r="B67" t="n">
-        <v>79838</v>
+        <v>79839</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7346,10 +7346,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131153679</v>
+        <v>131153694</v>
       </c>
       <c r="B68" t="n">
-        <v>79005</v>
+        <v>79249</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7357,21 +7357,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7381,10 +7381,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>432956</v>
+        <v>432842</v>
       </c>
       <c r="R68" t="n">
-        <v>6792683</v>
+        <v>6792572</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7443,10 +7443,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131153694</v>
+        <v>131153679</v>
       </c>
       <c r="B69" t="n">
-        <v>79248</v>
+        <v>79006</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7454,21 +7454,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7478,10 +7478,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>432842</v>
+        <v>432956</v>
       </c>
       <c r="R69" t="n">
-        <v>6792572</v>
+        <v>6792683</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7543,7 +7543,7 @@
         <v>131153636</v>
       </c>
       <c r="B70" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7648,7 +7648,7 @@
         <v>131153634</v>
       </c>
       <c r="B71" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7860,7 +7860,7 @@
         <v>131153625</v>
       </c>
       <c r="B73" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7958,10 +7958,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131153639</v>
+        <v>131153721</v>
       </c>
       <c r="B74" t="n">
-        <v>57883</v>
+        <v>79249</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7969,31 +7969,26 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -8001,10 +7996,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>432988</v>
+        <v>432957</v>
       </c>
       <c r="R74" t="n">
-        <v>6792798</v>
+        <v>6792790</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8039,12 +8034,18 @@
           <t>2026-02-14</t>
         </is>
       </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Måttligt med garnlav inom en radie av 50m</t>
+        </is>
+      </c>
       <c r="AD74" t="b">
         <v>0</v>
       </c>
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8063,10 +8064,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131153619</v>
+        <v>131153711</v>
       </c>
       <c r="B75" t="n">
-        <v>79838</v>
+        <v>79249</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8074,21 +8075,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8098,10 +8099,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>433004</v>
+        <v>432942</v>
       </c>
       <c r="R75" t="n">
-        <v>6792784</v>
+        <v>6792639</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8160,10 +8161,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131153711</v>
+        <v>131153726</v>
       </c>
       <c r="B76" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8195,10 +8196,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>432942</v>
+        <v>432891</v>
       </c>
       <c r="R76" t="n">
-        <v>6792639</v>
+        <v>6792834</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8257,10 +8258,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131153726</v>
+        <v>131153699</v>
       </c>
       <c r="B77" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8292,10 +8293,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>432891</v>
+        <v>432849</v>
       </c>
       <c r="R77" t="n">
-        <v>6792834</v>
+        <v>6792408</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8354,10 +8355,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131153721</v>
+        <v>131153705</v>
       </c>
       <c r="B78" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8383,19 +8384,16 @@
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>432957</v>
+        <v>433133</v>
       </c>
       <c r="R78" t="n">
-        <v>6792790</v>
+        <v>6792485</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8430,18 +8428,12 @@
           <t>2026-02-14</t>
         </is>
       </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Måttligt med garnlav inom en radie av 50m</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8460,10 +8452,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131153699</v>
+        <v>131153639</v>
       </c>
       <c r="B79" t="n">
-        <v>79248</v>
+        <v>57884</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8471,34 +8463,42 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>432849</v>
+        <v>432988</v>
       </c>
       <c r="R79" t="n">
-        <v>6792408</v>
+        <v>6792798</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8557,45 +8557,54 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131153705</v>
+        <v>131153669</v>
       </c>
       <c r="B80" t="n">
-        <v>79248</v>
+        <v>8451</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>433133</v>
+        <v>432941</v>
       </c>
       <c r="R80" t="n">
-        <v>6792485</v>
+        <v>6792778</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8636,6 +8645,7 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8654,54 +8664,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131153669</v>
+        <v>131153619</v>
       </c>
       <c r="B81" t="n">
-        <v>8451</v>
+        <v>79839</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>432941</v>
+        <v>433004</v>
       </c>
       <c r="R81" t="n">
-        <v>6792778</v>
+        <v>6792784</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8742,7 +8743,6 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -8764,7 +8764,7 @@
         <v>131153624</v>
       </c>
       <c r="B82" t="n">
-        <v>91837</v>
+        <v>91838</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8865,7 +8865,7 @@
         <v>131153728</v>
       </c>
       <c r="B83" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9283,7 +9283,7 @@
         <v>131153617</v>
       </c>
       <c r="B87" t="n">
-        <v>79838</v>
+        <v>79839</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9380,7 +9380,7 @@
         <v>131153642</v>
       </c>
       <c r="B88" t="n">
-        <v>57883</v>
+        <v>57884</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9482,10 +9482,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131153678</v>
+        <v>131153652</v>
       </c>
       <c r="B89" t="n">
-        <v>79005</v>
+        <v>79007</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9493,21 +9493,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9517,10 +9517,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>433104</v>
+        <v>433073</v>
       </c>
       <c r="R89" t="n">
-        <v>6792573</v>
+        <v>6792637</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9582,7 +9582,7 @@
         <v>131153717</v>
       </c>
       <c r="B90" t="n">
-        <v>79248</v>
+        <v>79249</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131153652</v>
+        <v>131153678</v>
       </c>
       <c r="B91" t="n">
         <v>79006</v>
@@ -9687,21 +9687,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9711,10 +9711,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>433073</v>
+        <v>433104</v>
       </c>
       <c r="R91" t="n">
-        <v>6792637</v>
+        <v>6792573</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9776,7 +9776,7 @@
         <v>131153681</v>
       </c>
       <c r="B92" t="n">
-        <v>57886</v>
+        <v>57887</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 1159-2026 artfynd.xlsx
+++ b/artfynd/A 1159-2026 artfynd.xlsx
@@ -1101,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131153725</v>
+        <v>131153677</v>
       </c>
       <c r="B6" t="n">
-        <v>79249</v>
+        <v>79006</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1112,21 +1112,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1136,10 +1136,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>432886</v>
+        <v>433058</v>
       </c>
       <c r="R6" t="n">
-        <v>6792852</v>
+        <v>6792459</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,10 +1198,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131153677</v>
+        <v>131153725</v>
       </c>
       <c r="B7" t="n">
-        <v>79006</v>
+        <v>79249</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1209,21 +1209,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1233,10 +1233,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>433058</v>
+        <v>432886</v>
       </c>
       <c r="R7" t="n">
-        <v>6792459</v>
+        <v>6792852</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1604,7 +1604,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131153656</v>
+        <v>131153663</v>
       </c>
       <c r="B11" t="n">
         <v>8451</v>
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>432815</v>
+        <v>433024</v>
       </c>
       <c r="R11" t="n">
-        <v>6792564</v>
+        <v>6792572</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1711,7 +1711,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131153663</v>
+        <v>131153656</v>
       </c>
       <c r="B12" t="n">
         <v>8451</v>
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>433024</v>
+        <v>432815</v>
       </c>
       <c r="R12" t="n">
-        <v>6792572</v>
+        <v>6792564</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2206,10 +2206,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131153635</v>
+        <v>131153706</v>
       </c>
       <c r="B17" t="n">
-        <v>57884</v>
+        <v>79249</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2217,31 +2217,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2249,10 +2244,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>432968</v>
+        <v>433126</v>
       </c>
       <c r="R17" t="n">
-        <v>6792680</v>
+        <v>6792522</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2293,6 +2288,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2311,54 +2307,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131153645</v>
+        <v>131153695</v>
       </c>
       <c r="B18" t="n">
-        <v>5480</v>
+        <v>79249</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>101920</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>432996</v>
+        <v>432708</v>
       </c>
       <c r="R18" t="n">
-        <v>6792672</v>
+        <v>6792430</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2397,9 +2384,8 @@
         <v>0</v>
       </c>
       <c r="AE18" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF18" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2418,32 +2404,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131153668</v>
+        <v>131153645</v>
       </c>
       <c r="B19" t="n">
-        <v>8451</v>
+        <v>5480</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>106545</v>
+        <v>101920</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2462,10 +2448,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>432974</v>
+        <v>432996</v>
       </c>
       <c r="R19" t="n">
-        <v>6792777</v>
+        <v>6792672</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2504,7 +2490,7 @@
         <v>0</v>
       </c>
       <c r="AE19" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
@@ -2525,10 +2511,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131153706</v>
+        <v>131153635</v>
       </c>
       <c r="B20" t="n">
-        <v>79249</v>
+        <v>57884</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2536,26 +2522,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2563,10 +2554,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>433126</v>
+        <v>432968</v>
       </c>
       <c r="R20" t="n">
-        <v>6792522</v>
+        <v>6792680</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2607,7 +2598,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2626,45 +2616,54 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131153695</v>
+        <v>131153668</v>
       </c>
       <c r="B21" t="n">
-        <v>79249</v>
+        <v>8451</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>432708</v>
+        <v>432974</v>
       </c>
       <c r="R21" t="n">
-        <v>6792430</v>
+        <v>6792777</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2705,6 +2704,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3026,54 +3026,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131153672</v>
+        <v>131153718</v>
       </c>
       <c r="B25" t="n">
-        <v>8451</v>
+        <v>79249</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>432901</v>
+        <v>432974</v>
       </c>
       <c r="R25" t="n">
-        <v>6792829</v>
+        <v>6792746</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3114,7 +3105,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3133,45 +3123,54 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131153718</v>
+        <v>131153672</v>
       </c>
       <c r="B26" t="n">
-        <v>79249</v>
+        <v>8451</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>432974</v>
+        <v>432901</v>
       </c>
       <c r="R26" t="n">
-        <v>6792746</v>
+        <v>6792829</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3212,6 +3211,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3230,10 +3230,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131153650</v>
+        <v>131153701</v>
       </c>
       <c r="B27" t="n">
-        <v>79007</v>
+        <v>79249</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3241,21 +3241,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>433062</v>
+        <v>432958</v>
       </c>
       <c r="R27" t="n">
-        <v>6792357</v>
+        <v>6792418</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3327,10 +3327,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131153701</v>
+        <v>131153650</v>
       </c>
       <c r="B28" t="n">
-        <v>79249</v>
+        <v>79007</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3338,21 +3338,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3362,10 +3362,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>432958</v>
+        <v>433062</v>
       </c>
       <c r="R28" t="n">
-        <v>6792418</v>
+        <v>6792357</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3424,10 +3424,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131153630</v>
+        <v>131153716</v>
       </c>
       <c r="B29" t="n">
-        <v>57884</v>
+        <v>79249</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3435,42 +3435,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>433062</v>
+        <v>432960</v>
       </c>
       <c r="R29" t="n">
-        <v>6792357</v>
+        <v>6792712</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3529,10 +3521,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131153641</v>
+        <v>131153690</v>
       </c>
       <c r="B30" t="n">
-        <v>57884</v>
+        <v>79249</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3540,31 +3532,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3572,10 +3559,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>432909</v>
+        <v>432874</v>
       </c>
       <c r="R30" t="n">
-        <v>6792876</v>
+        <v>6792733</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3616,6 +3603,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3634,10 +3622,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131153616</v>
+        <v>131153641</v>
       </c>
       <c r="B31" t="n">
-        <v>79839</v>
+        <v>57884</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3645,34 +3633,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>432773</v>
+        <v>432909</v>
       </c>
       <c r="R31" t="n">
-        <v>6792537</v>
+        <v>6792876</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3731,41 +3727,40 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131153658</v>
+        <v>131153630</v>
       </c>
       <c r="B32" t="n">
-        <v>8451</v>
+        <v>57884</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3775,10 +3770,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>433053</v>
+        <v>433062</v>
       </c>
       <c r="R32" t="n">
-        <v>6792381</v>
+        <v>6792357</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3819,7 +3814,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3838,7 +3832,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131153665</v>
+        <v>131153658</v>
       </c>
       <c r="B33" t="n">
         <v>8451</v>
@@ -3872,7 +3866,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -3882,10 +3876,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>432959</v>
+        <v>433053</v>
       </c>
       <c r="R33" t="n">
-        <v>6792711</v>
+        <v>6792381</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3945,45 +3939,54 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131153716</v>
+        <v>131153665</v>
       </c>
       <c r="B34" t="n">
-        <v>79249</v>
+        <v>8451</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>432960</v>
+        <v>432959</v>
       </c>
       <c r="R34" t="n">
-        <v>6792712</v>
+        <v>6792711</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4024,6 +4027,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4042,10 +4046,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131153690</v>
+        <v>131153616</v>
       </c>
       <c r="B35" t="n">
-        <v>79249</v>
+        <v>79839</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4053,37 +4057,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>432874</v>
+        <v>432773</v>
       </c>
       <c r="R35" t="n">
-        <v>6792733</v>
+        <v>6792537</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4124,7 +4125,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4143,10 +4143,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131153628</v>
+        <v>131153703</v>
       </c>
       <c r="B36" t="n">
-        <v>57884</v>
+        <v>79249</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4154,42 +4154,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>432884</v>
+        <v>433063</v>
       </c>
       <c r="R36" t="n">
-        <v>6792734</v>
+        <v>6792351</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4248,7 +4240,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131153703</v>
+        <v>131153702</v>
       </c>
       <c r="B37" t="n">
         <v>79249</v>
@@ -4283,10 +4275,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>433063</v>
+        <v>433004</v>
       </c>
       <c r="R37" t="n">
-        <v>6792351</v>
+        <v>6792374</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4345,7 +4337,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131153702</v>
+        <v>131153698</v>
       </c>
       <c r="B38" t="n">
         <v>79249</v>
@@ -4380,10 +4372,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>433004</v>
+        <v>432819</v>
       </c>
       <c r="R38" t="n">
-        <v>6792374</v>
+        <v>6792432</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4442,7 +4434,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131153698</v>
+        <v>131153714</v>
       </c>
       <c r="B39" t="n">
         <v>79249</v>
@@ -4477,10 +4469,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>432819</v>
+        <v>432946</v>
       </c>
       <c r="R39" t="n">
-        <v>6792432</v>
+        <v>6792696</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4513,6 +4505,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Måttligt med garnlav inom en radie av 50 m</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4539,10 +4536,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131153714</v>
+        <v>131153628</v>
       </c>
       <c r="B40" t="n">
-        <v>79249</v>
+        <v>57884</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4550,34 +4547,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>432946</v>
+        <v>432884</v>
       </c>
       <c r="R40" t="n">
-        <v>6792696</v>
+        <v>6792734</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4610,11 +4615,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-02-14</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Måttligt med garnlav inom en radie av 50 m</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4641,10 +4641,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131153710</v>
+        <v>131153640</v>
       </c>
       <c r="B41" t="n">
-        <v>79249</v>
+        <v>57884</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4652,34 +4652,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>433013</v>
+        <v>432940</v>
       </c>
       <c r="R41" t="n">
-        <v>6792587</v>
+        <v>6792843</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4738,10 +4746,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131153691</v>
+        <v>131153643</v>
       </c>
       <c r="B42" t="n">
-        <v>79249</v>
+        <v>57884</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4749,34 +4757,42 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>432881</v>
+        <v>432969</v>
       </c>
       <c r="R42" t="n">
-        <v>6792694</v>
+        <v>6792418</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4835,45 +4851,54 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131153692</v>
+        <v>131153660</v>
       </c>
       <c r="B43" t="n">
-        <v>79249</v>
+        <v>8451</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>432901</v>
+        <v>433068</v>
       </c>
       <c r="R43" t="n">
-        <v>6792625</v>
+        <v>6792415</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4914,6 +4939,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4932,10 +4958,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131153640</v>
+        <v>131153708</v>
       </c>
       <c r="B44" t="n">
-        <v>57884</v>
+        <v>79249</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4943,42 +4969,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>432940</v>
+        <v>433106</v>
       </c>
       <c r="R44" t="n">
-        <v>6792843</v>
+        <v>6792609</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5037,10 +5055,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131153643</v>
+        <v>131153710</v>
       </c>
       <c r="B45" t="n">
-        <v>57884</v>
+        <v>79249</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5048,42 +5066,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>432969</v>
+        <v>433013</v>
       </c>
       <c r="R45" t="n">
-        <v>6792418</v>
+        <v>6792587</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5142,7 +5152,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131153708</v>
+        <v>131153691</v>
       </c>
       <c r="B46" t="n">
         <v>79249</v>
@@ -5177,10 +5187,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>433106</v>
+        <v>432881</v>
       </c>
       <c r="R46" t="n">
-        <v>6792609</v>
+        <v>6792694</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5336,54 +5346,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131153660</v>
+        <v>131153692</v>
       </c>
       <c r="B48" t="n">
-        <v>8451</v>
+        <v>79249</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>433068</v>
+        <v>432901</v>
       </c>
       <c r="R48" t="n">
-        <v>6792415</v>
+        <v>6792625</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5424,7 +5425,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5550,10 +5550,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131153631</v>
+        <v>131153709</v>
       </c>
       <c r="B50" t="n">
-        <v>57884</v>
+        <v>79249</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5561,42 +5561,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>433074</v>
+        <v>433034</v>
       </c>
       <c r="R50" t="n">
-        <v>6792635</v>
+        <v>6792553</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5655,7 +5647,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131153709</v>
+        <v>131153700</v>
       </c>
       <c r="B51" t="n">
         <v>79249</v>
@@ -5690,10 +5682,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>433034</v>
+        <v>432910</v>
       </c>
       <c r="R51" t="n">
-        <v>6792553</v>
+        <v>6792364</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5752,7 +5744,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131153700</v>
+        <v>131153713</v>
       </c>
       <c r="B52" t="n">
         <v>79249</v>
@@ -5787,10 +5779,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>432910</v>
+        <v>432988</v>
       </c>
       <c r="R52" t="n">
-        <v>6792364</v>
+        <v>6792669</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5849,10 +5841,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131153713</v>
+        <v>131153653</v>
       </c>
       <c r="B53" t="n">
-        <v>79249</v>
+        <v>79007</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5860,34 +5852,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>432988</v>
+        <v>432956</v>
       </c>
       <c r="R53" t="n">
-        <v>6792669</v>
+        <v>6792683</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5928,6 +5923,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5946,7 +5942,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131153653</v>
+        <v>131153651</v>
       </c>
       <c r="B54" t="n">
         <v>79007</v>
@@ -5984,10 +5980,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>432956</v>
+        <v>433104</v>
       </c>
       <c r="R54" t="n">
-        <v>6792683</v>
+        <v>6792573</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6047,10 +6043,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131153651</v>
+        <v>131153631</v>
       </c>
       <c r="B55" t="n">
-        <v>79007</v>
+        <v>57884</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6058,26 +6054,31 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6085,10 +6086,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>433104</v>
+        <v>433074</v>
       </c>
       <c r="R55" t="n">
-        <v>6792573</v>
+        <v>6792635</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6129,7 +6130,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6342,7 +6342,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131153704</v>
+        <v>131153697</v>
       </c>
       <c r="B58" t="n">
         <v>79249</v>
@@ -6377,10 +6377,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>433115</v>
+        <v>432785</v>
       </c>
       <c r="R58" t="n">
-        <v>6792436</v>
+        <v>6792460</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6439,7 +6439,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131153697</v>
+        <v>131153704</v>
       </c>
       <c r="B59" t="n">
         <v>79249</v>
@@ -6474,10 +6474,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>432785</v>
+        <v>433115</v>
       </c>
       <c r="R59" t="n">
-        <v>6792460</v>
+        <v>6792436</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6835,54 +6835,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131153654</v>
+        <v>131153693</v>
       </c>
       <c r="B63" t="n">
-        <v>8451</v>
+        <v>79249</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>432866</v>
+        <v>432849</v>
       </c>
       <c r="R63" t="n">
-        <v>6792755</v>
+        <v>6792616</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6923,7 +6914,6 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
-      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -7043,45 +7033,54 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131153693</v>
+        <v>131153654</v>
       </c>
       <c r="B65" t="n">
-        <v>79249</v>
+        <v>8451</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>432849</v>
+        <v>432866</v>
       </c>
       <c r="R65" t="n">
-        <v>6792616</v>
+        <v>6792755</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7122,6 +7121,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7245,37 +7245,43 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131153620</v>
+        <v>131153655</v>
       </c>
       <c r="B67" t="n">
-        <v>79839</v>
+        <v>8451</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -7283,10 +7289,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>433058</v>
+        <v>432876</v>
       </c>
       <c r="R67" t="n">
-        <v>6792468</v>
+        <v>6792590</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7346,10 +7352,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131153694</v>
+        <v>131153620</v>
       </c>
       <c r="B68" t="n">
-        <v>79249</v>
+        <v>79839</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7357,34 +7363,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>432842</v>
+        <v>433058</v>
       </c>
       <c r="R68" t="n">
-        <v>6792572</v>
+        <v>6792468</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7425,6 +7434,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7750,54 +7760,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131153655</v>
+        <v>131153694</v>
       </c>
       <c r="B72" t="n">
-        <v>8451</v>
+        <v>79249</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>432876</v>
+        <v>432842</v>
       </c>
       <c r="R72" t="n">
-        <v>6792590</v>
+        <v>6792572</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7838,7 +7839,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7857,10 +7857,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131153625</v>
+        <v>131153699</v>
       </c>
       <c r="B73" t="n">
-        <v>91838</v>
+        <v>79249</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7868,37 +7868,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>433119</v>
+        <v>432849</v>
       </c>
       <c r="R73" t="n">
-        <v>6792436</v>
+        <v>6792408</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7939,7 +7936,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -7958,10 +7954,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131153721</v>
+        <v>131153625</v>
       </c>
       <c r="B74" t="n">
-        <v>79249</v>
+        <v>91838</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7969,21 +7965,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7996,10 +7992,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>432957</v>
+        <v>433119</v>
       </c>
       <c r="R74" t="n">
-        <v>6792790</v>
+        <v>6792436</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8032,11 +8028,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2026-02-14</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Måttligt med garnlav inom en radie av 50m</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8064,10 +8055,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131153711</v>
+        <v>131153619</v>
       </c>
       <c r="B75" t="n">
-        <v>79249</v>
+        <v>79839</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8075,21 +8066,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8099,10 +8090,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>432942</v>
+        <v>433004</v>
       </c>
       <c r="R75" t="n">
-        <v>6792639</v>
+        <v>6792784</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8161,7 +8152,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131153726</v>
+        <v>131153711</v>
       </c>
       <c r="B76" t="n">
         <v>79249</v>
@@ -8196,10 +8187,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>432891</v>
+        <v>432942</v>
       </c>
       <c r="R76" t="n">
-        <v>6792834</v>
+        <v>6792639</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8258,7 +8249,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131153699</v>
+        <v>131153726</v>
       </c>
       <c r="B77" t="n">
         <v>79249</v>
@@ -8293,10 +8284,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>432849</v>
+        <v>432891</v>
       </c>
       <c r="R77" t="n">
-        <v>6792408</v>
+        <v>6792834</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8355,7 +8346,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131153705</v>
+        <v>131153721</v>
       </c>
       <c r="B78" t="n">
         <v>79249</v>
@@ -8384,16 +8375,19 @@
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>433133</v>
+        <v>432957</v>
       </c>
       <c r="R78" t="n">
-        <v>6792485</v>
+        <v>6792790</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8428,12 +8422,18 @@
           <t>2026-02-14</t>
         </is>
       </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Måttligt med garnlav inom en radie av 50m</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8452,10 +8452,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131153639</v>
+        <v>131153705</v>
       </c>
       <c r="B79" t="n">
-        <v>57884</v>
+        <v>79249</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8463,42 +8463,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>432988</v>
+        <v>433133</v>
       </c>
       <c r="R79" t="n">
-        <v>6792798</v>
+        <v>6792485</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8557,41 +8549,40 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131153669</v>
+        <v>131153639</v>
       </c>
       <c r="B80" t="n">
-        <v>8451</v>
+        <v>57884</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
@@ -8601,10 +8592,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>432941</v>
+        <v>432988</v>
       </c>
       <c r="R80" t="n">
-        <v>6792778</v>
+        <v>6792798</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8645,7 +8636,6 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8664,45 +8654,54 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131153619</v>
+        <v>131153669</v>
       </c>
       <c r="B81" t="n">
-        <v>79839</v>
+        <v>8451</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>433004</v>
+        <v>432941</v>
       </c>
       <c r="R81" t="n">
-        <v>6792784</v>
+        <v>6792778</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8743,6 +8742,7 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -8761,10 +8761,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131153624</v>
+        <v>131153728</v>
       </c>
       <c r="B82" t="n">
-        <v>91838</v>
+        <v>79249</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8772,37 +8772,34 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
-      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>433010</v>
+        <v>432945</v>
       </c>
       <c r="R82" t="n">
-        <v>6792353</v>
+        <v>6792842</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8843,7 +8840,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -8862,45 +8858,54 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131153728</v>
+        <v>131153659</v>
       </c>
       <c r="B83" t="n">
-        <v>79249</v>
+        <v>8451</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>432945</v>
+        <v>433073</v>
       </c>
       <c r="R83" t="n">
-        <v>6792842</v>
+        <v>6792412</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8941,6 +8946,7 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
@@ -8959,43 +8965,37 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131153659</v>
+        <v>131153624</v>
       </c>
       <c r="B84" t="n">
-        <v>8451</v>
+        <v>91838</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -9003,10 +9003,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>433073</v>
+        <v>433010</v>
       </c>
       <c r="R84" t="n">
-        <v>6792412</v>
+        <v>6792353</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9066,7 +9066,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131153666</v>
+        <v>131153664</v>
       </c>
       <c r="B85" t="n">
         <v>8451</v>
@@ -9100,7 +9100,7 @@
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N85" t="inlineStr"/>
@@ -9110,10 +9110,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>432913</v>
+        <v>433001</v>
       </c>
       <c r="R85" t="n">
-        <v>6792742</v>
+        <v>6792569</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9173,7 +9173,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131153664</v>
+        <v>131153666</v>
       </c>
       <c r="B86" t="n">
         <v>8451</v>
@@ -9207,7 +9207,7 @@
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N86" t="inlineStr"/>
@@ -9217,10 +9217,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>433001</v>
+        <v>432913</v>
       </c>
       <c r="R86" t="n">
-        <v>6792569</v>
+        <v>6792742</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9377,10 +9377,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131153642</v>
+        <v>131153678</v>
       </c>
       <c r="B88" t="n">
-        <v>57884</v>
+        <v>79006</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9388,42 +9388,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>432888</v>
+        <v>433104</v>
       </c>
       <c r="R88" t="n">
-        <v>6792650</v>
+        <v>6792573</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9482,10 +9474,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131153652</v>
+        <v>131153642</v>
       </c>
       <c r="B89" t="n">
-        <v>79007</v>
+        <v>57884</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9493,34 +9485,42 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>433073</v>
+        <v>432888</v>
       </c>
       <c r="R89" t="n">
-        <v>6792637</v>
+        <v>6792650</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9579,10 +9579,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131153717</v>
+        <v>131153652</v>
       </c>
       <c r="B90" t="n">
-        <v>79249</v>
+        <v>79007</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9590,21 +9590,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9614,10 +9614,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>432932</v>
+        <v>433073</v>
       </c>
       <c r="R90" t="n">
-        <v>6792709</v>
+        <v>6792637</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9676,10 +9676,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131153678</v>
+        <v>131153717</v>
       </c>
       <c r="B91" t="n">
-        <v>79006</v>
+        <v>79249</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9687,21 +9687,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9711,10 +9711,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>433104</v>
+        <v>432932</v>
       </c>
       <c r="R91" t="n">
-        <v>6792573</v>
+        <v>6792709</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>

--- a/artfynd/A 1159-2026 artfynd.xlsx
+++ b/artfynd/A 1159-2026 artfynd.xlsx
@@ -1101,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131153677</v>
+        <v>131153725</v>
       </c>
       <c r="B6" t="n">
-        <v>79006</v>
+        <v>79249</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1112,21 +1112,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1136,10 +1136,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>433058</v>
+        <v>432886</v>
       </c>
       <c r="R6" t="n">
-        <v>6792459</v>
+        <v>6792852</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,45 +1198,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131153725</v>
+        <v>131153667</v>
       </c>
       <c r="B7" t="n">
-        <v>79249</v>
+        <v>8451</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>432886</v>
+        <v>432988</v>
       </c>
       <c r="R7" t="n">
-        <v>6792852</v>
+        <v>6792738</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1277,6 +1286,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1295,54 +1305,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131153667</v>
+        <v>131153677</v>
       </c>
       <c r="B8" t="n">
-        <v>8451</v>
+        <v>79006</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>432988</v>
+        <v>433058</v>
       </c>
       <c r="R8" t="n">
-        <v>6792738</v>
+        <v>6792459</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1383,7 +1384,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1604,7 +1604,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131153663</v>
+        <v>131153656</v>
       </c>
       <c r="B11" t="n">
         <v>8451</v>
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>433024</v>
+        <v>432815</v>
       </c>
       <c r="R11" t="n">
-        <v>6792572</v>
+        <v>6792564</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1711,7 +1711,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131153656</v>
+        <v>131153663</v>
       </c>
       <c r="B12" t="n">
         <v>8451</v>
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>432815</v>
+        <v>433024</v>
       </c>
       <c r="R12" t="n">
-        <v>6792564</v>
+        <v>6792572</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1818,10 +1818,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131153676</v>
+        <v>131153720</v>
       </c>
       <c r="B13" t="n">
-        <v>79006</v>
+        <v>79249</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1829,21 +1829,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1853,10 +1853,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>432719</v>
+        <v>432962</v>
       </c>
       <c r="R13" t="n">
-        <v>6792423</v>
+        <v>6792773</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1915,10 +1915,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131153712</v>
+        <v>131153621</v>
       </c>
       <c r="B14" t="n">
-        <v>79249</v>
+        <v>79839</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1926,21 +1926,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1950,10 +1950,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>432967</v>
+        <v>433070</v>
       </c>
       <c r="R14" t="n">
-        <v>6792669</v>
+        <v>6792624</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2012,7 +2012,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131153720</v>
+        <v>131153712</v>
       </c>
       <c r="B15" t="n">
         <v>79249</v>
@@ -2047,10 +2047,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>432962</v>
+        <v>432967</v>
       </c>
       <c r="R15" t="n">
-        <v>6792773</v>
+        <v>6792669</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2109,10 +2109,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131153621</v>
+        <v>131153676</v>
       </c>
       <c r="B16" t="n">
-        <v>79839</v>
+        <v>79006</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2120,21 +2120,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2144,10 +2144,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>433070</v>
+        <v>432719</v>
       </c>
       <c r="R16" t="n">
-        <v>6792624</v>
+        <v>6792423</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2206,37 +2206,43 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131153706</v>
+        <v>131153645</v>
       </c>
       <c r="B17" t="n">
-        <v>79249</v>
+        <v>5480</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>101920</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2244,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>433126</v>
+        <v>432996</v>
       </c>
       <c r="R17" t="n">
-        <v>6792522</v>
+        <v>6792672</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2286,7 +2292,7 @@
         <v>0</v>
       </c>
       <c r="AE17" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
@@ -2307,7 +2313,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131153695</v>
+        <v>131153706</v>
       </c>
       <c r="B18" t="n">
         <v>79249</v>
@@ -2336,16 +2342,19 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>432708</v>
+        <v>433126</v>
       </c>
       <c r="R18" t="n">
-        <v>6792430</v>
+        <v>6792522</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2386,6 +2395,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2404,54 +2414,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131153645</v>
+        <v>131153695</v>
       </c>
       <c r="B19" t="n">
-        <v>5480</v>
+        <v>79249</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>101920</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>432996</v>
+        <v>432708</v>
       </c>
       <c r="R19" t="n">
-        <v>6792672</v>
+        <v>6792430</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2490,9 +2491,8 @@
         <v>0</v>
       </c>
       <c r="AE19" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF19" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -3622,7 +3622,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131153641</v>
+        <v>131153630</v>
       </c>
       <c r="B31" t="n">
         <v>57884</v>
@@ -3655,7 +3655,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3665,10 +3665,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>432909</v>
+        <v>433062</v>
       </c>
       <c r="R31" t="n">
-        <v>6792876</v>
+        <v>6792357</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3727,7 +3727,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131153630</v>
+        <v>131153641</v>
       </c>
       <c r="B32" t="n">
         <v>57884</v>
@@ -3760,7 +3760,7 @@
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3770,10 +3770,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>433062</v>
+        <v>432909</v>
       </c>
       <c r="R32" t="n">
-        <v>6792357</v>
+        <v>6792876</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4641,40 +4641,41 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131153640</v>
+        <v>131153660</v>
       </c>
       <c r="B41" t="n">
-        <v>57884</v>
+        <v>8451</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -4684,10 +4685,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>432940</v>
+        <v>433068</v>
       </c>
       <c r="R41" t="n">
-        <v>6792843</v>
+        <v>6792415</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4728,6 +4729,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4851,41 +4853,40 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131153660</v>
+        <v>131153640</v>
       </c>
       <c r="B43" t="n">
-        <v>8451</v>
+        <v>57884</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
       <c r="M43" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N43" t="inlineStr"/>
@@ -4895,10 +4896,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>433068</v>
+        <v>432940</v>
       </c>
       <c r="R43" t="n">
-        <v>6792415</v>
+        <v>6792843</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4939,7 +4940,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5841,10 +5841,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131153653</v>
+        <v>131153631</v>
       </c>
       <c r="B53" t="n">
-        <v>79007</v>
+        <v>57884</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5852,26 +5852,31 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -5879,10 +5884,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>432956</v>
+        <v>433074</v>
       </c>
       <c r="R53" t="n">
-        <v>6792683</v>
+        <v>6792635</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5923,7 +5928,6 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
-      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5942,7 +5946,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131153651</v>
+        <v>131153653</v>
       </c>
       <c r="B54" t="n">
         <v>79007</v>
@@ -5980,10 +5984,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>433104</v>
+        <v>432956</v>
       </c>
       <c r="R54" t="n">
-        <v>6792573</v>
+        <v>6792683</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6043,10 +6047,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131153631</v>
+        <v>131153651</v>
       </c>
       <c r="B55" t="n">
-        <v>57884</v>
+        <v>79007</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6054,31 +6058,26 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
@@ -6086,10 +6085,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>433074</v>
+        <v>433104</v>
       </c>
       <c r="R55" t="n">
-        <v>6792635</v>
+        <v>6792573</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6130,6 +6129,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -7033,41 +7033,40 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131153654</v>
+        <v>131153633</v>
       </c>
       <c r="B65" t="n">
-        <v>8451</v>
+        <v>57884</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N65" t="inlineStr"/>
@@ -7077,10 +7076,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>432866</v>
+        <v>432972</v>
       </c>
       <c r="R65" t="n">
-        <v>6792755</v>
+        <v>6792667</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7121,7 +7120,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7140,40 +7138,41 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131153633</v>
+        <v>131153654</v>
       </c>
       <c r="B66" t="n">
-        <v>57884</v>
+        <v>8451</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -7183,10 +7182,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>432972</v>
+        <v>432866</v>
       </c>
       <c r="R66" t="n">
-        <v>6792667</v>
+        <v>6792755</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7227,6 +7226,7 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
+      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7245,54 +7245,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131153655</v>
+        <v>131153694</v>
       </c>
       <c r="B67" t="n">
-        <v>8451</v>
+        <v>79249</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>432876</v>
+        <v>432842</v>
       </c>
       <c r="R67" t="n">
-        <v>6792590</v>
+        <v>6792572</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7333,7 +7324,6 @@
       <c r="AE67" t="b">
         <v>0</v>
       </c>
-      <c r="AF67" t="inlineStr"/>
       <c r="AG67" t="b">
         <v>0</v>
       </c>
@@ -7352,10 +7342,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131153620</v>
+        <v>131153679</v>
       </c>
       <c r="B68" t="n">
-        <v>79839</v>
+        <v>79006</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7363,37 +7353,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>433058</v>
+        <v>432956</v>
       </c>
       <c r="R68" t="n">
-        <v>6792468</v>
+        <v>6792683</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7434,7 +7421,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7453,10 +7439,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131153679</v>
+        <v>131153636</v>
       </c>
       <c r="B69" t="n">
-        <v>79006</v>
+        <v>57884</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7464,34 +7450,42 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>432956</v>
+        <v>432931</v>
       </c>
       <c r="R69" t="n">
-        <v>6792683</v>
+        <v>6792717</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7550,7 +7544,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131153636</v>
+        <v>131153634</v>
       </c>
       <c r="B70" t="n">
         <v>57884</v>
@@ -7583,7 +7577,7 @@
       <c r="L70" t="inlineStr"/>
       <c r="M70" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N70" t="inlineStr"/>
@@ -7593,10 +7587,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>432931</v>
+        <v>432989</v>
       </c>
       <c r="R70" t="n">
-        <v>6792717</v>
+        <v>6792671</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7655,40 +7649,41 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131153634</v>
+        <v>131153655</v>
       </c>
       <c r="B71" t="n">
-        <v>57884</v>
+        <v>8451</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
       <c r="M71" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N71" t="inlineStr"/>
@@ -7698,10 +7693,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>432989</v>
+        <v>432876</v>
       </c>
       <c r="R71" t="n">
-        <v>6792671</v>
+        <v>6792590</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7742,6 +7737,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7760,10 +7756,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131153694</v>
+        <v>131153620</v>
       </c>
       <c r="B72" t="n">
-        <v>79249</v>
+        <v>79839</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7771,34 +7767,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>432842</v>
+        <v>433058</v>
       </c>
       <c r="R72" t="n">
-        <v>6792572</v>
+        <v>6792468</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7839,6 +7838,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7857,7 +7857,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131153699</v>
+        <v>131153711</v>
       </c>
       <c r="B73" t="n">
         <v>79249</v>
@@ -7892,10 +7892,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>432849</v>
+        <v>432942</v>
       </c>
       <c r="R73" t="n">
-        <v>6792408</v>
+        <v>6792639</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7954,10 +7954,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131153625</v>
+        <v>131153726</v>
       </c>
       <c r="B74" t="n">
-        <v>91838</v>
+        <v>79249</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7965,37 +7965,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>433119</v>
+        <v>432891</v>
       </c>
       <c r="R74" t="n">
-        <v>6792436</v>
+        <v>6792834</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8036,7 +8033,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8055,10 +8051,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131153619</v>
+        <v>131153721</v>
       </c>
       <c r="B75" t="n">
-        <v>79839</v>
+        <v>79249</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8066,34 +8062,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>433004</v>
+        <v>432957</v>
       </c>
       <c r="R75" t="n">
-        <v>6792784</v>
+        <v>6792790</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8128,12 +8127,18 @@
           <t>2026-02-14</t>
         </is>
       </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Måttligt med garnlav inom en radie av 50m</t>
+        </is>
+      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8152,7 +8157,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131153711</v>
+        <v>131153699</v>
       </c>
       <c r="B76" t="n">
         <v>79249</v>
@@ -8187,10 +8192,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>432942</v>
+        <v>432849</v>
       </c>
       <c r="R76" t="n">
-        <v>6792639</v>
+        <v>6792408</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8249,7 +8254,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131153726</v>
+        <v>131153705</v>
       </c>
       <c r="B77" t="n">
         <v>79249</v>
@@ -8284,10 +8289,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>432891</v>
+        <v>433133</v>
       </c>
       <c r="R77" t="n">
-        <v>6792834</v>
+        <v>6792485</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8346,10 +8351,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131153721</v>
+        <v>131153625</v>
       </c>
       <c r="B78" t="n">
-        <v>79249</v>
+        <v>91838</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8357,21 +8362,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8384,10 +8389,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>432957</v>
+        <v>433119</v>
       </c>
       <c r="R78" t="n">
-        <v>6792790</v>
+        <v>6792436</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8420,11 +8425,6 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2026-02-14</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Måttligt med garnlav inom en radie av 50m</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8452,10 +8452,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131153705</v>
+        <v>131153639</v>
       </c>
       <c r="B79" t="n">
-        <v>79249</v>
+        <v>57884</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8463,34 +8463,42 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>433133</v>
+        <v>432988</v>
       </c>
       <c r="R79" t="n">
-        <v>6792485</v>
+        <v>6792798</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8549,40 +8557,41 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131153639</v>
+        <v>131153669</v>
       </c>
       <c r="B80" t="n">
-        <v>57884</v>
+        <v>8451</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
@@ -8592,10 +8601,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>432988</v>
+        <v>432941</v>
       </c>
       <c r="R80" t="n">
-        <v>6792798</v>
+        <v>6792778</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8636,6 +8645,7 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8654,54 +8664,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131153669</v>
+        <v>131153619</v>
       </c>
       <c r="B81" t="n">
-        <v>8451</v>
+        <v>79839</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>432941</v>
+        <v>433004</v>
       </c>
       <c r="R81" t="n">
-        <v>6792778</v>
+        <v>6792784</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8742,7 +8743,6 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -8858,43 +8858,37 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>131153659</v>
+        <v>131153624</v>
       </c>
       <c r="B83" t="n">
-        <v>8451</v>
+        <v>91838</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>106545</v>
+        <v>5442</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
       <c r="K83" t="inlineStr"/>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
@@ -8902,10 +8896,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>433073</v>
+        <v>433010</v>
       </c>
       <c r="R83" t="n">
-        <v>6792412</v>
+        <v>6792353</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8965,37 +8959,43 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131153624</v>
+        <v>131153659</v>
       </c>
       <c r="B84" t="n">
-        <v>91838</v>
+        <v>8451</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
+      <c r="L84" t="inlineStr"/>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
@@ -9003,10 +9003,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>433010</v>
+        <v>433073</v>
       </c>
       <c r="R84" t="n">
-        <v>6792353</v>
+        <v>6792412</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9066,7 +9066,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131153664</v>
+        <v>131153666</v>
       </c>
       <c r="B85" t="n">
         <v>8451</v>
@@ -9100,7 +9100,7 @@
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N85" t="inlineStr"/>
@@ -9110,10 +9110,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>433001</v>
+        <v>432913</v>
       </c>
       <c r="R85" t="n">
-        <v>6792569</v>
+        <v>6792742</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9173,7 +9173,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131153666</v>
+        <v>131153664</v>
       </c>
       <c r="B86" t="n">
         <v>8451</v>
@@ -9207,7 +9207,7 @@
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N86" t="inlineStr"/>
@@ -9217,10 +9217,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>432913</v>
+        <v>433001</v>
       </c>
       <c r="R86" t="n">
-        <v>6792742</v>
+        <v>6792569</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9377,10 +9377,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131153678</v>
+        <v>131153717</v>
       </c>
       <c r="B88" t="n">
-        <v>79006</v>
+        <v>79249</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9388,21 +9388,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9412,10 +9412,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>433104</v>
+        <v>432932</v>
       </c>
       <c r="R88" t="n">
-        <v>6792573</v>
+        <v>6792709</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9579,10 +9579,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131153652</v>
+        <v>131153678</v>
       </c>
       <c r="B90" t="n">
-        <v>79007</v>
+        <v>79006</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9590,21 +9590,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9614,10 +9614,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>433073</v>
+        <v>433104</v>
       </c>
       <c r="R90" t="n">
-        <v>6792637</v>
+        <v>6792573</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9676,10 +9676,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131153717</v>
+        <v>131153652</v>
       </c>
       <c r="B91" t="n">
-        <v>79249</v>
+        <v>79007</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9687,21 +9687,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9711,10 +9711,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>432932</v>
+        <v>433073</v>
       </c>
       <c r="R91" t="n">
-        <v>6792709</v>
+        <v>6792637</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>

--- a/artfynd/A 1159-2026 artfynd.xlsx
+++ b/artfynd/A 1159-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131153674</v>
       </c>
       <c r="B2" t="n">
-        <v>58259</v>
+        <v>58260</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -780,7 +780,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131153673</v>
+        <v>131153657</v>
       </c>
       <c r="B3" t="n">
         <v>8451</v>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>432931</v>
+        <v>432798</v>
       </c>
       <c r="R3" t="n">
-        <v>6792867</v>
+        <v>6792471</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131153657</v>
+        <v>131153661</v>
       </c>
       <c r="B4" t="n">
         <v>8451</v>
@@ -921,7 +921,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>432798</v>
+        <v>433099</v>
       </c>
       <c r="R4" t="n">
-        <v>6792471</v>
+        <v>6792610</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,7 +994,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131153661</v>
+        <v>131153673</v>
       </c>
       <c r="B5" t="n">
         <v>8451</v>
@@ -1028,7 +1028,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1038,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>433099</v>
+        <v>432931</v>
       </c>
       <c r="R5" t="n">
-        <v>6792610</v>
+        <v>6792867</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131153725</v>
+        <v>131153677</v>
       </c>
       <c r="B6" t="n">
-        <v>79249</v>
+        <v>79007</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1112,21 +1112,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1136,10 +1136,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>432886</v>
+        <v>433058</v>
       </c>
       <c r="R6" t="n">
-        <v>6792852</v>
+        <v>6792459</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,54 +1198,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131153667</v>
+        <v>131153725</v>
       </c>
       <c r="B7" t="n">
-        <v>8451</v>
+        <v>79250</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>432988</v>
+        <v>432886</v>
       </c>
       <c r="R7" t="n">
-        <v>6792738</v>
+        <v>6792852</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1286,7 +1277,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1305,45 +1295,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>131153677</v>
+        <v>131153667</v>
       </c>
       <c r="B8" t="n">
-        <v>79006</v>
+        <v>8451</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>433058</v>
+        <v>432988</v>
       </c>
       <c r="R8" t="n">
-        <v>6792459</v>
+        <v>6792738</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1384,6 +1383,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1402,10 +1402,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131153689</v>
+        <v>131153632</v>
       </c>
       <c r="B9" t="n">
-        <v>79249</v>
+        <v>57885</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1413,34 +1413,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>432855</v>
+        <v>433068</v>
       </c>
       <c r="R9" t="n">
-        <v>6792784</v>
+        <v>6792622</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,10 +1507,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131153632</v>
+        <v>131153689</v>
       </c>
       <c r="B10" t="n">
-        <v>57884</v>
+        <v>79250</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1510,42 +1518,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>433068</v>
+        <v>432855</v>
       </c>
       <c r="R10" t="n">
-        <v>6792622</v>
+        <v>6792784</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1604,7 +1604,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>131153656</v>
+        <v>131153663</v>
       </c>
       <c r="B11" t="n">
         <v>8451</v>
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>432815</v>
+        <v>433024</v>
       </c>
       <c r="R11" t="n">
-        <v>6792564</v>
+        <v>6792572</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1711,7 +1711,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131153663</v>
+        <v>131153656</v>
       </c>
       <c r="B12" t="n">
         <v>8451</v>
@@ -1755,10 +1755,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>433024</v>
+        <v>432815</v>
       </c>
       <c r="R12" t="n">
-        <v>6792572</v>
+        <v>6792564</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1818,10 +1818,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131153720</v>
+        <v>131153676</v>
       </c>
       <c r="B13" t="n">
-        <v>79249</v>
+        <v>79007</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1829,21 +1829,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1853,10 +1853,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>432962</v>
+        <v>432719</v>
       </c>
       <c r="R13" t="n">
-        <v>6792773</v>
+        <v>6792423</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1915,10 +1915,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131153621</v>
+        <v>131153712</v>
       </c>
       <c r="B14" t="n">
-        <v>79839</v>
+        <v>79250</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1926,21 +1926,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1950,10 +1950,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>433070</v>
+        <v>432967</v>
       </c>
       <c r="R14" t="n">
-        <v>6792624</v>
+        <v>6792669</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2012,10 +2012,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131153712</v>
+        <v>131153720</v>
       </c>
       <c r="B15" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2047,10 +2047,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>432967</v>
+        <v>432962</v>
       </c>
       <c r="R15" t="n">
-        <v>6792669</v>
+        <v>6792773</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2109,10 +2109,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131153676</v>
+        <v>131153621</v>
       </c>
       <c r="B16" t="n">
-        <v>79006</v>
+        <v>79840</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2120,21 +2120,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2144,10 +2144,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>432719</v>
+        <v>433070</v>
       </c>
       <c r="R16" t="n">
-        <v>6792423</v>
+        <v>6792624</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2206,32 +2206,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131153645</v>
+        <v>131153668</v>
       </c>
       <c r="B17" t="n">
-        <v>5480</v>
+        <v>8451</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>101920</v>
+        <v>106545</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2250,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>432996</v>
+        <v>432974</v>
       </c>
       <c r="R17" t="n">
-        <v>6792672</v>
+        <v>6792777</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2292,7 +2292,7 @@
         <v>0</v>
       </c>
       <c r="AE17" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
@@ -2313,10 +2313,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131153706</v>
+        <v>131153635</v>
       </c>
       <c r="B18" t="n">
-        <v>79249</v>
+        <v>57885</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2324,26 +2324,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2351,10 +2356,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>433126</v>
+        <v>432968</v>
       </c>
       <c r="R18" t="n">
-        <v>6792522</v>
+        <v>6792680</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2395,7 +2400,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2414,45 +2418,54 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131153695</v>
+        <v>131153645</v>
       </c>
       <c r="B19" t="n">
-        <v>79249</v>
+        <v>5480</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>101920</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>432708</v>
+        <v>432996</v>
       </c>
       <c r="R19" t="n">
-        <v>6792430</v>
+        <v>6792672</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2491,8 +2504,9 @@
         <v>0</v>
       </c>
       <c r="AE19" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2511,10 +2525,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131153635</v>
+        <v>131153706</v>
       </c>
       <c r="B20" t="n">
-        <v>57884</v>
+        <v>79250</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2522,31 +2536,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2554,10 +2563,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>432968</v>
+        <v>433126</v>
       </c>
       <c r="R20" t="n">
-        <v>6792680</v>
+        <v>6792522</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2598,6 +2607,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2616,54 +2626,45 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131153668</v>
+        <v>131153695</v>
       </c>
       <c r="B21" t="n">
-        <v>8451</v>
+        <v>79250</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>432974</v>
+        <v>432708</v>
       </c>
       <c r="R21" t="n">
-        <v>6792777</v>
+        <v>6792430</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2704,7 +2705,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2723,10 +2723,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131153719</v>
+        <v>131153622</v>
       </c>
       <c r="B22" t="n">
-        <v>79249</v>
+        <v>57888</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2734,26 +2734,31 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2761,10 +2766,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>432964</v>
+        <v>432996</v>
       </c>
       <c r="R22" t="n">
-        <v>6792760</v>
+        <v>6792778</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2805,7 +2810,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2824,10 +2828,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131153729</v>
+        <v>131153719</v>
       </c>
       <c r="B23" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2853,16 +2857,19 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>432924</v>
+        <v>432964</v>
       </c>
       <c r="R23" t="n">
-        <v>6792835</v>
+        <v>6792760</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2903,6 +2910,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2921,10 +2929,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131153622</v>
+        <v>131153729</v>
       </c>
       <c r="B24" t="n">
-        <v>57887</v>
+        <v>79250</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2932,42 +2940,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>432996</v>
+        <v>432924</v>
       </c>
       <c r="R24" t="n">
-        <v>6792778</v>
+        <v>6792835</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3026,45 +3026,54 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131153718</v>
+        <v>131153672</v>
       </c>
       <c r="B25" t="n">
-        <v>79249</v>
+        <v>8451</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>432974</v>
+        <v>432901</v>
       </c>
       <c r="R25" t="n">
-        <v>6792746</v>
+        <v>6792829</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3105,6 +3114,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3123,54 +3133,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131153672</v>
+        <v>131153718</v>
       </c>
       <c r="B26" t="n">
-        <v>8451</v>
+        <v>79250</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>432901</v>
+        <v>432974</v>
       </c>
       <c r="R26" t="n">
-        <v>6792829</v>
+        <v>6792746</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3211,7 +3212,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3233,7 +3233,7 @@
         <v>131153701</v>
       </c>
       <c r="B27" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3330,7 +3330,7 @@
         <v>131153650</v>
       </c>
       <c r="B28" t="n">
-        <v>79007</v>
+        <v>79008</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3427,7 +3427,7 @@
         <v>131153716</v>
       </c>
       <c r="B29" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         <v>131153690</v>
       </c>
       <c r="B30" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3622,40 +3622,41 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131153630</v>
+        <v>131153658</v>
       </c>
       <c r="B31" t="n">
-        <v>57884</v>
+        <v>8451</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3665,10 +3666,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>433062</v>
+        <v>433053</v>
       </c>
       <c r="R31" t="n">
-        <v>6792357</v>
+        <v>6792381</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3709,6 +3710,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3727,40 +3729,41 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131153641</v>
+        <v>131153665</v>
       </c>
       <c r="B32" t="n">
-        <v>57884</v>
+        <v>8451</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3770,10 +3773,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>432909</v>
+        <v>432959</v>
       </c>
       <c r="R32" t="n">
-        <v>6792876</v>
+        <v>6792711</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3814,6 +3817,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3832,54 +3836,45 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131153658</v>
+        <v>131153616</v>
       </c>
       <c r="B33" t="n">
-        <v>8451</v>
+        <v>79840</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>433053</v>
+        <v>432773</v>
       </c>
       <c r="R33" t="n">
-        <v>6792381</v>
+        <v>6792537</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3920,7 +3915,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3939,41 +3933,40 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131153665</v>
+        <v>131153630</v>
       </c>
       <c r="B34" t="n">
-        <v>8451</v>
+        <v>57885</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -3983,10 +3976,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>432959</v>
+        <v>433062</v>
       </c>
       <c r="R34" t="n">
-        <v>6792711</v>
+        <v>6792357</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4027,7 +4020,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4046,10 +4038,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131153616</v>
+        <v>131153641</v>
       </c>
       <c r="B35" t="n">
-        <v>79839</v>
+        <v>57885</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4057,34 +4049,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>432773</v>
+        <v>432909</v>
       </c>
       <c r="R35" t="n">
-        <v>6792537</v>
+        <v>6792876</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4143,10 +4143,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131153703</v>
+        <v>131153628</v>
       </c>
       <c r="B36" t="n">
-        <v>79249</v>
+        <v>57885</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4154,34 +4154,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>433063</v>
+        <v>432884</v>
       </c>
       <c r="R36" t="n">
-        <v>6792351</v>
+        <v>6792734</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4240,10 +4248,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131153702</v>
+        <v>131153703</v>
       </c>
       <c r="B37" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4275,10 +4283,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>433004</v>
+        <v>433063</v>
       </c>
       <c r="R37" t="n">
-        <v>6792374</v>
+        <v>6792351</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4337,10 +4345,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131153698</v>
+        <v>131153702</v>
       </c>
       <c r="B38" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4372,10 +4380,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>432819</v>
+        <v>433004</v>
       </c>
       <c r="R38" t="n">
-        <v>6792432</v>
+        <v>6792374</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4434,10 +4442,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131153714</v>
+        <v>131153698</v>
       </c>
       <c r="B39" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4469,10 +4477,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>432946</v>
+        <v>432819</v>
       </c>
       <c r="R39" t="n">
-        <v>6792696</v>
+        <v>6792432</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4505,11 +4513,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-02-14</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Måttligt med garnlav inom en radie av 50 m</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4536,10 +4539,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131153628</v>
+        <v>131153714</v>
       </c>
       <c r="B40" t="n">
-        <v>57884</v>
+        <v>79250</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4547,42 +4550,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>432884</v>
+        <v>432946</v>
       </c>
       <c r="R40" t="n">
-        <v>6792734</v>
+        <v>6792696</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4615,6 +4610,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Måttligt med garnlav inom en radie av 50 m</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4641,41 +4641,40 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131153660</v>
+        <v>131153643</v>
       </c>
       <c r="B41" t="n">
-        <v>8451</v>
+        <v>57885</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -4685,10 +4684,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>433068</v>
+        <v>432969</v>
       </c>
       <c r="R41" t="n">
-        <v>6792415</v>
+        <v>6792418</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4729,7 +4728,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4748,10 +4746,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131153643</v>
+        <v>131153640</v>
       </c>
       <c r="B42" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4791,10 +4789,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>432969</v>
+        <v>432940</v>
       </c>
       <c r="R42" t="n">
-        <v>6792418</v>
+        <v>6792843</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4853,10 +4851,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131153640</v>
+        <v>131153708</v>
       </c>
       <c r="B43" t="n">
-        <v>57884</v>
+        <v>79250</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4864,42 +4862,34 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>432940</v>
+        <v>433106</v>
       </c>
       <c r="R43" t="n">
-        <v>6792843</v>
+        <v>6792609</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4958,10 +4948,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131153708</v>
+        <v>131153710</v>
       </c>
       <c r="B44" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4993,10 +4983,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>433106</v>
+        <v>433013</v>
       </c>
       <c r="R44" t="n">
-        <v>6792609</v>
+        <v>6792587</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5055,10 +5045,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131153710</v>
+        <v>131153691</v>
       </c>
       <c r="B45" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5090,10 +5080,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>433013</v>
+        <v>432881</v>
       </c>
       <c r="R45" t="n">
-        <v>6792587</v>
+        <v>6792694</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5152,10 +5142,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131153691</v>
+        <v>131153722</v>
       </c>
       <c r="B46" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5187,10 +5177,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>432881</v>
+        <v>432939</v>
       </c>
       <c r="R46" t="n">
-        <v>6792694</v>
+        <v>6792795</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5249,10 +5239,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131153722</v>
+        <v>131153692</v>
       </c>
       <c r="B47" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5284,10 +5274,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>432939</v>
+        <v>432901</v>
       </c>
       <c r="R47" t="n">
-        <v>6792795</v>
+        <v>6792625</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5346,45 +5336,54 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131153692</v>
+        <v>131153660</v>
       </c>
       <c r="B48" t="n">
-        <v>79249</v>
+        <v>8451</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>432901</v>
+        <v>433068</v>
       </c>
       <c r="R48" t="n">
-        <v>6792625</v>
+        <v>6792415</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5425,6 +5424,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5550,10 +5550,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131153709</v>
+        <v>131153631</v>
       </c>
       <c r="B50" t="n">
-        <v>79249</v>
+        <v>57885</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5561,34 +5561,42 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>433034</v>
+        <v>433074</v>
       </c>
       <c r="R50" t="n">
-        <v>6792553</v>
+        <v>6792635</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5647,10 +5655,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131153700</v>
+        <v>131153709</v>
       </c>
       <c r="B51" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5682,10 +5690,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>432910</v>
+        <v>433034</v>
       </c>
       <c r="R51" t="n">
-        <v>6792364</v>
+        <v>6792553</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5744,10 +5752,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131153713</v>
+        <v>131153700</v>
       </c>
       <c r="B52" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5779,10 +5787,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>432988</v>
+        <v>432910</v>
       </c>
       <c r="R52" t="n">
-        <v>6792669</v>
+        <v>6792364</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5841,10 +5849,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131153631</v>
+        <v>131153713</v>
       </c>
       <c r="B53" t="n">
-        <v>57884</v>
+        <v>79250</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5852,42 +5860,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>433074</v>
+        <v>432988</v>
       </c>
       <c r="R53" t="n">
-        <v>6792635</v>
+        <v>6792669</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5946,10 +5946,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131153653</v>
+        <v>131153651</v>
       </c>
       <c r="B54" t="n">
-        <v>79007</v>
+        <v>79008</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5984,10 +5984,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>432956</v>
+        <v>433104</v>
       </c>
       <c r="R54" t="n">
-        <v>6792683</v>
+        <v>6792573</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6047,10 +6047,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131153651</v>
+        <v>131153653</v>
       </c>
       <c r="B55" t="n">
-        <v>79007</v>
+        <v>79008</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6085,10 +6085,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>433104</v>
+        <v>432956</v>
       </c>
       <c r="R55" t="n">
-        <v>6792573</v>
+        <v>6792683</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6148,10 +6148,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131153696</v>
+        <v>131153638</v>
       </c>
       <c r="B56" t="n">
-        <v>79249</v>
+        <v>57885</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6159,34 +6159,42 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>432758</v>
+        <v>432927</v>
       </c>
       <c r="R56" t="n">
-        <v>6792450</v>
+        <v>6792752</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6245,10 +6253,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131153707</v>
+        <v>131153696</v>
       </c>
       <c r="B57" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6280,10 +6288,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>433128</v>
+        <v>432758</v>
       </c>
       <c r="R57" t="n">
-        <v>6792592</v>
+        <v>6792450</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6342,10 +6350,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131153697</v>
+        <v>131153707</v>
       </c>
       <c r="B58" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6377,10 +6385,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>432785</v>
+        <v>433128</v>
       </c>
       <c r="R58" t="n">
-        <v>6792460</v>
+        <v>6792592</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6439,10 +6447,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131153704</v>
+        <v>131153697</v>
       </c>
       <c r="B59" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6474,10 +6482,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>433115</v>
+        <v>432785</v>
       </c>
       <c r="R59" t="n">
-        <v>6792436</v>
+        <v>6792460</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6536,10 +6544,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131153638</v>
+        <v>131153704</v>
       </c>
       <c r="B60" t="n">
-        <v>57884</v>
+        <v>79250</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6547,42 +6555,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>432927</v>
+        <v>433115</v>
       </c>
       <c r="R60" t="n">
-        <v>6792752</v>
+        <v>6792436</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6644,7 +6644,7 @@
         <v>131153618</v>
       </c>
       <c r="B61" t="n">
-        <v>79839</v>
+        <v>79840</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6741,7 +6741,7 @@
         <v>131153649</v>
       </c>
       <c r="B62" t="n">
-        <v>79007</v>
+        <v>79008</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6838,7 +6838,7 @@
         <v>131153693</v>
       </c>
       <c r="B63" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6932,10 +6932,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131153727</v>
+        <v>131153633</v>
       </c>
       <c r="B64" t="n">
-        <v>79249</v>
+        <v>57885</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6943,26 +6943,31 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -6970,10 +6975,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>432935</v>
+        <v>432972</v>
       </c>
       <c r="R64" t="n">
-        <v>6792834</v>
+        <v>6792667</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7014,7 +7019,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7033,10 +7037,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131153633</v>
+        <v>131153727</v>
       </c>
       <c r="B65" t="n">
-        <v>57884</v>
+        <v>79250</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7044,31 +7048,26 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7076,10 +7075,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>432972</v>
+        <v>432935</v>
       </c>
       <c r="R65" t="n">
-        <v>6792667</v>
+        <v>6792834</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7120,6 +7119,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7245,10 +7245,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131153694</v>
+        <v>131153634</v>
       </c>
       <c r="B67" t="n">
-        <v>79249</v>
+        <v>57885</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7256,34 +7256,42 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>432842</v>
+        <v>432989</v>
       </c>
       <c r="R67" t="n">
-        <v>6792572</v>
+        <v>6792671</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7342,10 +7350,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131153679</v>
+        <v>131153620</v>
       </c>
       <c r="B68" t="n">
-        <v>79006</v>
+        <v>79840</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7353,34 +7361,37 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>432956</v>
+        <v>433058</v>
       </c>
       <c r="R68" t="n">
-        <v>6792683</v>
+        <v>6792468</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7421,6 +7432,7 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
+      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7442,7 +7454,7 @@
         <v>131153636</v>
       </c>
       <c r="B69" t="n">
-        <v>57884</v>
+        <v>57885</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7544,10 +7556,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131153634</v>
+        <v>131153694</v>
       </c>
       <c r="B70" t="n">
-        <v>57884</v>
+        <v>79250</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7555,42 +7567,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>432989</v>
+        <v>432842</v>
       </c>
       <c r="R70" t="n">
-        <v>6792671</v>
+        <v>6792572</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7649,54 +7653,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131153655</v>
+        <v>131153679</v>
       </c>
       <c r="B71" t="n">
-        <v>8451</v>
+        <v>79007</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="J71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>432876</v>
+        <v>432956</v>
       </c>
       <c r="R71" t="n">
-        <v>6792590</v>
+        <v>6792683</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7737,7 +7732,6 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
-      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7756,37 +7750,43 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131153620</v>
+        <v>131153655</v>
       </c>
       <c r="B72" t="n">
-        <v>79839</v>
+        <v>8451</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -7794,10 +7794,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>433058</v>
+        <v>432876</v>
       </c>
       <c r="R72" t="n">
-        <v>6792468</v>
+        <v>6792590</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7857,10 +7857,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131153711</v>
+        <v>131153639</v>
       </c>
       <c r="B73" t="n">
-        <v>79249</v>
+        <v>57885</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7868,34 +7868,42 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="K73" t="inlineStr"/>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>432942</v>
+        <v>432988</v>
       </c>
       <c r="R73" t="n">
-        <v>6792639</v>
+        <v>6792798</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7954,10 +7962,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131153726</v>
+        <v>131153625</v>
       </c>
       <c r="B74" t="n">
-        <v>79249</v>
+        <v>91839</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7965,34 +7973,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>432891</v>
+        <v>433119</v>
       </c>
       <c r="R74" t="n">
-        <v>6792834</v>
+        <v>6792436</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8033,6 +8044,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8051,37 +8063,43 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131153721</v>
+        <v>131153669</v>
       </c>
       <c r="B75" t="n">
-        <v>79249</v>
+        <v>8451</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
@@ -8089,10 +8107,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>432957</v>
+        <v>432941</v>
       </c>
       <c r="R75" t="n">
-        <v>6792790</v>
+        <v>6792778</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8125,11 +8143,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2026-02-14</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Måttligt med garnlav inom en radie av 50m</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8157,10 +8170,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131153699</v>
+        <v>131153711</v>
       </c>
       <c r="B76" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8192,10 +8205,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>432849</v>
+        <v>432942</v>
       </c>
       <c r="R76" t="n">
-        <v>6792408</v>
+        <v>6792639</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8254,10 +8267,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131153705</v>
+        <v>131153726</v>
       </c>
       <c r="B77" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8289,10 +8302,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>433133</v>
+        <v>432891</v>
       </c>
       <c r="R77" t="n">
-        <v>6792485</v>
+        <v>6792834</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8351,10 +8364,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131153625</v>
+        <v>131153721</v>
       </c>
       <c r="B78" t="n">
-        <v>91838</v>
+        <v>79250</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8362,21 +8375,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8389,10 +8402,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>433119</v>
+        <v>432957</v>
       </c>
       <c r="R78" t="n">
-        <v>6792436</v>
+        <v>6792790</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8425,6 +8438,11 @@
       <c r="AA78" t="inlineStr">
         <is>
           <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Måttligt med garnlav inom en radie av 50m</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8452,10 +8470,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131153639</v>
+        <v>131153699</v>
       </c>
       <c r="B79" t="n">
-        <v>57884</v>
+        <v>79250</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8463,42 +8481,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>432988</v>
+        <v>432849</v>
       </c>
       <c r="R79" t="n">
-        <v>6792798</v>
+        <v>6792408</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8557,54 +8567,45 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131153669</v>
+        <v>131153705</v>
       </c>
       <c r="B80" t="n">
-        <v>8451</v>
+        <v>79250</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>432941</v>
+        <v>433133</v>
       </c>
       <c r="R80" t="n">
-        <v>6792778</v>
+        <v>6792485</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8645,7 +8646,6 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
-      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8667,7 +8667,7 @@
         <v>131153619</v>
       </c>
       <c r="B81" t="n">
-        <v>79839</v>
+        <v>79840</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>131153728</v>
       </c>
       <c r="B82" t="n">
-        <v>79249</v>
+        <v>79250</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8861,7 +8861,7 @@
         <v>131153624</v>
       </c>
       <c r="B83" t="n">
-        <v>91838</v>
+        <v>91839</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9066,7 +9066,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131153666</v>
+        <v>131153664</v>
       </c>
       <c r="B85" t="n">
         <v>8451</v>
@@ -9100,7 +9100,7 @@
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N85" t="inlineStr"/>
@@ -9110,10 +9110,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>432913</v>
+        <v>433001</v>
       </c>
       <c r="R85" t="n">
-        <v>6792742</v>
+        <v>6792569</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9173,7 +9173,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131153664</v>
+        <v>131153666</v>
       </c>
       <c r="B86" t="n">
         <v>8451</v>
@@ -9207,7 +9207,7 @@
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N86" t="inlineStr"/>
@@ -9217,10 +9217,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>433001</v>
+        <v>432913</v>
       </c>
       <c r="R86" t="n">
-        <v>6792569</v>
+        <v>6792742</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9283,7 +9283,7 @@
         <v>131153617</v>
       </c>
       <c r="B87" t="n">
-        <v>79839</v>
+        <v>79840</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9377,10 +9377,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131153717</v>
+        <v>131153642</v>
       </c>
       <c r="B88" t="n">
-        <v>79249</v>
+        <v>57885</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9388,34 +9388,42 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>432932</v>
+        <v>432888</v>
       </c>
       <c r="R88" t="n">
-        <v>6792709</v>
+        <v>6792650</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9474,10 +9482,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131153642</v>
+        <v>131153717</v>
       </c>
       <c r="B89" t="n">
-        <v>57884</v>
+        <v>79250</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9485,42 +9493,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>432888</v>
+        <v>432932</v>
       </c>
       <c r="R89" t="n">
-        <v>6792650</v>
+        <v>6792709</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9582,7 +9582,7 @@
         <v>131153678</v>
       </c>
       <c r="B90" t="n">
-        <v>79006</v>
+        <v>79007</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
         <v>131153652</v>
       </c>
       <c r="B91" t="n">
-        <v>79007</v>
+        <v>79008</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9776,7 +9776,7 @@
         <v>131153681</v>
       </c>
       <c r="B92" t="n">
-        <v>57887</v>
+        <v>57888</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 1159-2026 artfynd.xlsx
+++ b/artfynd/A 1159-2026 artfynd.xlsx
@@ -780,7 +780,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>131153657</v>
+        <v>131153673</v>
       </c>
       <c r="B3" t="n">
         <v>8451</v>
@@ -824,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>432798</v>
+        <v>432931</v>
       </c>
       <c r="R3" t="n">
-        <v>6792471</v>
+        <v>6792867</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>131153661</v>
+        <v>131153657</v>
       </c>
       <c r="B4" t="n">
         <v>8451</v>
@@ -921,7 +921,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>433099</v>
+        <v>432798</v>
       </c>
       <c r="R4" t="n">
-        <v>6792610</v>
+        <v>6792471</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,7 +994,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>131153673</v>
+        <v>131153661</v>
       </c>
       <c r="B5" t="n">
         <v>8451</v>
@@ -1028,7 +1028,7 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N5" t="inlineStr"/>
@@ -1038,10 +1038,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>432931</v>
+        <v>433099</v>
       </c>
       <c r="R5" t="n">
-        <v>6792867</v>
+        <v>6792610</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1402,10 +1402,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131153632</v>
+        <v>131153689</v>
       </c>
       <c r="B9" t="n">
-        <v>57885</v>
+        <v>79250</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1413,42 +1413,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>433068</v>
+        <v>432855</v>
       </c>
       <c r="R9" t="n">
-        <v>6792622</v>
+        <v>6792784</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1507,10 +1499,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131153689</v>
+        <v>131153632</v>
       </c>
       <c r="B10" t="n">
-        <v>79250</v>
+        <v>57885</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1518,34 +1510,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>432855</v>
+        <v>433068</v>
       </c>
       <c r="R10" t="n">
-        <v>6792784</v>
+        <v>6792622</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -2206,41 +2206,40 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131153668</v>
+        <v>131153635</v>
       </c>
       <c r="B17" t="n">
-        <v>8451</v>
+        <v>57885</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2250,10 +2249,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>432974</v>
+        <v>432968</v>
       </c>
       <c r="R17" t="n">
-        <v>6792777</v>
+        <v>6792680</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2294,7 +2293,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2313,10 +2311,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131153635</v>
+        <v>131153706</v>
       </c>
       <c r="B18" t="n">
-        <v>57885</v>
+        <v>79250</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2324,31 +2322,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2356,10 +2349,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>432968</v>
+        <v>433126</v>
       </c>
       <c r="R18" t="n">
-        <v>6792680</v>
+        <v>6792522</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2400,6 +2393,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2418,54 +2412,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131153645</v>
+        <v>131153695</v>
       </c>
       <c r="B19" t="n">
-        <v>5480</v>
+        <v>79250</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>101920</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>432996</v>
+        <v>432708</v>
       </c>
       <c r="R19" t="n">
-        <v>6792672</v>
+        <v>6792430</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2504,9 +2489,8 @@
         <v>0</v>
       </c>
       <c r="AE19" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF19" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2525,37 +2509,43 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131153706</v>
+        <v>131153645</v>
       </c>
       <c r="B20" t="n">
-        <v>79250</v>
+        <v>5480</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>101920</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2563,10 +2553,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>433126</v>
+        <v>432996</v>
       </c>
       <c r="R20" t="n">
-        <v>6792522</v>
+        <v>6792672</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2605,7 +2595,7 @@
         <v>0</v>
       </c>
       <c r="AE20" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
@@ -2626,45 +2616,54 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131153695</v>
+        <v>131153668</v>
       </c>
       <c r="B21" t="n">
-        <v>79250</v>
+        <v>8451</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>432708</v>
+        <v>432974</v>
       </c>
       <c r="R21" t="n">
-        <v>6792430</v>
+        <v>6792777</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2705,6 +2704,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3026,54 +3026,45 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131153672</v>
+        <v>131153718</v>
       </c>
       <c r="B25" t="n">
-        <v>8451</v>
+        <v>79250</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>432901</v>
+        <v>432974</v>
       </c>
       <c r="R25" t="n">
-        <v>6792829</v>
+        <v>6792746</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3114,7 +3105,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3133,45 +3123,54 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131153718</v>
+        <v>131153672</v>
       </c>
       <c r="B26" t="n">
-        <v>79250</v>
+        <v>8451</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>432974</v>
+        <v>432901</v>
       </c>
       <c r="R26" t="n">
-        <v>6792746</v>
+        <v>6792829</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3212,6 +3211,7 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3622,54 +3622,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131153658</v>
+        <v>131153616</v>
       </c>
       <c r="B31" t="n">
-        <v>8451</v>
+        <v>79840</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>433053</v>
+        <v>432773</v>
       </c>
       <c r="R31" t="n">
-        <v>6792381</v>
+        <v>6792537</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3710,7 +3701,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3729,41 +3719,40 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131153665</v>
+        <v>131153641</v>
       </c>
       <c r="B32" t="n">
-        <v>8451</v>
+        <v>57885</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3773,10 +3762,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>432959</v>
+        <v>432909</v>
       </c>
       <c r="R32" t="n">
-        <v>6792711</v>
+        <v>6792876</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3817,7 +3806,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3836,10 +3824,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131153616</v>
+        <v>131153630</v>
       </c>
       <c r="B33" t="n">
-        <v>79840</v>
+        <v>57885</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3847,34 +3835,42 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>432773</v>
+        <v>433062</v>
       </c>
       <c r="R33" t="n">
-        <v>6792537</v>
+        <v>6792357</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3933,40 +3929,41 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131153630</v>
+        <v>131153658</v>
       </c>
       <c r="B34" t="n">
-        <v>57885</v>
+        <v>8451</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -3976,10 +3973,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>433062</v>
+        <v>433053</v>
       </c>
       <c r="R34" t="n">
-        <v>6792357</v>
+        <v>6792381</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4020,6 +4017,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4038,40 +4036,41 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131153641</v>
+        <v>131153665</v>
       </c>
       <c r="B35" t="n">
-        <v>57885</v>
+        <v>8451</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N35" t="inlineStr"/>
@@ -4081,10 +4080,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>432909</v>
+        <v>432959</v>
       </c>
       <c r="R35" t="n">
-        <v>6792876</v>
+        <v>6792711</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4125,6 +4124,7 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
+      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4143,10 +4143,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131153628</v>
+        <v>131153703</v>
       </c>
       <c r="B36" t="n">
-        <v>57885</v>
+        <v>79250</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4154,42 +4154,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>432884</v>
+        <v>433063</v>
       </c>
       <c r="R36" t="n">
-        <v>6792734</v>
+        <v>6792351</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4248,7 +4240,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131153703</v>
+        <v>131153702</v>
       </c>
       <c r="B37" t="n">
         <v>79250</v>
@@ -4283,10 +4275,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>433063</v>
+        <v>433004</v>
       </c>
       <c r="R37" t="n">
-        <v>6792351</v>
+        <v>6792374</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4345,7 +4337,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131153702</v>
+        <v>131153698</v>
       </c>
       <c r="B38" t="n">
         <v>79250</v>
@@ -4380,10 +4372,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>433004</v>
+        <v>432819</v>
       </c>
       <c r="R38" t="n">
-        <v>6792374</v>
+        <v>6792432</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4442,7 +4434,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131153698</v>
+        <v>131153714</v>
       </c>
       <c r="B39" t="n">
         <v>79250</v>
@@ -4477,10 +4469,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>432819</v>
+        <v>432946</v>
       </c>
       <c r="R39" t="n">
-        <v>6792432</v>
+        <v>6792696</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4513,6 +4505,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Måttligt med garnlav inom en radie av 50 m</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4539,10 +4536,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131153714</v>
+        <v>131153628</v>
       </c>
       <c r="B40" t="n">
-        <v>79250</v>
+        <v>57885</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4550,34 +4547,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>432946</v>
+        <v>432884</v>
       </c>
       <c r="R40" t="n">
-        <v>6792696</v>
+        <v>6792734</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4610,11 +4615,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-02-14</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Måttligt med garnlav inom en radie av 50 m</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4641,7 +4641,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131153643</v>
+        <v>131153640</v>
       </c>
       <c r="B41" t="n">
         <v>57885</v>
@@ -4684,10 +4684,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>432969</v>
+        <v>432940</v>
       </c>
       <c r="R41" t="n">
-        <v>6792418</v>
+        <v>6792843</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4746,7 +4746,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131153640</v>
+        <v>131153643</v>
       </c>
       <c r="B42" t="n">
         <v>57885</v>
@@ -4789,10 +4789,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>432940</v>
+        <v>432969</v>
       </c>
       <c r="R42" t="n">
-        <v>6792843</v>
+        <v>6792418</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4851,45 +4851,54 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131153708</v>
+        <v>131153660</v>
       </c>
       <c r="B43" t="n">
-        <v>79250</v>
+        <v>8451</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>433106</v>
+        <v>433068</v>
       </c>
       <c r="R43" t="n">
-        <v>6792609</v>
+        <v>6792415</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4930,6 +4939,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4948,7 +4958,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131153710</v>
+        <v>131153708</v>
       </c>
       <c r="B44" t="n">
         <v>79250</v>
@@ -4983,10 +4993,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>433013</v>
+        <v>433106</v>
       </c>
       <c r="R44" t="n">
-        <v>6792587</v>
+        <v>6792609</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5045,7 +5055,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131153691</v>
+        <v>131153710</v>
       </c>
       <c r="B45" t="n">
         <v>79250</v>
@@ -5080,10 +5090,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>432881</v>
+        <v>433013</v>
       </c>
       <c r="R45" t="n">
-        <v>6792694</v>
+        <v>6792587</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5142,7 +5152,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131153722</v>
+        <v>131153691</v>
       </c>
       <c r="B46" t="n">
         <v>79250</v>
@@ -5177,10 +5187,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>432939</v>
+        <v>432881</v>
       </c>
       <c r="R46" t="n">
-        <v>6792795</v>
+        <v>6792694</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5239,7 +5249,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131153692</v>
+        <v>131153722</v>
       </c>
       <c r="B47" t="n">
         <v>79250</v>
@@ -5274,10 +5284,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>432901</v>
+        <v>432939</v>
       </c>
       <c r="R47" t="n">
-        <v>6792625</v>
+        <v>6792795</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5336,54 +5346,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131153660</v>
+        <v>131153692</v>
       </c>
       <c r="B48" t="n">
-        <v>8451</v>
+        <v>79250</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>433068</v>
+        <v>432901</v>
       </c>
       <c r="R48" t="n">
-        <v>6792415</v>
+        <v>6792625</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5424,7 +5425,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5655,10 +5655,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131153709</v>
+        <v>131153651</v>
       </c>
       <c r="B51" t="n">
-        <v>79250</v>
+        <v>79008</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5666,34 +5666,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>433034</v>
+        <v>433104</v>
       </c>
       <c r="R51" t="n">
-        <v>6792553</v>
+        <v>6792573</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5734,6 +5737,7 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
+      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5752,10 +5756,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131153700</v>
+        <v>131153653</v>
       </c>
       <c r="B52" t="n">
-        <v>79250</v>
+        <v>79008</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5763,34 +5767,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>432910</v>
+        <v>432956</v>
       </c>
       <c r="R52" t="n">
-        <v>6792364</v>
+        <v>6792683</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5831,6 +5838,7 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5849,7 +5857,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131153713</v>
+        <v>131153709</v>
       </c>
       <c r="B53" t="n">
         <v>79250</v>
@@ -5884,10 +5892,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>432988</v>
+        <v>433034</v>
       </c>
       <c r="R53" t="n">
-        <v>6792669</v>
+        <v>6792553</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5946,10 +5954,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131153651</v>
+        <v>131153700</v>
       </c>
       <c r="B54" t="n">
-        <v>79008</v>
+        <v>79250</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5957,37 +5965,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>433104</v>
+        <v>432910</v>
       </c>
       <c r="R54" t="n">
-        <v>6792573</v>
+        <v>6792364</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6028,7 +6033,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6047,10 +6051,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131153653</v>
+        <v>131153713</v>
       </c>
       <c r="B55" t="n">
-        <v>79008</v>
+        <v>79250</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6058,37 +6062,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>432956</v>
+        <v>432988</v>
       </c>
       <c r="R55" t="n">
-        <v>6792683</v>
+        <v>6792669</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6129,7 +6130,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6148,10 +6148,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131153638</v>
+        <v>131153618</v>
       </c>
       <c r="B56" t="n">
-        <v>57885</v>
+        <v>79840</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6159,42 +6159,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>432927</v>
+        <v>433073</v>
       </c>
       <c r="R56" t="n">
-        <v>6792752</v>
+        <v>6792637</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6253,10 +6245,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131153696</v>
+        <v>131153649</v>
       </c>
       <c r="B57" t="n">
-        <v>79250</v>
+        <v>79008</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6264,21 +6256,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6288,10 +6280,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>432758</v>
+        <v>432719</v>
       </c>
       <c r="R57" t="n">
-        <v>6792450</v>
+        <v>6792423</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6350,7 +6342,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131153707</v>
+        <v>131153696</v>
       </c>
       <c r="B58" t="n">
         <v>79250</v>
@@ -6385,10 +6377,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>433128</v>
+        <v>432758</v>
       </c>
       <c r="R58" t="n">
-        <v>6792592</v>
+        <v>6792450</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6447,7 +6439,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131153697</v>
+        <v>131153707</v>
       </c>
       <c r="B59" t="n">
         <v>79250</v>
@@ -6482,10 +6474,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>432785</v>
+        <v>433128</v>
       </c>
       <c r="R59" t="n">
-        <v>6792460</v>
+        <v>6792592</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6544,7 +6536,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131153704</v>
+        <v>131153697</v>
       </c>
       <c r="B60" t="n">
         <v>79250</v>
@@ -6579,10 +6571,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>433115</v>
+        <v>432785</v>
       </c>
       <c r="R60" t="n">
-        <v>6792436</v>
+        <v>6792460</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6641,10 +6633,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131153618</v>
+        <v>131153704</v>
       </c>
       <c r="B61" t="n">
-        <v>79840</v>
+        <v>79250</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6652,21 +6644,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6676,10 +6668,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>433073</v>
+        <v>433115</v>
       </c>
       <c r="R61" t="n">
-        <v>6792637</v>
+        <v>6792436</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6738,10 +6730,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131153649</v>
+        <v>131153638</v>
       </c>
       <c r="B62" t="n">
-        <v>79008</v>
+        <v>57885</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6749,34 +6741,42 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>432719</v>
+        <v>432927</v>
       </c>
       <c r="R62" t="n">
-        <v>6792423</v>
+        <v>6792752</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6932,10 +6932,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131153633</v>
+        <v>131153727</v>
       </c>
       <c r="B64" t="n">
-        <v>57885</v>
+        <v>79250</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6943,31 +6943,26 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
@@ -6975,10 +6970,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>432972</v>
+        <v>432935</v>
       </c>
       <c r="R64" t="n">
-        <v>6792667</v>
+        <v>6792834</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7019,6 +7014,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7037,10 +7033,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131153727</v>
+        <v>131153633</v>
       </c>
       <c r="B65" t="n">
-        <v>79250</v>
+        <v>57885</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7048,26 +7044,31 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7075,10 +7076,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>432935</v>
+        <v>432972</v>
       </c>
       <c r="R65" t="n">
-        <v>6792834</v>
+        <v>6792667</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7119,7 +7120,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7245,10 +7245,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131153634</v>
+        <v>131153694</v>
       </c>
       <c r="B67" t="n">
-        <v>57885</v>
+        <v>79250</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7256,42 +7256,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>432989</v>
+        <v>432842</v>
       </c>
       <c r="R67" t="n">
-        <v>6792671</v>
+        <v>6792572</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7350,10 +7342,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131153620</v>
+        <v>131153679</v>
       </c>
       <c r="B68" t="n">
-        <v>79840</v>
+        <v>79007</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7361,37 +7353,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>433058</v>
+        <v>432956</v>
       </c>
       <c r="R68" t="n">
-        <v>6792468</v>
+        <v>6792683</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7432,7 +7421,6 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
       </c>
@@ -7451,40 +7439,41 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131153636</v>
+        <v>131153655</v>
       </c>
       <c r="B69" t="n">
-        <v>57885</v>
+        <v>8451</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
@@ -7494,10 +7483,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>432931</v>
+        <v>432876</v>
       </c>
       <c r="R69" t="n">
-        <v>6792717</v>
+        <v>6792590</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7538,6 +7527,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7556,10 +7546,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131153694</v>
+        <v>131153636</v>
       </c>
       <c r="B70" t="n">
-        <v>79250</v>
+        <v>57885</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7567,34 +7557,42 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>432842</v>
+        <v>432931</v>
       </c>
       <c r="R70" t="n">
-        <v>6792572</v>
+        <v>6792717</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7653,10 +7651,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131153679</v>
+        <v>131153634</v>
       </c>
       <c r="B71" t="n">
-        <v>79007</v>
+        <v>57885</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7664,34 +7662,42 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>432956</v>
+        <v>432989</v>
       </c>
       <c r="R71" t="n">
-        <v>6792683</v>
+        <v>6792671</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7750,43 +7756,37 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131153655</v>
+        <v>131153620</v>
       </c>
       <c r="B72" t="n">
-        <v>8451</v>
+        <v>79840</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -7794,10 +7794,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>432876</v>
+        <v>433058</v>
       </c>
       <c r="R72" t="n">
-        <v>6792590</v>
+        <v>6792468</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7857,40 +7857,41 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131153639</v>
+        <v>131153669</v>
       </c>
       <c r="B73" t="n">
-        <v>57885</v>
+        <v>8451</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
@@ -7900,10 +7901,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>432988</v>
+        <v>432941</v>
       </c>
       <c r="R73" t="n">
-        <v>6792798</v>
+        <v>6792778</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7944,6 +7945,7 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
+      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -7962,10 +7964,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131153625</v>
+        <v>131153711</v>
       </c>
       <c r="B74" t="n">
-        <v>91839</v>
+        <v>79250</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7973,37 +7975,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>433119</v>
+        <v>432942</v>
       </c>
       <c r="R74" t="n">
-        <v>6792436</v>
+        <v>6792639</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8044,7 +8043,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8063,54 +8061,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131153669</v>
+        <v>131153726</v>
       </c>
       <c r="B75" t="n">
-        <v>8451</v>
+        <v>79250</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="J75" t="inlineStr"/>
-      <c r="K75" t="inlineStr"/>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>432941</v>
+        <v>432891</v>
       </c>
       <c r="R75" t="n">
-        <v>6792778</v>
+        <v>6792834</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8151,7 +8140,6 @@
       <c r="AE75" t="b">
         <v>0</v>
       </c>
-      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8170,7 +8158,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131153711</v>
+        <v>131153721</v>
       </c>
       <c r="B76" t="n">
         <v>79250</v>
@@ -8199,16 +8187,19 @@
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>432942</v>
+        <v>432957</v>
       </c>
       <c r="R76" t="n">
-        <v>6792639</v>
+        <v>6792790</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8243,12 +8234,18 @@
           <t>2026-02-14</t>
         </is>
       </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Måttligt med garnlav inom en radie av 50m</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
+      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8267,7 +8264,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131153726</v>
+        <v>131153699</v>
       </c>
       <c r="B77" t="n">
         <v>79250</v>
@@ -8302,10 +8299,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>432891</v>
+        <v>432849</v>
       </c>
       <c r="R77" t="n">
-        <v>6792834</v>
+        <v>6792408</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8364,7 +8361,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131153721</v>
+        <v>131153705</v>
       </c>
       <c r="B78" t="n">
         <v>79250</v>
@@ -8393,19 +8390,16 @@
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>432957</v>
+        <v>433133</v>
       </c>
       <c r="R78" t="n">
-        <v>6792790</v>
+        <v>6792485</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8440,18 +8434,12 @@
           <t>2026-02-14</t>
         </is>
       </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Måttligt med garnlav inom en radie av 50m</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8470,10 +8458,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131153699</v>
+        <v>131153625</v>
       </c>
       <c r="B79" t="n">
-        <v>79250</v>
+        <v>91839</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8481,34 +8469,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>432849</v>
+        <v>433119</v>
       </c>
       <c r="R79" t="n">
-        <v>6792408</v>
+        <v>6792436</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8549,6 +8540,7 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8567,10 +8559,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131153705</v>
+        <v>131153639</v>
       </c>
       <c r="B80" t="n">
-        <v>79250</v>
+        <v>57885</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8578,34 +8570,42 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>433133</v>
+        <v>432988</v>
       </c>
       <c r="R80" t="n">
-        <v>6792485</v>
+        <v>6792798</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9377,10 +9377,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131153642</v>
+        <v>131153652</v>
       </c>
       <c r="B88" t="n">
-        <v>57885</v>
+        <v>79008</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9388,42 +9388,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>432888</v>
+        <v>433073</v>
       </c>
       <c r="R88" t="n">
-        <v>6792650</v>
+        <v>6792637</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9676,10 +9668,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131153652</v>
+        <v>131153642</v>
       </c>
       <c r="B91" t="n">
-        <v>79008</v>
+        <v>57885</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9687,34 +9679,42 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>433073</v>
+        <v>432888</v>
       </c>
       <c r="R91" t="n">
-        <v>6792637</v>
+        <v>6792650</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>

--- a/artfynd/A 1159-2026 artfynd.xlsx
+++ b/artfynd/A 1159-2026 artfynd.xlsx
@@ -2206,10 +2206,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>131153635</v>
+        <v>131153706</v>
       </c>
       <c r="B17" t="n">
-        <v>57885</v>
+        <v>79250</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2217,31 +2217,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2249,10 +2244,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>432968</v>
+        <v>433126</v>
       </c>
       <c r="R17" t="n">
-        <v>6792680</v>
+        <v>6792522</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2293,6 +2288,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2311,7 +2307,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131153706</v>
+        <v>131153695</v>
       </c>
       <c r="B18" t="n">
         <v>79250</v>
@@ -2340,19 +2336,16 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>433126</v>
+        <v>432708</v>
       </c>
       <c r="R18" t="n">
-        <v>6792522</v>
+        <v>6792430</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2393,7 +2386,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2412,45 +2404,54 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131153695</v>
+        <v>131153645</v>
       </c>
       <c r="B19" t="n">
-        <v>79250</v>
+        <v>5480</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>101920</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>432708</v>
+        <v>432996</v>
       </c>
       <c r="R19" t="n">
-        <v>6792430</v>
+        <v>6792672</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2489,8 +2490,9 @@
         <v>0</v>
       </c>
       <c r="AE19" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2509,41 +2511,40 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131153645</v>
+        <v>131153635</v>
       </c>
       <c r="B20" t="n">
-        <v>5480</v>
+        <v>57885</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>101920</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2553,10 +2554,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>432996</v>
+        <v>432968</v>
       </c>
       <c r="R20" t="n">
-        <v>6792672</v>
+        <v>6792680</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2595,9 +2596,8 @@
         <v>0</v>
       </c>
       <c r="AE20" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF20" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -3622,45 +3622,54 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131153616</v>
+        <v>131153658</v>
       </c>
       <c r="B31" t="n">
-        <v>79840</v>
+        <v>8451</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>432773</v>
+        <v>433053</v>
       </c>
       <c r="R31" t="n">
-        <v>6792537</v>
+        <v>6792381</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3701,6 +3710,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3719,40 +3729,41 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131153641</v>
+        <v>131153665</v>
       </c>
       <c r="B32" t="n">
-        <v>57885</v>
+        <v>8451</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3762,10 +3773,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>432909</v>
+        <v>432959</v>
       </c>
       <c r="R32" t="n">
-        <v>6792876</v>
+        <v>6792711</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3806,6 +3817,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3824,7 +3836,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131153630</v>
+        <v>131153641</v>
       </c>
       <c r="B33" t="n">
         <v>57885</v>
@@ -3857,7 +3869,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -3867,10 +3879,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>433062</v>
+        <v>432909</v>
       </c>
       <c r="R33" t="n">
-        <v>6792357</v>
+        <v>6792876</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3929,41 +3941,40 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131153658</v>
+        <v>131153630</v>
       </c>
       <c r="B34" t="n">
-        <v>8451</v>
+        <v>57885</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -3973,10 +3984,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>433053</v>
+        <v>433062</v>
       </c>
       <c r="R34" t="n">
-        <v>6792381</v>
+        <v>6792357</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4017,7 +4028,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4036,54 +4046,45 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131153665</v>
+        <v>131153616</v>
       </c>
       <c r="B35" t="n">
-        <v>8451</v>
+        <v>79840</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>432959</v>
+        <v>432773</v>
       </c>
       <c r="R35" t="n">
-        <v>6792711</v>
+        <v>6792537</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4124,7 +4125,6 @@
       <c r="AE35" t="b">
         <v>0</v>
       </c>
-      <c r="AF35" t="inlineStr"/>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4143,10 +4143,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131153703</v>
+        <v>131153628</v>
       </c>
       <c r="B36" t="n">
-        <v>79250</v>
+        <v>57885</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4154,34 +4154,42 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>433063</v>
+        <v>432884</v>
       </c>
       <c r="R36" t="n">
-        <v>6792351</v>
+        <v>6792734</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4240,7 +4248,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131153702</v>
+        <v>131153703</v>
       </c>
       <c r="B37" t="n">
         <v>79250</v>
@@ -4275,10 +4283,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>433004</v>
+        <v>433063</v>
       </c>
       <c r="R37" t="n">
-        <v>6792374</v>
+        <v>6792351</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4337,7 +4345,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131153698</v>
+        <v>131153702</v>
       </c>
       <c r="B38" t="n">
         <v>79250</v>
@@ -4372,10 +4380,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>432819</v>
+        <v>433004</v>
       </c>
       <c r="R38" t="n">
-        <v>6792432</v>
+        <v>6792374</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4434,7 +4442,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131153714</v>
+        <v>131153698</v>
       </c>
       <c r="B39" t="n">
         <v>79250</v>
@@ -4469,10 +4477,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>432946</v>
+        <v>432819</v>
       </c>
       <c r="R39" t="n">
-        <v>6792696</v>
+        <v>6792432</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4505,11 +4513,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-02-14</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Måttligt med garnlav inom en radie av 50 m</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4536,10 +4539,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131153628</v>
+        <v>131153714</v>
       </c>
       <c r="B40" t="n">
-        <v>57885</v>
+        <v>79250</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4547,42 +4550,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>432884</v>
+        <v>432946</v>
       </c>
       <c r="R40" t="n">
-        <v>6792734</v>
+        <v>6792696</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4615,6 +4610,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Måttligt med garnlav inom en radie av 50 m</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4641,40 +4641,41 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131153640</v>
+        <v>131153660</v>
       </c>
       <c r="B41" t="n">
-        <v>57885</v>
+        <v>8451</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N41" t="inlineStr"/>
@@ -4684,10 +4685,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>432940</v>
+        <v>433068</v>
       </c>
       <c r="R41" t="n">
-        <v>6792843</v>
+        <v>6792415</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4728,6 +4729,7 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
+      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4746,10 +4748,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131153643</v>
+        <v>131153708</v>
       </c>
       <c r="B42" t="n">
-        <v>57885</v>
+        <v>79250</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4757,42 +4759,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>432969</v>
+        <v>433106</v>
       </c>
       <c r="R42" t="n">
-        <v>6792418</v>
+        <v>6792609</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4851,54 +4845,45 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131153660</v>
+        <v>131153710</v>
       </c>
       <c r="B43" t="n">
-        <v>8451</v>
+        <v>79250</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>433068</v>
+        <v>433013</v>
       </c>
       <c r="R43" t="n">
-        <v>6792415</v>
+        <v>6792587</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4939,7 +4924,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -4958,7 +4942,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131153708</v>
+        <v>131153691</v>
       </c>
       <c r="B44" t="n">
         <v>79250</v>
@@ -4993,10 +4977,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>433106</v>
+        <v>432881</v>
       </c>
       <c r="R44" t="n">
-        <v>6792609</v>
+        <v>6792694</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5055,7 +5039,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131153710</v>
+        <v>131153722</v>
       </c>
       <c r="B45" t="n">
         <v>79250</v>
@@ -5090,10 +5074,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>433013</v>
+        <v>432939</v>
       </c>
       <c r="R45" t="n">
-        <v>6792587</v>
+        <v>6792795</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5152,7 +5136,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131153691</v>
+        <v>131153692</v>
       </c>
       <c r="B46" t="n">
         <v>79250</v>
@@ -5187,10 +5171,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>432881</v>
+        <v>432901</v>
       </c>
       <c r="R46" t="n">
-        <v>6792694</v>
+        <v>6792625</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5249,10 +5233,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131153722</v>
+        <v>131153640</v>
       </c>
       <c r="B47" t="n">
-        <v>79250</v>
+        <v>57885</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5260,34 +5244,42 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>432939</v>
+        <v>432940</v>
       </c>
       <c r="R47" t="n">
-        <v>6792795</v>
+        <v>6792843</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5346,10 +5338,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131153692</v>
+        <v>131153643</v>
       </c>
       <c r="B48" t="n">
-        <v>79250</v>
+        <v>57885</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5357,34 +5349,42 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>432901</v>
+        <v>432969</v>
       </c>
       <c r="R48" t="n">
-        <v>6792625</v>
+        <v>6792418</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -7857,41 +7857,40 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131153669</v>
+        <v>131153639</v>
       </c>
       <c r="B73" t="n">
-        <v>8451</v>
+        <v>57885</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
       <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N73" t="inlineStr"/>
@@ -7901,10 +7900,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>432941</v>
+        <v>432988</v>
       </c>
       <c r="R73" t="n">
-        <v>6792778</v>
+        <v>6792798</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7945,7 +7944,6 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
       </c>
@@ -7964,45 +7962,54 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131153711</v>
+        <v>131153669</v>
       </c>
       <c r="B74" t="n">
-        <v>79250</v>
+        <v>8451</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr"/>
+      <c r="L74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>432942</v>
+        <v>432941</v>
       </c>
       <c r="R74" t="n">
-        <v>6792639</v>
+        <v>6792778</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8043,6 +8050,7 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
+      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8061,10 +8069,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131153726</v>
+        <v>131153619</v>
       </c>
       <c r="B75" t="n">
-        <v>79250</v>
+        <v>79840</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8072,21 +8080,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8096,10 +8104,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>432891</v>
+        <v>433004</v>
       </c>
       <c r="R75" t="n">
-        <v>6792834</v>
+        <v>6792784</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8158,7 +8166,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131153721</v>
+        <v>131153711</v>
       </c>
       <c r="B76" t="n">
         <v>79250</v>
@@ -8187,19 +8195,16 @@
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
-      <c r="J76" t="inlineStr"/>
-      <c r="K76" t="inlineStr"/>
-      <c r="N76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>432957</v>
+        <v>432942</v>
       </c>
       <c r="R76" t="n">
-        <v>6792790</v>
+        <v>6792639</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8234,18 +8239,12 @@
           <t>2026-02-14</t>
         </is>
       </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Måttligt med garnlav inom en radie av 50m</t>
-        </is>
-      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
       <c r="AE76" t="b">
         <v>0</v>
       </c>
-      <c r="AF76" t="inlineStr"/>
       <c r="AG76" t="b">
         <v>0</v>
       </c>
@@ -8264,7 +8263,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131153699</v>
+        <v>131153726</v>
       </c>
       <c r="B77" t="n">
         <v>79250</v>
@@ -8299,10 +8298,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>432849</v>
+        <v>432891</v>
       </c>
       <c r="R77" t="n">
-        <v>6792408</v>
+        <v>6792834</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8361,7 +8360,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131153705</v>
+        <v>131153721</v>
       </c>
       <c r="B78" t="n">
         <v>79250</v>
@@ -8390,16 +8389,19 @@
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr"/>
+      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>433133</v>
+        <v>432957</v>
       </c>
       <c r="R78" t="n">
-        <v>6792485</v>
+        <v>6792790</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8434,12 +8436,18 @@
           <t>2026-02-14</t>
         </is>
       </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Måttligt med garnlav inom en radie av 50m</t>
+        </is>
+      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
+      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8458,10 +8466,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131153625</v>
+        <v>131153699</v>
       </c>
       <c r="B79" t="n">
-        <v>91839</v>
+        <v>79250</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8469,37 +8477,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr"/>
-      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>433119</v>
+        <v>432849</v>
       </c>
       <c r="R79" t="n">
-        <v>6792436</v>
+        <v>6792408</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8540,7 +8545,6 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8559,10 +8563,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131153639</v>
+        <v>131153705</v>
       </c>
       <c r="B80" t="n">
-        <v>57885</v>
+        <v>79250</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8570,42 +8574,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>432988</v>
+        <v>433133</v>
       </c>
       <c r="R80" t="n">
-        <v>6792798</v>
+        <v>6792485</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8664,10 +8660,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131153619</v>
+        <v>131153625</v>
       </c>
       <c r="B81" t="n">
-        <v>79840</v>
+        <v>91839</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8675,34 +8671,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>229821</v>
+        <v>5442</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>433004</v>
+        <v>433119</v>
       </c>
       <c r="R81" t="n">
-        <v>6792784</v>
+        <v>6792436</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8743,6 +8742,7 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 1159-2026 artfynd.xlsx
+++ b/artfynd/A 1159-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131153674</v>
       </c>
       <c r="B2" t="n">
-        <v>58260</v>
+        <v>58263</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>131153673</v>
       </c>
       <c r="B3" t="n">
-        <v>8451</v>
+        <v>8453</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -890,7 +890,7 @@
         <v>131153657</v>
       </c>
       <c r="B4" t="n">
-        <v>8451</v>
+        <v>8453</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
         <v>131153661</v>
       </c>
       <c r="B5" t="n">
-        <v>8451</v>
+        <v>8453</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1104,7 +1104,7 @@
         <v>131153677</v>
       </c>
       <c r="B6" t="n">
-        <v>79007</v>
+        <v>79010</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1201,7 +1201,7 @@
         <v>131153725</v>
       </c>
       <c r="B7" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>131153667</v>
       </c>
       <c r="B8" t="n">
-        <v>8451</v>
+        <v>8453</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1402,10 +1402,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131153689</v>
+        <v>131153632</v>
       </c>
       <c r="B9" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1413,34 +1413,42 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>432855</v>
+        <v>433068</v>
       </c>
       <c r="R9" t="n">
-        <v>6792784</v>
+        <v>6792622</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1499,40 +1507,41 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131153632</v>
+        <v>131153656</v>
       </c>
       <c r="B10" t="n">
-        <v>57885</v>
+        <v>8453</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1542,10 +1551,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>433068</v>
+        <v>432815</v>
       </c>
       <c r="R10" t="n">
-        <v>6792622</v>
+        <v>6792564</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1586,6 +1595,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1607,7 +1617,7 @@
         <v>131153663</v>
       </c>
       <c r="B11" t="n">
-        <v>8451</v>
+        <v>8453</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1711,54 +1721,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131153656</v>
+        <v>131153689</v>
       </c>
       <c r="B12" t="n">
-        <v>8451</v>
+        <v>79253</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>432815</v>
+        <v>432855</v>
       </c>
       <c r="R12" t="n">
-        <v>6792564</v>
+        <v>6792784</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1799,7 +1800,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1818,10 +1818,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131153676</v>
+        <v>131153720</v>
       </c>
       <c r="B13" t="n">
-        <v>79007</v>
+        <v>79253</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1829,21 +1829,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1853,10 +1853,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>432719</v>
+        <v>432962</v>
       </c>
       <c r="R13" t="n">
-        <v>6792423</v>
+        <v>6792773</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1918,7 +1918,7 @@
         <v>131153712</v>
       </c>
       <c r="B14" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2012,10 +2012,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131153720</v>
+        <v>131153676</v>
       </c>
       <c r="B15" t="n">
-        <v>79250</v>
+        <v>79010</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2023,21 +2023,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2047,10 +2047,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>432962</v>
+        <v>432719</v>
       </c>
       <c r="R15" t="n">
-        <v>6792773</v>
+        <v>6792423</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2112,7 +2112,7 @@
         <v>131153621</v>
       </c>
       <c r="B16" t="n">
-        <v>79840</v>
+        <v>79843</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2209,7 +2209,7 @@
         <v>131153706</v>
       </c>
       <c r="B17" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2307,45 +2307,54 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131153695</v>
+        <v>131153645</v>
       </c>
       <c r="B18" t="n">
-        <v>79250</v>
+        <v>5480</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>101920</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>432708</v>
+        <v>432996</v>
       </c>
       <c r="R18" t="n">
-        <v>6792430</v>
+        <v>6792672</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2384,8 +2393,9 @@
         <v>0</v>
       </c>
       <c r="AE18" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2404,54 +2414,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131153645</v>
+        <v>131153695</v>
       </c>
       <c r="B19" t="n">
-        <v>5480</v>
+        <v>79253</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>101920</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>432996</v>
+        <v>432708</v>
       </c>
       <c r="R19" t="n">
-        <v>6792672</v>
+        <v>6792430</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2490,9 +2491,8 @@
         <v>0</v>
       </c>
       <c r="AE19" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF19" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2514,7 +2514,7 @@
         <v>131153635</v>
       </c>
       <c r="B20" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2619,7 +2619,7 @@
         <v>131153668</v>
       </c>
       <c r="B21" t="n">
-        <v>8451</v>
+        <v>8453</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2723,10 +2723,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>131153622</v>
+        <v>131153719</v>
       </c>
       <c r="B22" t="n">
-        <v>57888</v>
+        <v>79253</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2734,31 +2734,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2766,10 +2761,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>432996</v>
+        <v>432964</v>
       </c>
       <c r="R22" t="n">
-        <v>6792778</v>
+        <v>6792760</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2810,6 +2805,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2828,10 +2824,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131153719</v>
+        <v>131153729</v>
       </c>
       <c r="B23" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2857,19 +2853,16 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>432964</v>
+        <v>432924</v>
       </c>
       <c r="R23" t="n">
-        <v>6792760</v>
+        <v>6792835</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2910,7 +2903,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -2929,10 +2921,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131153729</v>
+        <v>131153622</v>
       </c>
       <c r="B24" t="n">
-        <v>79250</v>
+        <v>57891</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2940,34 +2932,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>432924</v>
+        <v>432996</v>
       </c>
       <c r="R24" t="n">
-        <v>6792835</v>
+        <v>6792778</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3029,7 +3029,7 @@
         <v>131153718</v>
       </c>
       <c r="B25" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3126,7 +3126,7 @@
         <v>131153672</v>
       </c>
       <c r="B26" t="n">
-        <v>8451</v>
+        <v>8453</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3233,7 +3233,7 @@
         <v>131153701</v>
       </c>
       <c r="B27" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3330,7 +3330,7 @@
         <v>131153650</v>
       </c>
       <c r="B28" t="n">
-        <v>79008</v>
+        <v>79011</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3424,10 +3424,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131153716</v>
+        <v>131153690</v>
       </c>
       <c r="B29" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3453,16 +3453,19 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>432960</v>
+        <v>432874</v>
       </c>
       <c r="R29" t="n">
-        <v>6792712</v>
+        <v>6792733</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3503,6 +3506,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3521,10 +3525,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131153690</v>
+        <v>131153716</v>
       </c>
       <c r="B30" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3550,19 +3554,16 @@
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>432874</v>
+        <v>432960</v>
       </c>
       <c r="R30" t="n">
-        <v>6792733</v>
+        <v>6792712</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3603,7 +3604,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3622,41 +3622,40 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131153658</v>
+        <v>131153630</v>
       </c>
       <c r="B31" t="n">
-        <v>8451</v>
+        <v>57888</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3666,10 +3665,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>433053</v>
+        <v>433062</v>
       </c>
       <c r="R31" t="n">
-        <v>6792381</v>
+        <v>6792357</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3710,7 +3709,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3729,41 +3727,40 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131153665</v>
+        <v>131153641</v>
       </c>
       <c r="B32" t="n">
-        <v>8451</v>
+        <v>57888</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3773,10 +3770,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>432959</v>
+        <v>432909</v>
       </c>
       <c r="R32" t="n">
-        <v>6792711</v>
+        <v>6792876</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3817,7 +3814,6 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3836,40 +3832,41 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131153641</v>
+        <v>131153658</v>
       </c>
       <c r="B33" t="n">
-        <v>57885</v>
+        <v>8453</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -3879,10 +3876,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>432909</v>
+        <v>433053</v>
       </c>
       <c r="R33" t="n">
-        <v>6792876</v>
+        <v>6792381</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3923,6 +3920,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3941,40 +3939,41 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131153630</v>
+        <v>131153665</v>
       </c>
       <c r="B34" t="n">
-        <v>57885</v>
+        <v>8453</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -3984,10 +3983,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>433062</v>
+        <v>432959</v>
       </c>
       <c r="R34" t="n">
-        <v>6792357</v>
+        <v>6792711</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4028,6 +4027,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4049,7 +4049,7 @@
         <v>131153616</v>
       </c>
       <c r="B35" t="n">
-        <v>79840</v>
+        <v>79843</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4143,10 +4143,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131153628</v>
+        <v>131153703</v>
       </c>
       <c r="B36" t="n">
-        <v>57885</v>
+        <v>79253</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4154,42 +4154,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>432884</v>
+        <v>433063</v>
       </c>
       <c r="R36" t="n">
-        <v>6792734</v>
+        <v>6792351</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4248,10 +4240,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131153703</v>
+        <v>131153702</v>
       </c>
       <c r="B37" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4283,10 +4275,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>433063</v>
+        <v>433004</v>
       </c>
       <c r="R37" t="n">
-        <v>6792351</v>
+        <v>6792374</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4345,10 +4337,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131153702</v>
+        <v>131153714</v>
       </c>
       <c r="B38" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4380,10 +4372,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>433004</v>
+        <v>432946</v>
       </c>
       <c r="R38" t="n">
-        <v>6792374</v>
+        <v>6792696</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4416,6 +4408,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Måttligt med garnlav inom en radie av 50 m</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4445,7 +4442,7 @@
         <v>131153698</v>
       </c>
       <c r="B39" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4539,10 +4536,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131153714</v>
+        <v>131153628</v>
       </c>
       <c r="B40" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4550,34 +4547,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>432946</v>
+        <v>432884</v>
       </c>
       <c r="R40" t="n">
-        <v>6792696</v>
+        <v>6792734</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4610,11 +4615,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2026-02-14</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Måttligt med garnlav inom en radie av 50 m</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4641,54 +4641,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131153660</v>
+        <v>131153710</v>
       </c>
       <c r="B41" t="n">
-        <v>8451</v>
+        <v>79253</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>433068</v>
+        <v>433013</v>
       </c>
       <c r="R41" t="n">
-        <v>6792415</v>
+        <v>6792587</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4729,7 +4720,6 @@
       <c r="AE41" t="b">
         <v>0</v>
       </c>
-      <c r="AF41" t="inlineStr"/>
       <c r="AG41" t="b">
         <v>0</v>
       </c>
@@ -4748,10 +4738,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131153708</v>
+        <v>131153691</v>
       </c>
       <c r="B42" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4783,10 +4773,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>433106</v>
+        <v>432881</v>
       </c>
       <c r="R42" t="n">
-        <v>6792609</v>
+        <v>6792694</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4845,10 +4835,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131153710</v>
+        <v>131153708</v>
       </c>
       <c r="B43" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4880,10 +4870,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>433013</v>
+        <v>433106</v>
       </c>
       <c r="R43" t="n">
-        <v>6792587</v>
+        <v>6792609</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4942,10 +4932,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131153691</v>
+        <v>131153722</v>
       </c>
       <c r="B44" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4977,10 +4967,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>432881</v>
+        <v>432939</v>
       </c>
       <c r="R44" t="n">
-        <v>6792694</v>
+        <v>6792795</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5039,10 +5029,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131153722</v>
+        <v>131153692</v>
       </c>
       <c r="B45" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5074,10 +5064,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>432939</v>
+        <v>432901</v>
       </c>
       <c r="R45" t="n">
-        <v>6792795</v>
+        <v>6792625</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5136,45 +5126,54 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131153692</v>
+        <v>131153660</v>
       </c>
       <c r="B46" t="n">
-        <v>79250</v>
+        <v>8453</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>432901</v>
+        <v>433068</v>
       </c>
       <c r="R46" t="n">
-        <v>6792625</v>
+        <v>6792415</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5215,6 +5214,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5233,10 +5233,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131153640</v>
+        <v>131153643</v>
       </c>
       <c r="B47" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5276,10 +5276,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>432940</v>
+        <v>432969</v>
       </c>
       <c r="R47" t="n">
-        <v>6792843</v>
+        <v>6792418</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5338,10 +5338,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131153643</v>
+        <v>131153640</v>
       </c>
       <c r="B48" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5381,10 +5381,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>432969</v>
+        <v>432940</v>
       </c>
       <c r="R48" t="n">
-        <v>6792418</v>
+        <v>6792843</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5446,7 +5446,7 @@
         <v>131153662</v>
       </c>
       <c r="B49" t="n">
-        <v>8451</v>
+        <v>8453</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5550,10 +5550,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131153631</v>
+        <v>131153700</v>
       </c>
       <c r="B50" t="n">
-        <v>57885</v>
+        <v>79253</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5561,42 +5561,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>433074</v>
+        <v>432910</v>
       </c>
       <c r="R50" t="n">
-        <v>6792635</v>
+        <v>6792364</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5655,10 +5647,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131153651</v>
+        <v>131153713</v>
       </c>
       <c r="B51" t="n">
-        <v>79008</v>
+        <v>79253</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5666,37 +5658,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>433104</v>
+        <v>432988</v>
       </c>
       <c r="R51" t="n">
-        <v>6792573</v>
+        <v>6792669</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5737,7 +5726,6 @@
       <c r="AE51" t="b">
         <v>0</v>
       </c>
-      <c r="AF51" t="inlineStr"/>
       <c r="AG51" t="b">
         <v>0</v>
       </c>
@@ -5756,10 +5744,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131153653</v>
+        <v>131153709</v>
       </c>
       <c r="B52" t="n">
-        <v>79008</v>
+        <v>79253</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5767,37 +5755,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>432956</v>
+        <v>433034</v>
       </c>
       <c r="R52" t="n">
-        <v>6792683</v>
+        <v>6792553</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5838,7 +5823,6 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
-      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
@@ -5857,10 +5841,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131153709</v>
+        <v>131153631</v>
       </c>
       <c r="B53" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5868,34 +5852,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>433034</v>
+        <v>433074</v>
       </c>
       <c r="R53" t="n">
-        <v>6792553</v>
+        <v>6792635</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5954,10 +5946,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131153700</v>
+        <v>131153653</v>
       </c>
       <c r="B54" t="n">
-        <v>79250</v>
+        <v>79011</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5965,34 +5957,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>432910</v>
+        <v>432956</v>
       </c>
       <c r="R54" t="n">
-        <v>6792364</v>
+        <v>6792683</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6033,6 +6028,7 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6051,10 +6047,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131153713</v>
+        <v>131153651</v>
       </c>
       <c r="B55" t="n">
-        <v>79250</v>
+        <v>79011</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6062,34 +6058,37 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>432988</v>
+        <v>433104</v>
       </c>
       <c r="R55" t="n">
-        <v>6792669</v>
+        <v>6792573</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6130,6 +6129,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6148,10 +6148,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131153618</v>
+        <v>131153696</v>
       </c>
       <c r="B56" t="n">
-        <v>79840</v>
+        <v>79253</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6159,21 +6159,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6183,10 +6183,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>433073</v>
+        <v>432758</v>
       </c>
       <c r="R56" t="n">
-        <v>6792637</v>
+        <v>6792450</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6245,10 +6245,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131153649</v>
+        <v>131153707</v>
       </c>
       <c r="B57" t="n">
-        <v>79008</v>
+        <v>79253</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6256,21 +6256,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6280,10 +6280,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>432719</v>
+        <v>433128</v>
       </c>
       <c r="R57" t="n">
-        <v>6792423</v>
+        <v>6792592</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6342,10 +6342,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>131153696</v>
+        <v>131153697</v>
       </c>
       <c r="B58" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6377,10 +6377,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>432758</v>
+        <v>432785</v>
       </c>
       <c r="R58" t="n">
-        <v>6792450</v>
+        <v>6792460</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6439,10 +6439,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>131153707</v>
+        <v>131153704</v>
       </c>
       <c r="B59" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6474,10 +6474,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>433128</v>
+        <v>433115</v>
       </c>
       <c r="R59" t="n">
-        <v>6792592</v>
+        <v>6792436</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6536,10 +6536,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131153697</v>
+        <v>131153638</v>
       </c>
       <c r="B60" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6547,34 +6547,42 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>432785</v>
+        <v>432927</v>
       </c>
       <c r="R60" t="n">
-        <v>6792460</v>
+        <v>6792752</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6633,10 +6641,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131153704</v>
+        <v>131153618</v>
       </c>
       <c r="B61" t="n">
-        <v>79250</v>
+        <v>79843</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6644,21 +6652,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6668,10 +6676,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>433115</v>
+        <v>433073</v>
       </c>
       <c r="R61" t="n">
-        <v>6792436</v>
+        <v>6792637</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6730,10 +6738,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131153638</v>
+        <v>131153649</v>
       </c>
       <c r="B62" t="n">
-        <v>57885</v>
+        <v>79011</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6741,42 +6749,34 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>432927</v>
+        <v>432719</v>
       </c>
       <c r="R62" t="n">
-        <v>6792752</v>
+        <v>6792423</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6838,7 +6838,7 @@
         <v>131153693</v>
       </c>
       <c r="B63" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6935,7 +6935,7 @@
         <v>131153727</v>
       </c>
       <c r="B64" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7036,7 +7036,7 @@
         <v>131153633</v>
       </c>
       <c r="B65" t="n">
-        <v>57885</v>
+        <v>57888</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         <v>131153654</v>
       </c>
       <c r="B66" t="n">
-        <v>8451</v>
+        <v>8453</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7245,10 +7245,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131153694</v>
+        <v>131153636</v>
       </c>
       <c r="B67" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7256,34 +7256,42 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>432842</v>
+        <v>432931</v>
       </c>
       <c r="R67" t="n">
-        <v>6792572</v>
+        <v>6792717</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7342,10 +7350,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131153679</v>
+        <v>131153634</v>
       </c>
       <c r="B68" t="n">
-        <v>79007</v>
+        <v>57888</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7353,34 +7361,42 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>432956</v>
+        <v>432989</v>
       </c>
       <c r="R68" t="n">
-        <v>6792683</v>
+        <v>6792671</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7439,54 +7455,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131153655</v>
+        <v>131153679</v>
       </c>
       <c r="B69" t="n">
-        <v>8451</v>
+        <v>79010</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
-      <c r="K69" t="inlineStr"/>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>432876</v>
+        <v>432956</v>
       </c>
       <c r="R69" t="n">
-        <v>6792590</v>
+        <v>6792683</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7527,7 +7534,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7546,10 +7552,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131153636</v>
+        <v>131153620</v>
       </c>
       <c r="B70" t="n">
-        <v>57885</v>
+        <v>79843</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7557,31 +7563,26 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -7589,10 +7590,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>432931</v>
+        <v>433058</v>
       </c>
       <c r="R70" t="n">
-        <v>6792717</v>
+        <v>6792468</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7633,6 +7634,7 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
+      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7651,10 +7653,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131153634</v>
+        <v>131153694</v>
       </c>
       <c r="B71" t="n">
-        <v>57885</v>
+        <v>79253</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7662,42 +7664,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>432989</v>
+        <v>432842</v>
       </c>
       <c r="R71" t="n">
-        <v>6792671</v>
+        <v>6792572</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7756,37 +7750,43 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131153620</v>
+        <v>131153655</v>
       </c>
       <c r="B72" t="n">
-        <v>79840</v>
+        <v>8453</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
       <c r="K72" t="inlineStr"/>
+      <c r="L72" t="inlineStr"/>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
@@ -7794,10 +7794,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>433058</v>
+        <v>432876</v>
       </c>
       <c r="R72" t="n">
-        <v>6792468</v>
+        <v>6792590</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7857,10 +7857,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131153639</v>
+        <v>131153619</v>
       </c>
       <c r="B73" t="n">
-        <v>57885</v>
+        <v>79843</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7868,42 +7868,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>432988</v>
+        <v>433004</v>
       </c>
       <c r="R73" t="n">
-        <v>6792798</v>
+        <v>6792784</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7962,54 +7954,45 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131153669</v>
+        <v>131153726</v>
       </c>
       <c r="B74" t="n">
-        <v>8451</v>
+        <v>79253</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>432941</v>
+        <v>432891</v>
       </c>
       <c r="R74" t="n">
-        <v>6792778</v>
+        <v>6792834</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8050,7 +8033,6 @@
       <c r="AE74" t="b">
         <v>0</v>
       </c>
-      <c r="AF74" t="inlineStr"/>
       <c r="AG74" t="b">
         <v>0</v>
       </c>
@@ -8069,10 +8051,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131153619</v>
+        <v>131153721</v>
       </c>
       <c r="B75" t="n">
-        <v>79840</v>
+        <v>79253</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8080,34 +8062,37 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr"/>
+      <c r="N75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>433004</v>
+        <v>432957</v>
       </c>
       <c r="R75" t="n">
-        <v>6792784</v>
+        <v>6792790</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8142,12 +8127,18 @@
           <t>2026-02-14</t>
         </is>
       </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Måttligt med garnlav inom en radie av 50m</t>
+        </is>
+      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
       <c r="AE75" t="b">
         <v>0</v>
       </c>
+      <c r="AF75" t="inlineStr"/>
       <c r="AG75" t="b">
         <v>0</v>
       </c>
@@ -8166,10 +8157,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131153711</v>
+        <v>131153705</v>
       </c>
       <c r="B76" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8201,10 +8192,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>432942</v>
+        <v>433133</v>
       </c>
       <c r="R76" t="n">
-        <v>6792639</v>
+        <v>6792485</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8263,10 +8254,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131153726</v>
+        <v>131153711</v>
       </c>
       <c r="B77" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8298,10 +8289,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>432891</v>
+        <v>432942</v>
       </c>
       <c r="R77" t="n">
-        <v>6792834</v>
+        <v>6792639</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8360,10 +8351,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131153721</v>
+        <v>131153699</v>
       </c>
       <c r="B78" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8389,19 +8380,16 @@
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
-      <c r="N78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>432957</v>
+        <v>432849</v>
       </c>
       <c r="R78" t="n">
-        <v>6792790</v>
+        <v>6792408</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8436,18 +8424,12 @@
           <t>2026-02-14</t>
         </is>
       </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Måttligt med garnlav inom en radie av 50m</t>
-        </is>
-      </c>
       <c r="AD78" t="b">
         <v>0</v>
       </c>
       <c r="AE78" t="b">
         <v>0</v>
       </c>
-      <c r="AF78" t="inlineStr"/>
       <c r="AG78" t="b">
         <v>0</v>
       </c>
@@ -8466,10 +8448,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131153699</v>
+        <v>131153625</v>
       </c>
       <c r="B79" t="n">
-        <v>79250</v>
+        <v>91842</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8477,34 +8459,37 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr"/>
+      <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>432849</v>
+        <v>433119</v>
       </c>
       <c r="R79" t="n">
-        <v>6792408</v>
+        <v>6792436</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8545,6 +8530,7 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
+      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8563,10 +8549,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131153705</v>
+        <v>131153639</v>
       </c>
       <c r="B80" t="n">
-        <v>79250</v>
+        <v>57888</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8574,34 +8560,42 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="K80" t="inlineStr"/>
+      <c r="L80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>433133</v>
+        <v>432988</v>
       </c>
       <c r="R80" t="n">
-        <v>6792485</v>
+        <v>6792798</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8660,37 +8654,43 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131153625</v>
+        <v>131153669</v>
       </c>
       <c r="B81" t="n">
-        <v>91839</v>
+        <v>8453</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5442</v>
+        <v>106545</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -8698,10 +8698,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>433119</v>
+        <v>432941</v>
       </c>
       <c r="R81" t="n">
-        <v>6792436</v>
+        <v>6792778</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8764,7 +8764,7 @@
         <v>131153728</v>
       </c>
       <c r="B82" t="n">
-        <v>79250</v>
+        <v>79253</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8861,7 +8861,7 @@
         <v>131153624</v>
       </c>
       <c r="B83" t="n">
-        <v>91839</v>
+        <v>91842</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8962,7 +8962,7 @@
         <v>131153659</v>
       </c>
       <c r="B84" t="n">
-        <v>8451</v>
+        <v>8453</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9066,54 +9066,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131153664</v>
+        <v>131153617</v>
       </c>
       <c r="B85" t="n">
-        <v>8451</v>
+        <v>79843</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>433001</v>
+        <v>432828</v>
       </c>
       <c r="R85" t="n">
-        <v>6792569</v>
+        <v>6792424</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9154,7 +9145,6 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -9176,7 +9166,7 @@
         <v>131153666</v>
       </c>
       <c r="B86" t="n">
-        <v>8451</v>
+        <v>8453</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9280,45 +9270,54 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131153617</v>
+        <v>131153664</v>
       </c>
       <c r="B87" t="n">
-        <v>79840</v>
+        <v>8453</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>432828</v>
+        <v>433001</v>
       </c>
       <c r="R87" t="n">
-        <v>6792424</v>
+        <v>6792569</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9359,6 +9358,7 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9377,10 +9377,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131153652</v>
+        <v>131153642</v>
       </c>
       <c r="B88" t="n">
-        <v>79008</v>
+        <v>57888</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9388,34 +9388,42 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>433073</v>
+        <v>432888</v>
       </c>
       <c r="R88" t="n">
-        <v>6792637</v>
+        <v>6792650</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9474,10 +9482,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131153717</v>
+        <v>131153652</v>
       </c>
       <c r="B89" t="n">
-        <v>79250</v>
+        <v>79011</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9485,21 +9493,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9509,10 +9517,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>432932</v>
+        <v>433073</v>
       </c>
       <c r="R89" t="n">
-        <v>6792709</v>
+        <v>6792637</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9571,10 +9579,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131153678</v>
+        <v>131153717</v>
       </c>
       <c r="B90" t="n">
-        <v>79007</v>
+        <v>79253</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9582,21 +9590,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9606,10 +9614,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>433104</v>
+        <v>432932</v>
       </c>
       <c r="R90" t="n">
-        <v>6792573</v>
+        <v>6792709</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9668,10 +9676,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131153642</v>
+        <v>131153678</v>
       </c>
       <c r="B91" t="n">
-        <v>57885</v>
+        <v>79010</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9679,42 +9687,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="K91" t="inlineStr"/>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>432888</v>
+        <v>433104</v>
       </c>
       <c r="R91" t="n">
-        <v>6792650</v>
+        <v>6792573</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9776,7 +9776,7 @@
         <v>131153681</v>
       </c>
       <c r="B92" t="n">
-        <v>57888</v>
+        <v>57891</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 1159-2026 artfynd.xlsx
+++ b/artfynd/A 1159-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>131153674</v>
       </c>
       <c r="B2" t="n">
-        <v>58263</v>
+        <v>58264</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1101,10 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>131153677</v>
+        <v>131153725</v>
       </c>
       <c r="B6" t="n">
-        <v>79010</v>
+        <v>79254</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1112,21 +1112,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1136,10 +1136,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>433058</v>
+        <v>432886</v>
       </c>
       <c r="R6" t="n">
-        <v>6792459</v>
+        <v>6792852</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,10 +1198,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>131153725</v>
+        <v>131153677</v>
       </c>
       <c r="B7" t="n">
-        <v>79253</v>
+        <v>79011</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1209,21 +1209,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1233,10 +1233,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>432886</v>
+        <v>433058</v>
       </c>
       <c r="R7" t="n">
-        <v>6792852</v>
+        <v>6792459</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1402,10 +1402,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>131153632</v>
+        <v>131153689</v>
       </c>
       <c r="B9" t="n">
-        <v>57888</v>
+        <v>79254</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1413,42 +1413,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>433068</v>
+        <v>432855</v>
       </c>
       <c r="R9" t="n">
-        <v>6792622</v>
+        <v>6792784</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1507,41 +1499,40 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>131153656</v>
+        <v>131153632</v>
       </c>
       <c r="B10" t="n">
-        <v>8453</v>
+        <v>57889</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N10" t="inlineStr"/>
@@ -1551,10 +1542,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>432815</v>
+        <v>433068</v>
       </c>
       <c r="R10" t="n">
-        <v>6792564</v>
+        <v>6792622</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1595,7 +1586,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1721,45 +1711,54 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>131153689</v>
+        <v>131153656</v>
       </c>
       <c r="B12" t="n">
-        <v>79253</v>
+        <v>8453</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>432855</v>
+        <v>432815</v>
       </c>
       <c r="R12" t="n">
-        <v>6792784</v>
+        <v>6792564</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1800,6 +1799,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1818,10 +1818,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131153720</v>
+        <v>131153621</v>
       </c>
       <c r="B13" t="n">
-        <v>79253</v>
+        <v>79844</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1829,21 +1829,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1853,10 +1853,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>432962</v>
+        <v>433070</v>
       </c>
       <c r="R13" t="n">
-        <v>6792773</v>
+        <v>6792624</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1918,7 +1918,7 @@
         <v>131153712</v>
       </c>
       <c r="B14" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2012,10 +2012,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>131153676</v>
+        <v>131153720</v>
       </c>
       <c r="B15" t="n">
-        <v>79010</v>
+        <v>79254</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2023,21 +2023,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2047,10 +2047,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>432719</v>
+        <v>432962</v>
       </c>
       <c r="R15" t="n">
-        <v>6792423</v>
+        <v>6792773</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2109,10 +2109,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>131153621</v>
+        <v>131153676</v>
       </c>
       <c r="B16" t="n">
-        <v>79843</v>
+        <v>79011</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2120,21 +2120,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2144,10 +2144,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>433070</v>
+        <v>432719</v>
       </c>
       <c r="R16" t="n">
-        <v>6792624</v>
+        <v>6792423</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2209,7 +2209,7 @@
         <v>131153706</v>
       </c>
       <c r="B17" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2307,54 +2307,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>131153645</v>
+        <v>131153695</v>
       </c>
       <c r="B18" t="n">
-        <v>5480</v>
+        <v>79254</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>101920</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Raggbock</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tragosoma depsarium</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1767)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>432996</v>
+        <v>432708</v>
       </c>
       <c r="R18" t="n">
-        <v>6792672</v>
+        <v>6792430</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2393,9 +2384,8 @@
         <v>0</v>
       </c>
       <c r="AE18" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF18" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2414,10 +2404,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>131153695</v>
+        <v>131153635</v>
       </c>
       <c r="B19" t="n">
-        <v>79253</v>
+        <v>57889</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2425,34 +2415,42 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>432708</v>
+        <v>432968</v>
       </c>
       <c r="R19" t="n">
-        <v>6792430</v>
+        <v>6792680</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2511,40 +2509,41 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>131153635</v>
+        <v>131153668</v>
       </c>
       <c r="B20" t="n">
-        <v>57888</v>
+        <v>8453</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2554,10 +2553,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>432968</v>
+        <v>432974</v>
       </c>
       <c r="R20" t="n">
-        <v>6792680</v>
+        <v>6792777</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2598,6 +2597,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2616,32 +2616,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>131153668</v>
+        <v>131153645</v>
       </c>
       <c r="B21" t="n">
-        <v>8453</v>
+        <v>5480</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106545</v>
+        <v>101920</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Raggbock</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tragosoma depsarium</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1767)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2660,10 +2660,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>432974</v>
+        <v>432996</v>
       </c>
       <c r="R21" t="n">
-        <v>6792777</v>
+        <v>6792672</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2702,7 +2702,7 @@
         <v>0</v>
       </c>
       <c r="AE21" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
@@ -2726,7 +2726,7 @@
         <v>131153719</v>
       </c>
       <c r="B22" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2827,7 +2827,7 @@
         <v>131153729</v>
       </c>
       <c r="B23" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2924,7 +2924,7 @@
         <v>131153622</v>
       </c>
       <c r="B24" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3026,45 +3026,54 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131153718</v>
+        <v>131153672</v>
       </c>
       <c r="B25" t="n">
-        <v>79253</v>
+        <v>8453</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>432974</v>
+        <v>432901</v>
       </c>
       <c r="R25" t="n">
-        <v>6792746</v>
+        <v>6792829</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3105,6 +3114,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3123,54 +3133,45 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131153672</v>
+        <v>131153718</v>
       </c>
       <c r="B26" t="n">
-        <v>8453</v>
+        <v>79254</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>432901</v>
+        <v>432974</v>
       </c>
       <c r="R26" t="n">
-        <v>6792829</v>
+        <v>6792746</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3211,7 +3212,6 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3233,7 +3233,7 @@
         <v>131153701</v>
       </c>
       <c r="B27" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3330,7 +3330,7 @@
         <v>131153650</v>
       </c>
       <c r="B28" t="n">
-        <v>79011</v>
+        <v>79012</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3424,10 +3424,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131153690</v>
+        <v>131153630</v>
       </c>
       <c r="B29" t="n">
-        <v>79253</v>
+        <v>57889</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3435,26 +3435,31 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3462,10 +3467,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>432874</v>
+        <v>433062</v>
       </c>
       <c r="R29" t="n">
-        <v>6792733</v>
+        <v>6792357</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3506,7 +3511,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3525,45 +3529,54 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131153716</v>
+        <v>131153658</v>
       </c>
       <c r="B30" t="n">
-        <v>79253</v>
+        <v>8453</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>432960</v>
+        <v>433053</v>
       </c>
       <c r="R30" t="n">
-        <v>6792712</v>
+        <v>6792381</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3604,6 +3617,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3622,40 +3636,41 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131153630</v>
+        <v>131153665</v>
       </c>
       <c r="B31" t="n">
-        <v>57888</v>
+        <v>8453</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre gnagspår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3665,10 +3680,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>433062</v>
+        <v>432959</v>
       </c>
       <c r="R31" t="n">
-        <v>6792357</v>
+        <v>6792711</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3709,6 +3724,7 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -3727,10 +3743,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131153641</v>
+        <v>131153616</v>
       </c>
       <c r="B32" t="n">
-        <v>57888</v>
+        <v>79844</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3738,42 +3754,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100049</v>
+        <v>229821</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>432909</v>
+        <v>432773</v>
       </c>
       <c r="R32" t="n">
-        <v>6792876</v>
+        <v>6792537</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3832,43 +3840,37 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131153658</v>
+        <v>131153690</v>
       </c>
       <c r="B33" t="n">
-        <v>8453</v>
+        <v>79254</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -3876,10 +3878,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>433053</v>
+        <v>432874</v>
       </c>
       <c r="R33" t="n">
-        <v>6792381</v>
+        <v>6792733</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3939,54 +3941,45 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131153665</v>
+        <v>131153716</v>
       </c>
       <c r="B34" t="n">
-        <v>8453</v>
+        <v>79254</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>432959</v>
+        <v>432960</v>
       </c>
       <c r="R34" t="n">
-        <v>6792711</v>
+        <v>6792712</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4027,7 +4020,6 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4046,10 +4038,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131153616</v>
+        <v>131153641</v>
       </c>
       <c r="B35" t="n">
-        <v>79843</v>
+        <v>57889</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4057,34 +4049,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>432773</v>
+        <v>432909</v>
       </c>
       <c r="R35" t="n">
-        <v>6792537</v>
+        <v>6792876</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4146,7 +4146,7 @@
         <v>131153703</v>
       </c>
       <c r="B36" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4243,7 +4243,7 @@
         <v>131153702</v>
       </c>
       <c r="B37" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4337,10 +4337,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131153714</v>
+        <v>131153698</v>
       </c>
       <c r="B38" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4372,10 +4372,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>432946</v>
+        <v>432819</v>
       </c>
       <c r="R38" t="n">
-        <v>6792696</v>
+        <v>6792432</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4408,11 +4408,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2026-02-14</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Måttligt med garnlav inom en radie av 50 m</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4439,10 +4434,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131153698</v>
+        <v>131153714</v>
       </c>
       <c r="B39" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4474,10 +4469,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>432819</v>
+        <v>432946</v>
       </c>
       <c r="R39" t="n">
-        <v>6792432</v>
+        <v>6792696</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4510,6 +4505,11 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Måttligt med garnlav inom en radie av 50 m</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4539,7 +4539,7 @@
         <v>131153628</v>
       </c>
       <c r="B40" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4641,10 +4641,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131153710</v>
+        <v>131153708</v>
       </c>
       <c r="B41" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4676,10 +4676,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>433013</v>
+        <v>433106</v>
       </c>
       <c r="R41" t="n">
-        <v>6792587</v>
+        <v>6792609</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4738,10 +4738,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131153691</v>
+        <v>131153722</v>
       </c>
       <c r="B42" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4773,10 +4773,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>432881</v>
+        <v>432939</v>
       </c>
       <c r="R42" t="n">
-        <v>6792694</v>
+        <v>6792795</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4835,10 +4835,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131153708</v>
+        <v>131153692</v>
       </c>
       <c r="B43" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4870,10 +4870,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>433106</v>
+        <v>432901</v>
       </c>
       <c r="R43" t="n">
-        <v>6792609</v>
+        <v>6792625</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4932,10 +4932,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131153722</v>
+        <v>131153710</v>
       </c>
       <c r="B44" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4967,10 +4967,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>432939</v>
+        <v>433013</v>
       </c>
       <c r="R44" t="n">
-        <v>6792795</v>
+        <v>6792587</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5029,10 +5029,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131153692</v>
+        <v>131153691</v>
       </c>
       <c r="B45" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5064,10 +5064,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>432901</v>
+        <v>432881</v>
       </c>
       <c r="R45" t="n">
-        <v>6792625</v>
+        <v>6792694</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5126,41 +5126,40 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131153660</v>
+        <v>131153643</v>
       </c>
       <c r="B46" t="n">
-        <v>8453</v>
+        <v>57889</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N46" t="inlineStr"/>
@@ -5170,10 +5169,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>433068</v>
+        <v>432969</v>
       </c>
       <c r="R46" t="n">
-        <v>6792415</v>
+        <v>6792418</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5214,7 +5213,6 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
-      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -5233,10 +5231,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131153643</v>
+        <v>131153640</v>
       </c>
       <c r="B47" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5276,10 +5274,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>432969</v>
+        <v>432940</v>
       </c>
       <c r="R47" t="n">
-        <v>6792418</v>
+        <v>6792843</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5338,40 +5336,41 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131153640</v>
+        <v>131153660</v>
       </c>
       <c r="B48" t="n">
-        <v>57888</v>
+        <v>8453</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr"/>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -5381,10 +5380,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>432940</v>
+        <v>433068</v>
       </c>
       <c r="R48" t="n">
-        <v>6792843</v>
+        <v>6792415</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5425,6 +5424,7 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
+      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5553,7 +5553,7 @@
         <v>131153700</v>
       </c>
       <c r="B50" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5650,7 +5650,7 @@
         <v>131153713</v>
       </c>
       <c r="B51" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5744,10 +5744,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131153709</v>
+        <v>131153631</v>
       </c>
       <c r="B52" t="n">
-        <v>79253</v>
+        <v>57889</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5755,34 +5755,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>433034</v>
+        <v>433074</v>
       </c>
       <c r="R52" t="n">
-        <v>6792553</v>
+        <v>6792635</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5841,10 +5849,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131153631</v>
+        <v>131153651</v>
       </c>
       <c r="B53" t="n">
-        <v>57888</v>
+        <v>79012</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5852,31 +5860,26 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
@@ -5884,10 +5887,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>433074</v>
+        <v>433104</v>
       </c>
       <c r="R53" t="n">
-        <v>6792635</v>
+        <v>6792573</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5928,6 +5931,7 @@
       <c r="AE53" t="b">
         <v>0</v>
       </c>
+      <c r="AF53" t="inlineStr"/>
       <c r="AG53" t="b">
         <v>0</v>
       </c>
@@ -5949,7 +5953,7 @@
         <v>131153653</v>
       </c>
       <c r="B54" t="n">
-        <v>79011</v>
+        <v>79012</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6047,10 +6051,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131153651</v>
+        <v>131153709</v>
       </c>
       <c r="B55" t="n">
-        <v>79011</v>
+        <v>79254</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6058,37 +6062,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>433104</v>
+        <v>433034</v>
       </c>
       <c r="R55" t="n">
-        <v>6792573</v>
+        <v>6792553</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6129,7 +6130,6 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6148,10 +6148,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131153696</v>
+        <v>131153618</v>
       </c>
       <c r="B56" t="n">
-        <v>79253</v>
+        <v>79844</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6159,21 +6159,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6183,10 +6183,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>432758</v>
+        <v>433073</v>
       </c>
       <c r="R56" t="n">
-        <v>6792450</v>
+        <v>6792637</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6245,10 +6245,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>131153707</v>
+        <v>131153649</v>
       </c>
       <c r="B57" t="n">
-        <v>79253</v>
+        <v>79012</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6256,21 +6256,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6280,10 +6280,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>433128</v>
+        <v>432719</v>
       </c>
       <c r="R57" t="n">
-        <v>6792592</v>
+        <v>6792423</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6345,7 +6345,7 @@
         <v>131153697</v>
       </c>
       <c r="B58" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6442,7 +6442,7 @@
         <v>131153704</v>
       </c>
       <c r="B59" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6536,10 +6536,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>131153638</v>
+        <v>131153696</v>
       </c>
       <c r="B60" t="n">
-        <v>57888</v>
+        <v>79254</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6547,42 +6547,34 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>432927</v>
+        <v>432758</v>
       </c>
       <c r="R60" t="n">
-        <v>6792752</v>
+        <v>6792450</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6641,10 +6633,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131153618</v>
+        <v>131153707</v>
       </c>
       <c r="B61" t="n">
-        <v>79843</v>
+        <v>79254</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6652,21 +6644,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6676,10 +6668,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>433073</v>
+        <v>433128</v>
       </c>
       <c r="R61" t="n">
-        <v>6792637</v>
+        <v>6792592</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6738,10 +6730,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131153649</v>
+        <v>131153638</v>
       </c>
       <c r="B62" t="n">
-        <v>79011</v>
+        <v>57889</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6749,34 +6741,42 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>432719</v>
+        <v>432927</v>
       </c>
       <c r="R62" t="n">
-        <v>6792423</v>
+        <v>6792752</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6838,7 +6838,7 @@
         <v>131153693</v>
       </c>
       <c r="B63" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6935,7 +6935,7 @@
         <v>131153727</v>
       </c>
       <c r="B64" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7036,7 +7036,7 @@
         <v>131153633</v>
       </c>
       <c r="B65" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7248,7 +7248,7 @@
         <v>131153636</v>
       </c>
       <c r="B67" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7353,7 +7353,7 @@
         <v>131153634</v>
       </c>
       <c r="B68" t="n">
-        <v>57888</v>
+        <v>57889</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7455,45 +7455,54 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131153679</v>
+        <v>131153655</v>
       </c>
       <c r="B69" t="n">
-        <v>79010</v>
+        <v>8453</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6446</v>
+        <v>106545</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr"/>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>432956</v>
+        <v>432876</v>
       </c>
       <c r="R69" t="n">
-        <v>6792683</v>
+        <v>6792590</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7534,6 +7543,7 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7555,7 +7565,7 @@
         <v>131153620</v>
       </c>
       <c r="B70" t="n">
-        <v>79843</v>
+        <v>79844</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7656,7 +7666,7 @@
         <v>131153694</v>
       </c>
       <c r="B71" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7750,54 +7760,45 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131153655</v>
+        <v>131153679</v>
       </c>
       <c r="B72" t="n">
-        <v>8453</v>
+        <v>79011</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
-      <c r="J72" t="inlineStr"/>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>432876</v>
+        <v>432956</v>
       </c>
       <c r="R72" t="n">
-        <v>6792590</v>
+        <v>6792683</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7838,7 +7839,6 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
-      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -7857,10 +7857,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>131153619</v>
+        <v>131153711</v>
       </c>
       <c r="B73" t="n">
-        <v>79843</v>
+        <v>79254</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7868,21 +7868,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7892,10 +7892,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>433004</v>
+        <v>432942</v>
       </c>
       <c r="R73" t="n">
-        <v>6792784</v>
+        <v>6792639</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7954,10 +7954,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>131153726</v>
+        <v>131153699</v>
       </c>
       <c r="B74" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7989,10 +7989,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>432891</v>
+        <v>432849</v>
       </c>
       <c r="R74" t="n">
-        <v>6792834</v>
+        <v>6792408</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8051,10 +8051,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>131153721</v>
+        <v>131153625</v>
       </c>
       <c r="B75" t="n">
-        <v>79253</v>
+        <v>91843</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8062,21 +8062,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8089,10 +8089,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>432957</v>
+        <v>433119</v>
       </c>
       <c r="R75" t="n">
-        <v>6792790</v>
+        <v>6792436</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8125,11 +8125,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2026-02-14</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Måttligt med garnlav inom en radie av 50m</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8157,10 +8152,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>131153705</v>
+        <v>131153726</v>
       </c>
       <c r="B76" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8192,10 +8187,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>433133</v>
+        <v>432891</v>
       </c>
       <c r="R76" t="n">
-        <v>6792485</v>
+        <v>6792834</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8254,10 +8249,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>131153711</v>
+        <v>131153721</v>
       </c>
       <c r="B77" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8283,16 +8278,19 @@
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr"/>
+      <c r="N77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>432942</v>
+        <v>432957</v>
       </c>
       <c r="R77" t="n">
-        <v>6792639</v>
+        <v>6792790</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8327,12 +8325,18 @@
           <t>2026-02-14</t>
         </is>
       </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Måttligt med garnlav inom en radie av 50m</t>
+        </is>
+      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
       <c r="AE77" t="b">
         <v>0</v>
       </c>
+      <c r="AF77" t="inlineStr"/>
       <c r="AG77" t="b">
         <v>0</v>
       </c>
@@ -8351,10 +8355,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>131153699</v>
+        <v>131153705</v>
       </c>
       <c r="B78" t="n">
-        <v>79253</v>
+        <v>79254</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8386,10 +8390,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>432849</v>
+        <v>433133</v>
       </c>
       <c r="R78" t="n">
-        <v>6792408</v>
+        <v>6792485</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8448,10 +8452,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>131153625</v>
+        <v>131153639</v>
       </c>
       <c r="B79" t="n">
-        <v>91842</v>
+        <v>57889</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8459,26 +8463,31 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5442</v>
+        <v>100049</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
       <c r="K79" t="inlineStr"/>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
@@ -8486,10 +8495,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>433119</v>
+        <v>432988</v>
       </c>
       <c r="R79" t="n">
-        <v>6792436</v>
+        <v>6792798</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8530,7 +8539,6 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -8549,40 +8557,41 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>131153639</v>
+        <v>131153669</v>
       </c>
       <c r="B80" t="n">
-        <v>57888</v>
+        <v>8453</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N80" t="inlineStr"/>
@@ -8592,10 +8601,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>432988</v>
+        <v>432941</v>
       </c>
       <c r="R80" t="n">
-        <v>6792798</v>
+        <v>6792778</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8636,6 +8645,7 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -8654,54 +8664,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>131153669</v>
+        <v>131153619</v>
       </c>
       <c r="B81" t="n">
-        <v>8453</v>
+        <v>79844</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>432941</v>
+        <v>433004</v>
       </c>
       <c r="R81" t="n">
-        <v>6792778</v>
+        <v>6792784</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8742,7 +8743,6 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -8761,45 +8761,54 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>131153728</v>
+        <v>131153659</v>
       </c>
       <c r="B82" t="n">
-        <v>79253</v>
+        <v>8453</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>432945</v>
+        <v>433073</v>
       </c>
       <c r="R82" t="n">
-        <v>6792842</v>
+        <v>6792412</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8840,6 +8849,7 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -8861,7 +8871,7 @@
         <v>131153624</v>
       </c>
       <c r="B83" t="n">
-        <v>91842</v>
+        <v>91843</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8959,54 +8969,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>131153659</v>
+        <v>131153728</v>
       </c>
       <c r="B84" t="n">
-        <v>8453</v>
+        <v>79254</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>433073</v>
+        <v>432945</v>
       </c>
       <c r="R84" t="n">
-        <v>6792412</v>
+        <v>6792842</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9047,7 +9048,6 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
       </c>
@@ -9066,45 +9066,54 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131153617</v>
+        <v>131153664</v>
       </c>
       <c r="B85" t="n">
-        <v>79843</v>
+        <v>8453</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>432828</v>
+        <v>433001</v>
       </c>
       <c r="R85" t="n">
-        <v>6792424</v>
+        <v>6792569</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9145,6 +9154,7 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -9270,54 +9280,45 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131153664</v>
+        <v>131153617</v>
       </c>
       <c r="B87" t="n">
-        <v>8453</v>
+        <v>79844</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>433001</v>
+        <v>432828</v>
       </c>
       <c r="R87" t="n">
-        <v>6792569</v>
+        <v>6792424</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9358,7 +9359,6 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
-      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9377,10 +9377,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>131153642</v>
+        <v>131153717</v>
       </c>
       <c r="B88" t="n">
-        <v>57888</v>
+        <v>79254</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9388,42 +9388,34 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="K88" t="inlineStr"/>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>432888</v>
+        <v>432932</v>
       </c>
       <c r="R88" t="n">
-        <v>6792650</v>
+        <v>6792709</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9482,7 +9474,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>131153652</v>
+        <v>131153678</v>
       </c>
       <c r="B89" t="n">
         <v>79011</v>
@@ -9493,21 +9485,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9517,10 +9509,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>433073</v>
+        <v>433104</v>
       </c>
       <c r="R89" t="n">
-        <v>6792637</v>
+        <v>6792573</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9579,10 +9571,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131153717</v>
+        <v>131153642</v>
       </c>
       <c r="B90" t="n">
-        <v>79253</v>
+        <v>57889</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9590,34 +9582,42 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>432932</v>
+        <v>432888</v>
       </c>
       <c r="R90" t="n">
-        <v>6792709</v>
+        <v>6792650</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9676,10 +9676,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131153678</v>
+        <v>131153652</v>
       </c>
       <c r="B91" t="n">
-        <v>79010</v>
+        <v>79012</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9687,21 +9687,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -9711,10 +9711,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>433104</v>
+        <v>433073</v>
       </c>
       <c r="R91" t="n">
-        <v>6792573</v>
+        <v>6792637</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -9776,7 +9776,7 @@
         <v>131153681</v>
       </c>
       <c r="B92" t="n">
-        <v>57891</v>
+        <v>57892</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 1159-2026 artfynd.xlsx
+++ b/artfynd/A 1159-2026 artfynd.xlsx
@@ -1818,10 +1818,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>131153621</v>
+        <v>131153712</v>
       </c>
       <c r="B13" t="n">
-        <v>79844</v>
+        <v>79254</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1829,21 +1829,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1853,10 +1853,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>433070</v>
+        <v>432967</v>
       </c>
       <c r="R13" t="n">
-        <v>6792624</v>
+        <v>6792669</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1915,10 +1915,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>131153712</v>
+        <v>131153621</v>
       </c>
       <c r="B14" t="n">
-        <v>79254</v>
+        <v>79844</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1926,21 +1926,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1950,10 +1950,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>432967</v>
+        <v>433070</v>
       </c>
       <c r="R14" t="n">
-        <v>6792669</v>
+        <v>6792624</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -3230,10 +3230,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131153701</v>
+        <v>131153650</v>
       </c>
       <c r="B27" t="n">
-        <v>79254</v>
+        <v>79012</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3241,21 +3241,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3265,10 +3265,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>432958</v>
+        <v>433062</v>
       </c>
       <c r="R27" t="n">
-        <v>6792418</v>
+        <v>6792357</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3327,10 +3327,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131153650</v>
+        <v>131153701</v>
       </c>
       <c r="B28" t="n">
-        <v>79012</v>
+        <v>79254</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3338,21 +3338,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3362,10 +3362,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>433062</v>
+        <v>432958</v>
       </c>
       <c r="R28" t="n">
-        <v>6792357</v>
+        <v>6792418</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3529,41 +3529,40 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131153658</v>
+        <v>131153641</v>
       </c>
       <c r="B30" t="n">
-        <v>8453</v>
+        <v>57889</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
       <c r="M30" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N30" t="inlineStr"/>
@@ -3573,10 +3572,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>433053</v>
+        <v>432909</v>
       </c>
       <c r="R30" t="n">
-        <v>6792381</v>
+        <v>6792876</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3617,7 +3616,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -3636,7 +3634,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131153665</v>
+        <v>131153658</v>
       </c>
       <c r="B31" t="n">
         <v>8453</v>
@@ -3670,7 +3668,7 @@
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N31" t="inlineStr"/>
@@ -3680,10 +3678,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>432959</v>
+        <v>433053</v>
       </c>
       <c r="R31" t="n">
-        <v>6792711</v>
+        <v>6792381</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3743,45 +3741,54 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>131153616</v>
+        <v>131153665</v>
       </c>
       <c r="B32" t="n">
-        <v>79844</v>
+        <v>8453</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>432773</v>
+        <v>432959</v>
       </c>
       <c r="R32" t="n">
-        <v>6792537</v>
+        <v>6792711</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3822,6 +3829,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -3840,10 +3848,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131153690</v>
+        <v>131153616</v>
       </c>
       <c r="B33" t="n">
-        <v>79254</v>
+        <v>79844</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3851,37 +3859,34 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>432874</v>
+        <v>432773</v>
       </c>
       <c r="R33" t="n">
-        <v>6792733</v>
+        <v>6792537</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3922,7 +3927,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -3941,7 +3945,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131153716</v>
+        <v>131153690</v>
       </c>
       <c r="B34" t="n">
         <v>79254</v>
@@ -3970,16 +3974,19 @@
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>432960</v>
+        <v>432874</v>
       </c>
       <c r="R34" t="n">
-        <v>6792712</v>
+        <v>6792733</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4020,6 +4027,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4038,10 +4046,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>131153641</v>
+        <v>131153716</v>
       </c>
       <c r="B35" t="n">
-        <v>57889</v>
+        <v>79254</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4049,42 +4057,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>432909</v>
+        <v>432960</v>
       </c>
       <c r="R35" t="n">
-        <v>6792876</v>
+        <v>6792712</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4932,10 +4932,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131153710</v>
+        <v>131153643</v>
       </c>
       <c r="B44" t="n">
-        <v>79254</v>
+        <v>57889</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4943,34 +4943,42 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>433013</v>
+        <v>432969</v>
       </c>
       <c r="R44" t="n">
-        <v>6792587</v>
+        <v>6792418</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5029,10 +5037,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131153691</v>
+        <v>131153640</v>
       </c>
       <c r="B45" t="n">
-        <v>79254</v>
+        <v>57889</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5040,34 +5048,42 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>432881</v>
+        <v>432940</v>
       </c>
       <c r="R45" t="n">
-        <v>6792694</v>
+        <v>6792843</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5126,10 +5142,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>131153643</v>
+        <v>131153710</v>
       </c>
       <c r="B46" t="n">
-        <v>57889</v>
+        <v>79254</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5137,42 +5153,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>432969</v>
+        <v>433013</v>
       </c>
       <c r="R46" t="n">
-        <v>6792418</v>
+        <v>6792587</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5231,10 +5239,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>131153640</v>
+        <v>131153691</v>
       </c>
       <c r="B47" t="n">
-        <v>57889</v>
+        <v>79254</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5242,42 +5250,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>432940</v>
+        <v>432881</v>
       </c>
       <c r="R47" t="n">
-        <v>6792843</v>
+        <v>6792694</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6835,45 +6835,54 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131153693</v>
+        <v>131153654</v>
       </c>
       <c r="B63" t="n">
-        <v>79254</v>
+        <v>8453</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>432849</v>
+        <v>432866</v>
       </c>
       <c r="R63" t="n">
-        <v>6792616</v>
+        <v>6792755</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6914,6 +6923,7 @@
       <c r="AE63" t="b">
         <v>0</v>
       </c>
+      <c r="AF63" t="inlineStr"/>
       <c r="AG63" t="b">
         <v>0</v>
       </c>
@@ -6932,7 +6942,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>131153727</v>
+        <v>131153693</v>
       </c>
       <c r="B64" t="n">
         <v>79254</v>
@@ -6961,19 +6971,16 @@
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>432935</v>
+        <v>432849</v>
       </c>
       <c r="R64" t="n">
-        <v>6792834</v>
+        <v>6792616</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7014,7 +7021,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7033,10 +7039,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>131153633</v>
+        <v>131153727</v>
       </c>
       <c r="B65" t="n">
-        <v>57889</v>
+        <v>79254</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7044,31 +7050,26 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
@@ -7076,10 +7077,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>432972</v>
+        <v>432935</v>
       </c>
       <c r="R65" t="n">
-        <v>6792667</v>
+        <v>6792834</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7120,6 +7121,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7138,41 +7140,40 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>131153654</v>
+        <v>131153633</v>
       </c>
       <c r="B66" t="n">
-        <v>8453</v>
+        <v>57889</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
-      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N66" t="inlineStr"/>
@@ -7182,10 +7183,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>432866</v>
+        <v>432972</v>
       </c>
       <c r="R66" t="n">
-        <v>6792755</v>
+        <v>6792667</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7226,7 +7227,6 @@
       <c r="AE66" t="b">
         <v>0</v>
       </c>
-      <c r="AF66" t="inlineStr"/>
       <c r="AG66" t="b">
         <v>0</v>
       </c>
@@ -7245,10 +7245,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>131153636</v>
+        <v>131153694</v>
       </c>
       <c r="B67" t="n">
-        <v>57889</v>
+        <v>79254</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7256,42 +7256,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>432931</v>
+        <v>432842</v>
       </c>
       <c r="R67" t="n">
-        <v>6792717</v>
+        <v>6792572</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7350,10 +7342,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>131153634</v>
+        <v>131153679</v>
       </c>
       <c r="B68" t="n">
-        <v>57889</v>
+        <v>79011</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7361,42 +7353,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>432989</v>
+        <v>432956</v>
       </c>
       <c r="R68" t="n">
-        <v>6792671</v>
+        <v>6792683</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7455,41 +7439,40 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>131153655</v>
+        <v>131153636</v>
       </c>
       <c r="B69" t="n">
-        <v>8453</v>
+        <v>57889</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
-      <c r="J69" t="inlineStr"/>
       <c r="K69" t="inlineStr"/>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N69" t="inlineStr"/>
@@ -7499,10 +7482,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>432876</v>
+        <v>432931</v>
       </c>
       <c r="R69" t="n">
-        <v>6792590</v>
+        <v>6792717</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7543,7 +7526,6 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
-      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
       </c>
@@ -7562,10 +7544,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>131153620</v>
+        <v>131153634</v>
       </c>
       <c r="B70" t="n">
-        <v>79844</v>
+        <v>57889</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7573,26 +7555,31 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>229821</v>
+        <v>100049</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
-      <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
@@ -7600,10 +7587,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>433058</v>
+        <v>432989</v>
       </c>
       <c r="R70" t="n">
-        <v>6792468</v>
+        <v>6792671</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7644,7 +7631,6 @@
       <c r="AE70" t="b">
         <v>0</v>
       </c>
-      <c r="AF70" t="inlineStr"/>
       <c r="AG70" t="b">
         <v>0</v>
       </c>
@@ -7663,45 +7649,54 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>131153694</v>
+        <v>131153655</v>
       </c>
       <c r="B71" t="n">
-        <v>79254</v>
+        <v>8453</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr"/>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>432842</v>
+        <v>432876</v>
       </c>
       <c r="R71" t="n">
-        <v>6792572</v>
+        <v>6792590</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7742,6 +7737,7 @@
       <c r="AE71" t="b">
         <v>0</v>
       </c>
+      <c r="AF71" t="inlineStr"/>
       <c r="AG71" t="b">
         <v>0</v>
       </c>
@@ -7760,10 +7756,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>131153679</v>
+        <v>131153620</v>
       </c>
       <c r="B72" t="n">
-        <v>79011</v>
+        <v>79844</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7771,34 +7767,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>432956</v>
+        <v>433058</v>
       </c>
       <c r="R72" t="n">
-        <v>6792683</v>
+        <v>6792468</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7839,6 +7838,7 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
       </c>
@@ -9066,54 +9066,45 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>131153664</v>
+        <v>131153617</v>
       </c>
       <c r="B85" t="n">
-        <v>8453</v>
+        <v>79844</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>106545</v>
+        <v>229821</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>433001</v>
+        <v>432828</v>
       </c>
       <c r="R85" t="n">
-        <v>6792569</v>
+        <v>6792424</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9154,7 +9145,6 @@
       <c r="AE85" t="b">
         <v>0</v>
       </c>
-      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
       </c>
@@ -9173,7 +9163,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>131153666</v>
+        <v>131153664</v>
       </c>
       <c r="B86" t="n">
         <v>8453</v>
@@ -9207,7 +9197,7 @@
       <c r="L86" t="inlineStr"/>
       <c r="M86" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>färska gnagspår</t>
         </is>
       </c>
       <c r="N86" t="inlineStr"/>
@@ -9217,10 +9207,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>432913</v>
+        <v>433001</v>
       </c>
       <c r="R86" t="n">
-        <v>6792742</v>
+        <v>6792569</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9280,45 +9270,54 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>131153617</v>
+        <v>131153666</v>
       </c>
       <c r="B87" t="n">
-        <v>79844</v>
+        <v>8453</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>229821</v>
+        <v>106545</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>432828</v>
+        <v>432913</v>
       </c>
       <c r="R87" t="n">
-        <v>6792424</v>
+        <v>6792742</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9359,6 +9358,7 @@
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
       </c>
@@ -9571,10 +9571,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>131153642</v>
+        <v>131153652</v>
       </c>
       <c r="B90" t="n">
-        <v>57889</v>
+        <v>79012</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9582,42 +9582,34 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>432888</v>
+        <v>433073</v>
       </c>
       <c r="R90" t="n">
-        <v>6792650</v>
+        <v>6792637</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -9676,10 +9668,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>131153652</v>
+        <v>131153642</v>
       </c>
       <c r="B91" t="n">
-        <v>79012</v>
+        <v>57889</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9687,34 +9679,42 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Klittkarltjärnarna, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>433073</v>
+        <v>432888</v>
       </c>
       <c r="R91" t="n">
-        <v>6792637</v>
+        <v>6792650</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>

--- a/artfynd/A 1159-2026 artfynd.xlsx
+++ b/artfynd/A 1159-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY96"/>
+  <dimension ref="A1:AZ96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153624</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153625</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -971,6 +986,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153688</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1068,6 +1088,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153689</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1169,6 +1194,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153690</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1266,6 +1296,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153691</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1363,6 +1398,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153692</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1460,6 +1500,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153693</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1557,6 +1602,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153694</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1654,6 +1704,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153695</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1751,6 +1806,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153696</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1848,6 +1908,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153697</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1945,6 +2010,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153698</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2042,6 +2112,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153699</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2139,6 +2214,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153700</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2236,6 +2316,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153701</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2333,6 +2418,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153702</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2430,6 +2520,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153703</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2527,6 +2622,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153704</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2624,6 +2724,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153705</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2725,6 +2830,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153706</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2822,6 +2932,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153707</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2919,6 +3034,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153708</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3016,6 +3136,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153709</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3113,6 +3238,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153710</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3210,6 +3340,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153711</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3307,6 +3442,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153712</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3404,6 +3544,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153713</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3506,6 +3651,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153714</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3603,6 +3753,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153716</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3700,6 +3855,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153717</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3797,6 +3957,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153718</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3898,6 +4063,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153719</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3995,6 +4165,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153720</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4101,6 +4276,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153721</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4198,6 +4378,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153722</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4295,6 +4480,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153723</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4392,6 +4582,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153725</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4489,6 +4684,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153726</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4590,6 +4790,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153727</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4687,6 +4892,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153728</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4784,6 +4994,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153729</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4881,6 +5096,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153676</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -4978,6 +5198,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153677</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5075,6 +5300,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153678</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5172,6 +5402,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153679</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5277,6 +5512,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153628</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5382,6 +5622,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153630</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5487,6 +5732,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153631</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5592,6 +5842,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153632</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5697,6 +5952,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153633</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5802,6 +6062,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153634</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5907,6 +6172,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153635</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6012,6 +6282,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153636</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6117,6 +6392,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153638</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6222,6 +6502,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153639</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6327,6 +6612,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153640</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6432,6 +6722,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153641</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6537,6 +6832,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153642</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6642,6 +6942,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153643</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6747,6 +7052,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153622</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6852,6 +7162,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153681</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6959,6 +7274,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153645</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7064,6 +7384,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153674</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7171,6 +7496,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153654</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7278,6 +7608,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153655</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7385,6 +7720,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153656</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7492,6 +7832,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153657</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7599,6 +7944,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153658</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7706,6 +8056,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153659</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7813,6 +8168,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153660</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7920,6 +8280,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153661</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8027,6 +8392,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153662</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8134,6 +8504,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153663</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8241,6 +8616,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153664</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8348,6 +8728,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153665</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8455,6 +8840,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153666</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8562,6 +8952,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153667</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8669,6 +9064,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153668</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8776,6 +9176,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153669</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8883,6 +9288,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153670</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8990,6 +9400,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153671</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9097,6 +9512,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153672</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9204,6 +9624,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153673</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9301,6 +9726,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153649</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9398,6 +9828,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153650</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9499,6 +9934,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153651</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9596,6 +10036,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153652</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9697,6 +10142,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153653</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -9794,6 +10244,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153616</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -9891,6 +10346,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153617</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -9988,6 +10448,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153618</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10085,6 +10550,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153619</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10186,6 +10656,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153620</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10283,8 +10758,110 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131153621</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>